--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>419.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.5%</t>
+          <t>-686.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.8%</t>
+          <t>582.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.8%</t>
+          <t>-297.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-165.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.399720088096128</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>0.9103586383205362</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.2387486089204149</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.813852263224984</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.483541309370827</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.8796237713421378</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.2387486089204149</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.816645884756465</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.477388603318042</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.8827472021549099</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.2449013149731992</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.820999856779794</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.494197901468544</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.8751039596348194</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.2280920168226975</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.809994754629603</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.431899902692422</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>0.9663587129420892</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.2733862810971396</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.903506866991089</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-4.230109705027264</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.8493667937222793</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.471404473266294</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.824609784006709</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.280996417713459</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.8993023409699767</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.4205177605800994</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.864367988717167</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-4.194385675063652</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>0.9485743741459431</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.4991434917852577</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.926171163556306</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.254594973068937</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>0.9230266357685009</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.4389341937799732</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.888581565577807</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-4.205408324384585</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>0.9411929132821699</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.4389341937799732</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.887073183617735</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-4.161035192746017</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>0.9588050333730336</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.4833073254185418</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.913559930036313</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-4.183515543604901</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>0.9442066871680701</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.4833073254185418</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.907953724174903</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-4.135859813043846</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>0.9696507364202971</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.5309630559795975</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>2.942928919539341</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-4.035341654545091</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.014750373194524</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.631481214478352</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.008132188013319</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-4.019436325112738</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.007867177443337</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.5523685537691132</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>2.947419264063648</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.97459792350434</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.029900240697325</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.5569119867139827</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>2.954243026441198</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.994096379746348</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.0262617978316</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.5088273454340784</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.929553181304334</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.949893542660448</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.049822535193797</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.5530301825199788</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>2.961954486083711</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.957453208497495</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.045208669328226</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.6078335865297981</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>2.99324652895885</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.799161790958223</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.159773001526974</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.6078335865297981</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.04449429414189</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.591519787323747</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.241270507575018</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.8154755901642743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.167520200916829</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.540487694601218</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.256631572902299</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.8665076828868022</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.193087684788615</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.475263513474013</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.299908649445886</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>0.9317318640140079</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.249409597557643</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.437836493402879</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.31084042977362</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>0.9369834020431895</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.248521492674433</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.457948149437587</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.304052559690977</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>0.9480107470406087</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.256394692004125</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.429534886337704</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.475975635952141</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>0.8890351842941799</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.381567125377478</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.354752625312691</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.626001449579964</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>0.9638174453191926</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.546549391210303</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.328668541048883</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.628143059299346</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>0.9638174453191926</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.538257367224162</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896932</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.240790627939762</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.661487420126774</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.079743087742544</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.606005948261952</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.231898166546479</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.682598810410878</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.079743087742544</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.623560353988744</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.400374283516357</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.607063411027511</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.051795252025963</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.598646699963379</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.954118090886917</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.766835585267149</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>0.9570765823563301</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.523085195349461</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.931396987203764</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.766588049237314</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>0.9570765823563301</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.513749217846366</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-3.060598800497807</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.873813449770867</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.8278747690622879</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.595134255721109</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-3.086473198971833</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.900541512874903</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>0.872786377774029</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.659159043441801</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-3.079418508756659</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.900038744950517</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.8798410679892028</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.66006721356045</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-3.052467284430171</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>1.920825388325854</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>0.894721414016922</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.679001574821823</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784111</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-3.074011512260958</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.096310829338499</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>0.894721414016922</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.863104706966783</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-3.09641963006583</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.079464277119543</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>0.894721414016922</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.855221401869776</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-3.124643865643431</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.070228582438141</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>0.9126981664682305</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.868061452890199</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-3.134084791531961</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.122705929804576</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.035125284011622</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>3.997771441138081</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.033616930923246</v>
+        <v>-3.186358398867602</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.165784168593363</v>
+        <v>2.10468758141562</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>0.9828516766759808</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>3.969298371281997</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.109946908524152</v>
+        <v>-3.262688376468508</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.133363990446775</v>
+        <v>2.072267403269033</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>0.9828516766759808</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>3.967410184175773</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.203610853201693</v>
+        <v>-3.356352321146049</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.090718642178621</v>
+        <v>2.029622055000879</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.010353214102625</v>
+        <v>0.8891877319984394</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.978731336234621</v>
+        <v>3.906032046972109</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.365179278728948</v>
+        <v>-3.517920746673304</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.024525282177871</v>
+        <v>1.963428695000129</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.76240480820056</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.901095592166046</v>
+        <v>3.828396302903534</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.473479940599068</v>
+        <v>-3.626221408543424</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.994278424295742</v>
+        <v>1.933181837118</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.76240480820056</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.914168999031965</v>
+        <v>3.841469709769453</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.566627411902434</v>
+        <v>-3.71936887984679</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.949024632557335</v>
+        <v>1.887928045379593</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.6395755969180272</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.832476669045385</v>
+        <v>3.759777379782873</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.594528199011907</v>
+        <v>-3.747269666956263</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.936388358840548</v>
+        <v>1.875291771662806</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.6049786727750924</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810242555686626</v>
+        <v>3.737543266424114</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.717054301714801</v>
+        <v>-3.869795769659157</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.88414236173659</v>
+        <v>1.823045774558847</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.4824525700721985</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733491338042088</v>
+        <v>3.660792048779577</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.94756879790039</v>
+        <v>-4.100310265844746</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.858642522852858</v>
+        <v>1.797545935675116</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.2519380738866098</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.661888599921239</v>
+        <v>3.589189310658727</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.296313883124833</v>
+        <v>-4.449055351069189</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.859456207764927</v>
+        <v>1.798359620587185</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.143190119967712</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.736951546571747</v>
+        <v>3.664252257309236</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.450300300900974</v>
+        <v>-4.60304176884533</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.866841909800111</v>
+        <v>1.805745322622369</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.143190119967712</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.805931815717387</v>
+        <v>3.733232526454875</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.399778397073308</v>
+        <v>-4.552519865017664</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.873101873451298</v>
+        <v>1.812005286273556</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.143190119967712</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.791983017837508</v>
+        <v>3.719283728574996</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.652253551081032</v>
+        <v>-4.804995019025388</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.783982300903622</v>
+        <v>1.72288571372588</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.143190119967712</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.803853506892922</v>
+        <v>3.73115421763041</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.945149307560444</v>
+        <v>-5.0978907755048</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.668034532830801</v>
+        <v>1.606937945653059</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.143190119967712</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.805064041411865</v>
+        <v>3.732364752149354</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.131813435695253</v>
+        <v>-5.284554903639608</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.597490623804199</v>
+        <v>1.536394036626457</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.1164511491431521</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793142401144451</v>
+        <v>3.720443111881939</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.277834122609215</v>
+        <v>-5.430575590553571</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.534160201774804</v>
+        <v>1.473063614597062</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.1073680573492952</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.782770398804326</v>
+        <v>3.710071109541815</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.369548131718799</v>
+        <v>-5.522289599663155</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.659678654830014</v>
+        <v>1.598582067652272</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.1073680573492952</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94497445550337</v>
+        <v>3.872275166240859</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.401199790778769</v>
+        <v>-5.553941258723125</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.641864629169841</v>
+        <v>1.580768041992098</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.102199600104855</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93672001912052</v>
+        <v>3.864020729858009</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868148</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.483134609047652</v>
+        <v>-5.635876076992008</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.619320119430779</v>
+        <v>1.558223532253036</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.09226485451777477</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940988589336763</v>
+        <v>3.868289300074252</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332693</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.58511073129606</v>
+        <v>-5.737852199240415</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.587455308987318</v>
+        <v>1.526358721809576</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>-0.0097112677306328</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888728554443621</v>
+        <v>3.81602926518111</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79829678423181</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.475104447818838</v>
+        <v>-5.627845915763194</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.623610709622382</v>
+        <v>1.562514122444639</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.01349330418664241</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.894804184838162</v>
+        <v>3.82210489557565</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.332044872077912</v>
+        <v>-5.484786340022268</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.685084550640727</v>
+        <v>1.623987963462985</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.02150673077662169</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903862251514123</v>
+        <v>3.831162962251612</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.030598146606074</v>
+        <v>-5.18333961455043</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.812924123711998</v>
+        <v>1.751827536534255</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.3229534562484589</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.091991169679762</v>
+        <v>4.01929188041725</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.055188390841258</v>
+        <v>-5.207929858785614</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.804059203770635</v>
+        <v>1.742962616592893</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.3229534562484589</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.092962347432472</v>
+        <v>4.020263058169961</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.004150014834738</v>
+        <v>-5.156891482779094</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.825317458552999</v>
+        <v>1.764220871375256</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.3229534562484589</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093805251812228</v>
+        <v>4.021105962549717</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.963010719968107</v>
+        <v>-5.115752187912463</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.860811275373796</v>
+        <v>1.799714688196054</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.3640927511150898</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.137526927606352</v>
+        <v>4.06482763834384</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.866375807949467</v>
+        <v>-5.019117275893823</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.715649236305187</v>
+        <v>1.654552649127444</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.4607276631337297</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011691870941471</v>
+        <v>3.938992581678959</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.99695654248031</v>
+        <v>-5.149698010424665</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.666918986566814</v>
+        <v>1.605822399389071</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4513124107070731</v>
+        <v>0.3301469286028872</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936845474296929</v>
+        <v>3.864146185034418</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.832460208289348</v>
+        <v>-4.985201676233704</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.717144339319281</v>
+        <v>1.656047752141539</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.4946432627938491</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.019970093887589</v>
+        <v>3.947270804625077</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.85983014097378</v>
+        <v>-5.012571608918136</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.705384076681938</v>
+        <v>1.644287489504196</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.4946432627938491</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019157804324019</v>
+        <v>3.946458515061507</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.870215335863669</v>
+        <v>-5.022956803808025</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.711098777851055</v>
+        <v>1.650002190673312</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6054235500081456</v>
+        <v>0.4842580679039598</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.022795466515158</v>
+        <v>3.950096177252646</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.888803494585894</v>
+        <v>-5.04154496253025</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.77450052013859</v>
+        <v>1.713403932960848</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5868353912859203</v>
+        <v>0.4656699091817344</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.082479577058248</v>
+        <v>4.009780287795736</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.88910204128193</v>
+        <v>-5.041843509226286</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.771250112278474</v>
+        <v>1.710153525100732</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5865368445898844</v>
+        <v>0.4653713624856985</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079169459858925</v>
+        <v>4.006470170596413</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.788278907591502</v>
+        <v>-4.941020375535858</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.816110260694037</v>
+        <v>1.755013673516294</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5990010600742383</v>
+        <v>0.4778355779700523</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091178884088928</v>
+        <v>4.018479594826417</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.597497546839096</v>
+        <v>-4.750239014783451</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.892552058473543</v>
+        <v>1.8314554712958</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7897824208266456</v>
+        <v>0.6686169387224596</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.205776954018916</v>
+        <v>4.133077664756404</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.490534188989674</v>
+        <v>-4.64327565693403</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.915174247350908</v>
+        <v>1.854077660173165</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8482470287864471</v>
+        <v>0.7270815466822611</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.220692564532393</v>
+        <v>4.147993275269882</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.435203601087911</v>
+        <v>-4.587945069032267</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.972273419123671</v>
+        <v>1.911176831945929</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>0.7824121345840233</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.216158564622997</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.423149474174949</v>
+        <v>-4.575890942119305</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.970781637790294</v>
+        <v>1.909685050612552</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>0.7944662614969861</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.217077608672213</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.46430459374317</v>
+        <v>-4.617046061687526</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.956200220147141</v>
+        <v>1.895103632969399</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>0.7533111419287651</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.194265167115416</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.39625603105164</v>
+        <v>-4.548997498995996</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.996270671101636</v>
+        <v>1.935174083923894</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.821359704620295</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320644619870728</v>
+        <v>4.247945330608216</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.62785642422114</v>
+        <v>-4.780597892165496</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.92383318400743</v>
+        <v>1.862736596829688</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.821359704620295</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340847290044322</v>
+        <v>4.26814800078181</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.645928932512752</v>
+        <v>-4.798670400457108</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.916604180690785</v>
+        <v>1.855507593513043</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.821359704620295</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.340847290044322</v>
+        <v>4.26814800078181</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.821035765089198</v>
+        <v>-4.973777233033553</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.806813361253674</v>
+        <v>1.745716774075931</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.821359704620295</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.301099203637789</v>
+        <v>4.228399914375277</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.789749744548742</v>
+        <v>-4.942491212493098</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.826350388466796</v>
+        <v>1.765253801289054</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9738112072649363</v>
+        <v>0.8526457251607503</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.326893434959002</v>
+        <v>4.25419414569649</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.636724352435458</v>
+        <v>-4.789465820379814</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.986731544885014</v>
+        <v>1.925634957707272</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.12683659937822</v>
+        <v>1.005671117274034</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.517879669799877</v>
+        <v>4.445180380537366</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073884</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.665031666308728</v>
+        <v>-4.817773134253084</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.162874844243998</v>
+        <v>2.101778257066256</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.12683659937822</v>
+        <v>1.005671117274034</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.705345894708169</v>
+        <v>4.632646605445657</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.83162489142225</v>
+        <v>-4.984366359366606</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.065640505552671</v>
+        <v>2.004543918374929</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.839077892160512</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.574792910994137</v>
+        <v>4.502093621731627</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568383</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.808589098060684</v>
+        <v>-4.96133056600504</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.078531225559016</v>
+        <v>2.017434638381273</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.839077892160512</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.578469313655855</v>
+        <v>4.505770024393344</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682205</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.779343117604988</v>
+        <v>-4.932084585549344</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.08784767286479</v>
+        <v>2.026751085687047</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.839077892160512</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.57608736877935</v>
+        <v>4.50338807951684</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.886268665482839</v>
+        <v>-5.039010133427195</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.042370692871284</v>
+        <v>1.981274105693541</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8533178263868465</v>
+        <v>0.7321523442826606</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.509225279210275</v>
+        <v>4.436525989947763</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.031287223990088</v>
+        <v>-5.184028691934444</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.985792071611619</v>
+        <v>1.924695484433876</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.708299267879598</v>
+        <v>0.5871337857754121</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.42364294624916</v>
+        <v>4.350943656986648</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.149628989774805</v>
+        <v>-5.302370457719161</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.038386604555485</v>
+        <v>1.977290017377742</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.718985306442488</v>
+        <v>0.5978198243383022</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.529985808644647</v>
+        <v>4.457286519382135</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073534</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.201039412095513</v>
+        <v>-5.353780880039869</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.01560813275314</v>
+        <v>1.954511545575398</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.718985306442488</v>
+        <v>0.5978198243383022</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.527771505770586</v>
+        <v>4.455072216508074</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.280458863303265</v>
+        <v>-5.433200331247621</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.983743480344329</v>
+        <v>1.922646893166587</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.718985306442488</v>
+        <v>0.5978198243383022</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.527674633844875</v>
+        <v>4.454975344582364</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.375921861220482</v>
+        <v>-5.528663329164838</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.945552174735485</v>
+        <v>1.884455587557743</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.718985306442488</v>
+        <v>0.5978198243383022</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.527668527402919</v>
+        <v>4.454969238140407</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500737</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.415941859264266</v>
+        <v>-5.568683327208622</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.927640572080583</v>
+        <v>1.86654398490284</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.5577998262945183</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.501752925139259</v>
+        <v>4.429053635876747</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636272</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.47131102139646</v>
+        <v>-5.624052489340816</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.911226724975432</v>
+        <v>1.850130137797689</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.5577998262945183</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.507486742886986</v>
+        <v>4.434787453624474</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396015</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.516748801227287</v>
+        <v>-5.669490269171643</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.892589976386034</v>
+        <v>1.831493389208291</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.5149548356163587</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.481318111823023</v>
+        <v>4.408618822560511</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396424</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.428541967079709</v>
+        <v>-5.581283435024065</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.947747102895384</v>
+        <v>1.886650515717642</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.5149548356163587</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.501192504673342</v>
+        <v>4.42849321541083</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299178</v>
+        <v>3.794507029299172</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.252251742474401</v>
+        <v>-5.404993210418757</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.001963893262235</v>
+        <v>1.940867306084493</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.5149548356163587</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.48489320519807</v>
+        <v>4.412193915935559</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590409</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.069040079341306</v>
+        <v>-5.221781547285662</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.077679507979519</v>
+        <v>2.016582920801776</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.5149548356163587</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.487324154662115</v>
+        <v>4.414624865399604</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146288</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.997318632327455</v>
+        <v>-5.150060100271811</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.072159272632948</v>
+        <v>2.011062685455206</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7078417647343952</v>
+        <v>0.5866762826302093</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.496148208718315</v>
+        <v>4.423448919455804</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72380989067685</v>
+        <v>3.723809890676844</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.974945606719749</v>
+        <v>-5.127687074664105</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.028024228797203</v>
+        <v>1.96692764161946</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7190975158472968</v>
+        <v>0.5979320337431109</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.449817405307228</v>
+        <v>4.377118116044716</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739467</v>
+        <v>3.715627631739461</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.007961902630494</v>
+        <v>-5.16070337057485</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.20001591531826</v>
+        <v>2.138919328140518</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6496601391805452</v>
+        <v>0.5284946570763593</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.593353184192532</v>
+        <v>4.520653894930021</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166414</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.996434266980885</v>
+        <v>-5.149175734925241</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.196548195406352</v>
+        <v>2.13545160822861</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7086607973819077</v>
+        <v>0.5874953152777218</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.620674804941599</v>
+        <v>4.547975515679087</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519034</v>
+        <v>3.717170884519029</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.093775768323254</v>
+        <v>-5.24651723626761</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.161279707391194</v>
+        <v>2.100183120213452</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6642406152164193</v>
+        <v>0.5430751331122334</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.597690808164095</v>
+        <v>4.524991518901583</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710421</v>
+        <v>3.705221264710415</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.17963179766322</v>
+        <v>-5.332373265607576</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.128188377848045</v>
+        <v>2.067091790670303</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6218645459902843</v>
+        <v>0.5006990638860984</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.573516248821251</v>
+        <v>4.50081695955874</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893118</v>
+        <v>3.691855684893112</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.162822873263949</v>
+        <v>-5.315564341208305</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.117331149428256</v>
+        <v>2.056234562250513</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6459306416786644</v>
+        <v>0.5247651595744786</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.570375108054781</v>
+        <v>4.49767581879227</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.784889698262933</v>
+        <v>3.441790048094938</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.249165943767011</v>
+        <v>-5.2516299161104</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.09295843227208</v>
+        <v>2.091972843334724</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5595875711756029</v>
+        <v>0.5886995846723839</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.528733776797994</v>
+        <v>4.546200984896062</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.9%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.7%</t>
+          <t>-687.0%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-167.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>582.6%</t>
+          <t>588.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-297.0%</t>
+          <t>-308.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-165.1%</t>
+          <t>-168.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.399720088096128</v>
+        <v>-4.246978620151772</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9103586383205362</v>
+        <v>0.9714552254982785</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2387486089204149</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.813852263224984</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.483541309370827</v>
+        <v>-4.330799841426471</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8796237713421378</v>
+        <v>0.9407203585198802</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2387486089204149</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.816645884756465</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.477388603318042</v>
+        <v>-4.324647135373686</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8827472021549099</v>
+        <v>0.9438437893326523</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2449013149731992</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.820999856779794</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.494197901468544</v>
+        <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8751039596348194</v>
+        <v>0.9362005468125618</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2280920168226975</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.809994754629603</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.431899902692422</v>
+        <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9663587129420892</v>
+        <v>1.027455300119831</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2733862810971396</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.903506866991089</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.230109705027264</v>
+        <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8493667937222793</v>
+        <v>0.9104633809000218</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.471404473266294</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.824609784006709</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.280996417713459</v>
+        <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8993023409699767</v>
+        <v>0.9603989281477192</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4205177605800994</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.864367988717167</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.194385675063652</v>
+        <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9485743741459431</v>
+        <v>1.009670961323685</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4991434917852577</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.926171163556306</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.254594973068937</v>
+        <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9230266357685009</v>
+        <v>0.9841232229462431</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4389341937799732</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.888581565577807</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.205408324384585</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9411929132821699</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4389341937799732</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.887073183617735</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.161035192746017</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9588050333730336</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4833073254185418</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.913559930036313</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.183515543604901</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9442066871680701</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4833073254185418</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.907953724174903</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.135859813043846</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9696507364202971</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5309630559795975</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.942928919539341</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.035341654545091</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.014750373194524</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.631481214478352</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.008132188013319</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.019436325112738</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.007867177443337</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5523685537691132</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.947419264063648</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.97459792350434</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.029900240697325</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5569119867139827</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.954243026441198</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.994096379746348</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.0262617978316</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5088273454340784</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.929553181304334</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.949893542660448</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.049822535193797</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5530301825199788</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.961954486083711</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.957453208497495</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.045208669328226</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6078335865297981</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.99324652895885</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.799161790958223</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.159773001526974</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6078335865297981</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.04449429414189</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.591519787323747</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.241270507575018</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8154755901642743</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.167520200916829</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.540487694601218</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.256631572902299</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8665076828868022</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.193087684788615</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.475263513474013</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.299908649445886</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9317318640140079</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.249409597557643</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.437836493402879</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.31084042977362</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9369834020431895</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.248521492674433</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.457948149437587</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.304052559690977</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9480107470406087</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.256394692004125</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.429534886337704</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.475975635952141</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8890351842941799</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.381567125377478</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.354752625312691</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.626001449579964</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9638174453191926</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.546549391210303</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.328668541048883</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.628143059299346</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9638174453191926</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.538257367224162</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.240790627939762</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.661487420126774</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.079743087742544</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.606005948261952</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.231898166546479</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.682598810410878</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.079743087742544</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.623560353988744</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.400374283516357</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.607063411027511</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.051795252025963</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.598646699963379</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.954118090886917</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.766835585267149</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9570765823563301</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.523085195349461</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.931396987203764</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.766588049237314</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9570765823563301</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.513749217846366</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.060598800497807</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.873813449770867</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8278747690622879</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.595134255721109</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.086473198971833</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.900541512874903</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.872786377774029</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.659159043441801</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.079418508756659</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.900038744950517</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8798410679892028</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.66006721356045</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.052467284430171</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.920825388325854</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.894721414016922</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.679001574821823</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.074011512260958</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.096310829338499</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.894721414016922</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.863104706966783</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.09641963006583</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.079464277119543</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.894721414016922</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.855221401869776</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.124643865643431</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.070228582438141</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9126981664682305</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.868061452890199</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.134084791531961</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.122705929804576</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.035125284011622</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.997771441138081</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.186358398867602</v>
+        <v>-3.033616930923246</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.10468758141562</v>
+        <v>2.165784168593363</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9828516766759808</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.969298371281997</v>
+        <v>4.041997660544508</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.262688376468508</v>
+        <v>-3.109946908524152</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.072267403269033</v>
+        <v>2.133363990446775</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9828516766759808</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.967410184175773</v>
+        <v>4.040109473438283</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.356352321146049</v>
+        <v>-3.203610853201693</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.029622055000879</v>
+        <v>2.090718642178621</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8891877319984394</v>
+        <v>1.010353214102625</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.906032046972109</v>
+        <v>3.978731336234621</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.517920746673304</v>
+        <v>-3.365179278728948</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.963428695000129</v>
+        <v>2.024525282177871</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.76240480820056</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.828396302903534</v>
+        <v>3.901095592166046</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.626221408543424</v>
+        <v>-3.473479940599068</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.933181837118</v>
+        <v>1.994278424295742</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.76240480820056</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.841469709769453</v>
+        <v>3.914168999031965</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.71936887984679</v>
+        <v>-3.566627411902434</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.887928045379593</v>
+        <v>1.949024632557335</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6395755969180272</v>
+        <v>0.7607410790222131</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.759777379782873</v>
+        <v>3.832476669045385</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.747269666956263</v>
+        <v>-3.594528199011907</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.875291771662806</v>
+        <v>1.936388358840548</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6049786727750924</v>
+        <v>0.7261441548792783</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.737543266424114</v>
+        <v>3.810242555686626</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.869795769659157</v>
+        <v>-3.717054301714801</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.823045774558847</v>
+        <v>1.88414236173659</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4824525700721985</v>
+        <v>0.6036180521763844</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.660792048779577</v>
+        <v>3.733491338042088</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.100310265844746</v>
+        <v>-3.94756879790039</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.797545935675116</v>
+        <v>1.858642522852858</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2519380738866098</v>
+        <v>0.3731035559907957</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.589189310658727</v>
+        <v>3.661888599921239</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.449055351069189</v>
+        <v>-4.296313883124833</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.798359620587185</v>
+        <v>1.859456207764927</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.143190119967712</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.664252257309236</v>
+        <v>3.736951546571747</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.60304176884533</v>
+        <v>-4.450300300900974</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.805745322622369</v>
+        <v>1.866841909800111</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.143190119967712</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.733232526454875</v>
+        <v>3.805931815717387</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.552519865017664</v>
+        <v>-4.399778397073308</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.812005286273556</v>
+        <v>1.873101873451298</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.143190119967712</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.719283728574996</v>
+        <v>3.791983017837508</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.804995019025388</v>
+        <v>-4.652253551081032</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.72288571372588</v>
+        <v>1.783982300903622</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.143190119967712</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.73115421763041</v>
+        <v>3.803853506892922</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.0978907755048</v>
+        <v>-4.945149307560444</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.606937945653059</v>
+        <v>1.668034532830801</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.143190119967712</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.732364752149354</v>
+        <v>3.805064041411865</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.284554903639608</v>
+        <v>-5.131813435695253</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.536394036626457</v>
+        <v>1.597490623804199</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1164511491431521</v>
+        <v>0.237616631247338</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.720443111881939</v>
+        <v>3.793142401144451</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.430575590553571</v>
+        <v>-5.277834122609215</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.473063614597062</v>
+        <v>1.534160201774804</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1073680573492952</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.710071109541815</v>
+        <v>3.782770398804326</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.522289599663155</v>
+        <v>-5.369548131718799</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.598582067652272</v>
+        <v>1.659678654830014</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1073680573492952</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.872275166240859</v>
+        <v>3.94497445550337</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.553941258723125</v>
+        <v>-5.401199790778769</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.580768041992098</v>
+        <v>1.641864629169841</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.102199600104855</v>
+        <v>0.2233650822090408</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.864020729858009</v>
+        <v>3.93672001912052</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.635876076992008</v>
+        <v>-5.483134609047652</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.558223532253036</v>
+        <v>1.619320119430779</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.09226485451777477</v>
+        <v>0.2134303366219606</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.868289300074252</v>
+        <v>3.940988589336763</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.737852199240415</v>
+        <v>-5.58511073129606</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.526358721809576</v>
+        <v>1.587455308987318</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0097112677306328</v>
+        <v>0.1114542143735531</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.81602926518111</v>
+        <v>3.888728554443621</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.627845915763194</v>
+        <v>-5.475104447818838</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.562514122444639</v>
+        <v>1.623610709622382</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01349330418664241</v>
+        <v>0.1346587862908283</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.82210489557565</v>
+        <v>3.894804184838162</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.484786340022268</v>
+        <v>-5.332044872077912</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.623987963462985</v>
+        <v>1.685084550640727</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.02150673077662169</v>
+        <v>0.1426722128808076</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.831162962251612</v>
+        <v>3.903862251514123</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.18333961455043</v>
+        <v>-5.030598146606074</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.751827536534255</v>
+        <v>1.812924123711998</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3229534562484589</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.01929188041725</v>
+        <v>4.091991169679762</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.207929858785614</v>
+        <v>-5.055188390841258</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.742962616592893</v>
+        <v>1.804059203770635</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3229534562484589</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.020263058169961</v>
+        <v>4.092962347432472</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.156891482779094</v>
+        <v>-5.004150014834738</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.764220871375256</v>
+        <v>1.825317458552999</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3229534562484589</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.021105962549717</v>
+        <v>4.093805251812228</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.115752187912463</v>
+        <v>-4.963010719968107</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.799714688196054</v>
+        <v>1.860811275373796</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3640927511150898</v>
+        <v>0.4852582332192756</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.06482763834384</v>
+        <v>4.137526927606352</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.019117275893823</v>
+        <v>-4.866375807949467</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.654552649127444</v>
+        <v>1.715649236305187</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4607276631337297</v>
+        <v>0.5818931452379156</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.938992581678959</v>
+        <v>4.011691870941471</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.149698010424665</v>
+        <v>-4.99695654248031</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.605822399389071</v>
+        <v>1.666918986566814</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3301469286028872</v>
+        <v>0.4513124107070731</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.864146185034418</v>
+        <v>3.936845474296929</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.985201676233704</v>
+        <v>-4.832460208289348</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.656047752141539</v>
+        <v>1.717144339319281</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4946432627938491</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.947270804625077</v>
+        <v>4.019970093887589</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.012571608918136</v>
+        <v>-4.85983014097378</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.644287489504196</v>
+        <v>1.705384076681938</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4946432627938491</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.946458515061507</v>
+        <v>4.019157804324019</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.022956803808025</v>
+        <v>-4.870215335863669</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.650002190673312</v>
+        <v>1.711098777851055</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4842580679039598</v>
+        <v>0.6054235500081456</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.950096177252646</v>
+        <v>4.022795466515158</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.04154496253025</v>
+        <v>-4.888803494585894</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.713403932960848</v>
+        <v>1.77450052013859</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4656699091817344</v>
+        <v>0.5868353912859203</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.009780287795736</v>
+        <v>4.082479577058248</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.041843509226286</v>
+        <v>-4.88910204128193</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.710153525100732</v>
+        <v>1.771250112278474</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4653713624856985</v>
+        <v>0.5865368445898844</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.006470170596413</v>
+        <v>4.079169459858925</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.941020375535858</v>
+        <v>-4.788278907591502</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.755013673516294</v>
+        <v>1.816110260694037</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4778355779700523</v>
+        <v>0.5990010600742383</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.018479594826417</v>
+        <v>4.091178884088928</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.750239014783451</v>
+        <v>-4.597497546839096</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.8314554712958</v>
+        <v>1.892552058473543</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6686169387224596</v>
+        <v>0.7897824208266456</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.133077664756404</v>
+        <v>4.205776954018916</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.64327565693403</v>
+        <v>-4.490534188989674</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.854077660173165</v>
+        <v>1.915174247350908</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7270815466822611</v>
+        <v>0.8482470287864471</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.147993275269882</v>
+        <v>4.220692564532393</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.587945069032267</v>
+        <v>-4.435203601087911</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.911176831945929</v>
+        <v>1.972273419123671</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7824121345840233</v>
+        <v>0.9035776166882092</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.216158564622997</v>
+        <v>4.288857853885509</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.575890942119305</v>
+        <v>-4.423149474174949</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.909685050612552</v>
+        <v>1.970781637790294</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7944662614969861</v>
+        <v>0.9156317436011721</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.217077608672213</v>
+        <v>4.289776897934725</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.617046061687526</v>
+        <v>-4.46430459374317</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.895103632969399</v>
+        <v>1.956200220147141</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7533111419287651</v>
+        <v>0.8744766240329511</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.194265167115416</v>
+        <v>4.266964456377927</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.548997498995996</v>
+        <v>-4.39625603105164</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.935174083923894</v>
+        <v>1.996270671101636</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.821359704620295</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.247945330608216</v>
+        <v>4.320644619870728</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.780597892165496</v>
+        <v>-4.62785642422114</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.862736596829688</v>
+        <v>1.92383318400743</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.821359704620295</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.26814800078181</v>
+        <v>4.340847290044322</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.798670400457108</v>
+        <v>-4.645928932512752</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.855507593513043</v>
+        <v>1.916604180690785</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.821359704620295</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.26814800078181</v>
+        <v>4.340847290044322</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.973777233033553</v>
+        <v>-4.821035765089198</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.745716774075931</v>
+        <v>1.806813361253674</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.821359704620295</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.228399914375277</v>
+        <v>4.301099203637789</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.942491212493098</v>
+        <v>-4.789749744548742</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.765253801289054</v>
+        <v>1.826350388466796</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8526457251607503</v>
+        <v>0.9738112072649363</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.25419414569649</v>
+        <v>4.326893434959002</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.789465820379814</v>
+        <v>-4.636724352435458</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.925634957707272</v>
+        <v>1.986731544885014</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.005671117274034</v>
+        <v>1.12683659937822</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.445180380537366</v>
+        <v>4.517879669799877</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741298518073882</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.817773134253084</v>
+        <v>-4.665031666308728</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.101778257066256</v>
+        <v>2.162874844243998</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.005671117274034</v>
+        <v>1.12683659937822</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.632646605445657</v>
+        <v>4.705345894708169</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.984366359366606</v>
+        <v>-4.83162489142225</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.004543918374929</v>
+        <v>2.065640505552671</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.839077892160512</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.502093621731627</v>
+        <v>4.574792910994137</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.96133056600504</v>
+        <v>-4.808589098060684</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.017434638381273</v>
+        <v>2.078531225559016</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.839077892160512</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.505770024393344</v>
+        <v>4.578469313655855</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.932084585549344</v>
+        <v>-4.779343117604988</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.026751085687047</v>
+        <v>2.08784767286479</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.839077892160512</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.50338807951684</v>
+        <v>4.57608736877935</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539106</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.039010133427195</v>
+        <v>-4.886268665482839</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.981274105693541</v>
+        <v>2.042370692871284</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7321523442826606</v>
+        <v>0.8533178263868465</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.436525989947763</v>
+        <v>4.509225279210275</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.184028691934444</v>
+        <v>-5.031287223990088</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.924695484433876</v>
+        <v>1.985792071611619</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5871337857754121</v>
+        <v>0.708299267879598</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.350943656986648</v>
+        <v>4.42364294624916</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969748</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.302370457719161</v>
+        <v>-5.149628989774805</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.977290017377742</v>
+        <v>2.038386604555485</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5978198243383022</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.457286519382135</v>
+        <v>4.529985808644647</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073534</v>
+        <v>3.714899237073538</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.353780880039869</v>
+        <v>-5.201039412095513</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.954511545575398</v>
+        <v>2.01560813275314</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5978198243383022</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.455072216508074</v>
+        <v>4.527771505770586</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.433200331247621</v>
+        <v>-5.280458863303265</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.922646893166587</v>
+        <v>1.983743480344329</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5978198243383022</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.454975344582364</v>
+        <v>4.527674633844875</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.528663329164838</v>
+        <v>-5.375921861220482</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.884455587557743</v>
+        <v>1.945552174735485</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5978198243383022</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.454969238140407</v>
+        <v>4.527668527402919</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.568683327208622</v>
+        <v>-5.415941859264266</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.86654398490284</v>
+        <v>1.927640572080583</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5577998262945183</v>
+        <v>0.6789653083987042</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.429053635876747</v>
+        <v>4.501752925139259</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.624052489340816</v>
+        <v>-5.47131102139646</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.850130137797689</v>
+        <v>1.911226724975432</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5577998262945183</v>
+        <v>0.6789653083987042</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.434787453624474</v>
+        <v>4.507486742886986</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.669490269171643</v>
+        <v>-5.516748801227287</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.831493389208291</v>
+        <v>1.892589976386034</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5149548356163587</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.408618822560511</v>
+        <v>4.481318111823023</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.581283435024065</v>
+        <v>-5.428541967079709</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.886650515717642</v>
+        <v>1.947747102895384</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5149548356163587</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.42849321541083</v>
+        <v>4.501192504673342</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299172</v>
+        <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.404993210418757</v>
+        <v>-5.252251742474401</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.940867306084493</v>
+        <v>2.001963893262235</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5149548356163587</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.412193915935559</v>
+        <v>4.48489320519807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.221781547285662</v>
+        <v>-5.069040079341306</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.016582920801776</v>
+        <v>2.077679507979519</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5149548356163587</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.414624865399604</v>
+        <v>4.487324154662115</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.150060100271811</v>
+        <v>-4.997318632327455</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.011062685455206</v>
+        <v>2.072159272632948</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5866762826302093</v>
+        <v>0.7078417647343952</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.423448919455804</v>
+        <v>4.496148208718315</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676844</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.127687074664105</v>
+        <v>-4.974945606719749</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.96692764161946</v>
+        <v>2.028024228797203</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5979320337431109</v>
+        <v>0.7190975158472968</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.377118116044716</v>
+        <v>4.449817405307228</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739461</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.16070337057485</v>
+        <v>-5.007961902630494</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.138919328140518</v>
+        <v>2.20001591531826</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5284946570763593</v>
+        <v>0.6496601391805452</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.520653894930021</v>
+        <v>4.593353184192532</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.149175734925241</v>
+        <v>-4.996434266980885</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.13545160822861</v>
+        <v>2.196548195406352</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5874953152777218</v>
+        <v>0.7086607973819077</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.547975515679087</v>
+        <v>4.620674804941599</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519029</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.24651723626761</v>
+        <v>-5.093775768323254</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.100183120213452</v>
+        <v>2.161279707391194</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5430751331122334</v>
+        <v>0.6642406152164193</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.524991518901583</v>
+        <v>4.597690808164095</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710415</v>
+        <v>3.705221264710419</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.332373265607576</v>
+        <v>-5.17963179766322</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.067091790670303</v>
+        <v>2.128188377848045</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5006990638860984</v>
+        <v>0.6218645459902843</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.50081695955874</v>
+        <v>4.573516248821251</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893112</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.315564341208305</v>
+        <v>-5.162822873263949</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.056234562250513</v>
+        <v>2.117331149428256</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5247651595744786</v>
+        <v>0.6459306416786644</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.49767581879227</v>
+        <v>4.570375108054781</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.441790048094938</v>
+        <v>3.85167003146926</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.2516299161104</v>
+        <v>-5.254205435829408</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.091972843334724</v>
+        <v>2.090942635447122</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5886995846723839</v>
+        <v>0.5545480791132062</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.546200984896062</v>
+        <v>4.525710081560556</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.0%</t>
+          <t>-677.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.1%</t>
+          <t>-163.4%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.8%</t>
+          <t>589.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.5%</t>
+          <t>-306.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.5%</t>
+          <t>-168.1%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.765664472138297</v>
+        <v>-8.67740134386217</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3398267043036332</v>
+        <v>-0.3045214529931823</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.488355021484225</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.667757433461807</v>
+        <v>-8.57949430518568</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3009642038064975</v>
+        <v>-0.2656589524960467</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.420369271623669</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.643803892485849</v>
+        <v>-8.555540764209722</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2907142812706209</v>
+        <v>-0.2554090299601701</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.396415730647711</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.379743954163052</v>
+        <v>-8.291480825886925</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1983506221032543</v>
+        <v>-0.1630453707928035</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.132355792324915</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.672664330658214</v>
+        <v>-7.584401202382087</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.08169419363838015</v>
+        <v>0.116999444948831</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.132355792324915</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.632480032292023</v>
+        <v>-7.544216904015896</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.09811153687269769</v>
+        <v>0.1334167881831485</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.092171493958724</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.469080161352661</v>
+        <v>-7.380817033076534</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1628383064691996</v>
+        <v>0.1981435577796504</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9287716230193617</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.235598939123062</v>
+        <v>-7.147335810846935</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2641552241988916</v>
+        <v>0.2994604755093424</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6952904007897631</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.085932548115547</v>
+        <v>-6.99766941983942</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3211295702889383</v>
+        <v>0.3564348215993891</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6023869095472272</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.953657074484661</v>
+        <v>-6.865393946208534</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2753005457484474</v>
+        <v>0.3106057970588982</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4701114359163405</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.797918741924919</v>
+        <v>-6.709655613648792</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3404109394599812</v>
+        <v>0.3757161907704321</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.314373103356599</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712954075195599</v>
+        <v>-6.624690946919472</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3873031473753676</v>
+        <v>0.4226083986858185</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2294084366272794</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.818544064968703</v>
+        <v>-6.730280936692576</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2170912218669074</v>
+        <v>0.2523964731773582</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3349984264003837</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.750309480343276</v>
+        <v>-6.662046352067149</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2929293975941647</v>
+        <v>0.3282346489046155</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3165831035278477</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.602369438935677</v>
+        <v>-6.51410631065955</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2354846055187974</v>
+        <v>0.2707898568292482</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.2962621876192902</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.549399916681688</v>
+        <v>-6.461136788405561</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2479584281669145</v>
+        <v>0.2832636794773653</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2432926653653013</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.383611720721397</v>
+        <v>-6.29534859244527</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3073130944559379</v>
+        <v>0.3426183457663887</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2432926653653013</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.350248514242629</v>
+        <v>-6.261985385966502</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3351207314285882</v>
+        <v>0.370425982739039</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2432926653653013</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.241989377120107</v>
+        <v>-6.15372624884398</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3729565067367919</v>
+        <v>0.4082617580472427</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2432926653653013</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.118698242302976</v>
+        <v>-6.030435114026849</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.419771054674221</v>
+        <v>0.4550763059846719</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1200015305481708</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.066001375171685</v>
+        <v>-5.977738246895558</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4485507797640631</v>
+        <v>0.4838560310745139</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.06730466341687963</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.822235933188241</v>
+        <v>-5.733972804912113</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5418376649044916</v>
+        <v>0.5771429162149424</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.06730466341687963</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.732460260811768</v>
+        <v>-5.644197132535641</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5798722477750964</v>
+        <v>0.6151774990855472</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.005705218502569609</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.482609866862694</v>
+        <v>-5.394346738586567</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6725544803384285</v>
+        <v>0.7078597316488793</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.005705218502569609</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.306717774395262</v>
+        <v>-5.218454646119135</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7465104408460497</v>
+        <v>0.7818156921565005</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.005705218502569609</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.135271311372798</v>
+        <v>-5.047008183096671</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8284165321095891</v>
+        <v>0.8637217834200399</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1657412445198935</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055249024263677</v>
+        <v>-4.96698589598755</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8594459245695343</v>
+        <v>0.8947511758799851</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2457635316290145</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991613282029743</v>
+        <v>-4.903350153753616</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8895950225174254</v>
+        <v>0.9249002738278762</v>
       </c>
       <c r="F1923" t="n">
         <v>0.309399273862949</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.897915963813348</v>
+        <v>-4.809652835537221</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9082682085877791</v>
+        <v>0.9435734598982299</v>
       </c>
       <c r="F1924" t="n">
         <v>0.309399273862949</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.908418586878637</v>
+        <v>-4.820155458602509</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9058102359865408</v>
+        <v>0.9411154872969916</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2988966507976601</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.747912890431315</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.9739418284002896</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.730199203553449</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9817058870687758</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.606724932240431</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>1.028093666813977</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.386704134203421</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.117681023039395</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.253836445140143</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.186722281466529</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.133663361775644</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.235937359252631</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-3.998410000445667</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.300126806346061</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.05828482780336</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.26221436680441</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-3.938464596892522</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.325431628402954</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-3.940934303354328</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.232087945140673</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.009304489678338</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.12400173209637</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.121176769304489</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.069689528877801</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.176696845197078</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.184512335212968</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.001222585404609</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.259269271121743</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-3.993298210819694</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.238181049716916</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-3.987020008249845</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.169230644146306</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-3.927167389046122</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.203344078259927</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.840923926019745</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.232787734044339</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.886230745418725</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.206440781729272</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-3.915263850121026</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.195379412881453</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.822453368670167</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.161776297353162</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.866842837999595</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.145893985545992</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-3.983384443104938</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.094353052015578</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.023308537687509</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.083874710013216</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.051088935588862</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.084259752621215</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.169469608319</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8752632035298125</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.278083686762331</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.9519672328716857</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.242674648514188</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9806438742732657</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.204290985956037</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9934167806388949</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.027174655920871</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.060992341498263</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.072266900754417</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.043638835326758</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.892891479515649</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.109175979128679</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-3.937905693036255</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.071977749052027</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.204910203308691</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9708675072819983</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.306107984745863</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.9295923166036306</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.299597018131551</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.9297966648036724</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.280558890424254</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.9339366350948364</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.333074692699074</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>1.032224715819098</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.346941454032992</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>1.027511340271665</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.394721590386775</v>
+        <v>-4.306458462110647</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014407816127078</v>
+        <v>1.049713067437529</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.158715491875644</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>1.006760476808729</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3599140910246011</v>
@@ -46792,10 +46792,10 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.242536713150343</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.976025609830331</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3599140910246011</v>
@@ -46815,10 +46815,10 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.236384007097558</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.9791490406431032</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
@@ -46838,10 +46838,10 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.25319330524806</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.9715057981230126</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
@@ -46861,10 +46861,10 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.190895306471938</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>1.062760551430282</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
@@ -46884,10 +46884,10 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-3.98910510880678</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.9457686322104726</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
@@ -46907,10 +46907,10 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.039991821492975</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.99570417945817</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
@@ -46930,10 +46930,10 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-3.953381078843167</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>1.044976212634136</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
@@ -46953,10 +46953,10 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.013590376848452</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>1.019428474256694</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
@@ -46976,10 +46976,10 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-3.9644037281641</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>1.037594751770363</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
@@ -46999,10 +46999,10 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-3.920030596525532</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>1.055206871861227</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
@@ -47022,10 +47022,10 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-3.942510947384417</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>1.040608525656264</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47045,10 +47045,10 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-3.894855216823361</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>1.066052574908491</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47068,10 +47068,10 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.794337058324606</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.111152211682717</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47091,10 +47091,10 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.778431728892254</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.104269015931531</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47114,10 +47114,10 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.733593327283856</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.126302079185519</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.753091783525864</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.122663636319793</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47160,10 +47160,10 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.708888946439963</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.14622437368199</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47183,10 +47183,10 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.71644861227701</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.141610507816419</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47206,10 +47206,10 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.558157194737738</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.256174840015168</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47229,10 +47229,10 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.350515191103262</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.337672346063211</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47252,10 +47252,10 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.299483098380734</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.353033411390493</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47275,10 +47275,10 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.234258917253528</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.39631048793408</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47298,10 +47298,10 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.196831897182394</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.407242268261814</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47321,10 +47321,10 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.216943553217102</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.400454398179171</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47344,10 +47344,10 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.188530290117219</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.572377474440335</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47367,10 +47367,10 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.113748029092206</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.722403288068157</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47390,10 +47390,10 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.087663944828398</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.724544897787539</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47413,10 +47413,10 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-2.999786031719278</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.757889258614967</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47436,10 +47436,10 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-2.990893570325994</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.779000648899072</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47459,10 +47459,10 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.159369687295872</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.703465249515705</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47482,10 +47482,10 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.713113494666432</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.863237423755342</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47505,10 +47505,10 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.69039239098328</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.862989887725508</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47528,10 +47528,10 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.819594204277322</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.97021528825906</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47551,10 +47551,10 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.845468602751348</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.996943351363096</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47574,10 +47574,10 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.838413912536174</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.996440583438711</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
@@ -47597,10 +47597,10 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.811462688209686</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>2.017227226814048</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.833006916040473</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.192712667826693</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
@@ -47643,10 +47643,10 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.855415033845345</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.175866115607737</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
@@ -47666,10 +47666,10 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-2.883639269422946</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.166630420926334</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
@@ -47689,10 +47689,10 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-2.893080195311476</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.219107768292769</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
@@ -47712,10 +47712,10 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.033616930923246</v>
+        <v>-2.945353802647117</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.165784168593363</v>
+        <v>2.201089419903814</v>
       </c>
       <c r="F2007" t="n">
         <v>1.104017158780167</v>
@@ -47735,10 +47735,10 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.109946908524152</v>
+        <v>-3.021683780248023</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.133363990446775</v>
+        <v>2.168669241757226</v>
       </c>
       <c r="F2008" t="n">
         <v>1.104017158780167</v>
@@ -47758,10 +47758,10 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.203610853201693</v>
+        <v>-3.115347724925564</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.090718642178621</v>
+        <v>2.126023893489072</v>
       </c>
       <c r="F2009" t="n">
         <v>1.010353214102625</v>
@@ -47781,10 +47781,10 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.365179278728948</v>
+        <v>-3.276916150452819</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.024525282177871</v>
+        <v>2.059830533488323</v>
       </c>
       <c r="F2010" t="n">
         <v>0.8835702903047459</v>
@@ -47804,10 +47804,10 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.473479940599068</v>
+        <v>-3.385216812322939</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.994278424295742</v>
+        <v>2.029583675606193</v>
       </c>
       <c r="F2011" t="n">
         <v>0.8835702903047459</v>
@@ -47827,10 +47827,10 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.566627411902434</v>
+        <v>-3.478364283626306</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.949024632557335</v>
+        <v>1.984329883867787</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7607410790222131</v>
@@ -47850,10 +47850,10 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.594528199011907</v>
+        <v>-3.506265070735779</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.936388358840548</v>
+        <v>1.971693610150999</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7261441548792783</v>
@@ -47873,10 +47873,10 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.717054301714801</v>
+        <v>-3.628791173438672</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.88414236173659</v>
+        <v>1.919447613047041</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6036180521763844</v>
@@ -47896,10 +47896,10 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.94756879790039</v>
+        <v>-3.859305669624261</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.858642522852858</v>
+        <v>1.893947774163309</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3731035559907957</v>
@@ -47919,10 +47919,10 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.296313883124833</v>
+        <v>-4.208050754848704</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.859456207764927</v>
+        <v>1.894761459075379</v>
       </c>
       <c r="F2016" t="n">
         <v>0.2643556020718979</v>
@@ -47942,10 +47942,10 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.450300300900974</v>
+        <v>-4.362037172624845</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.866841909800111</v>
+        <v>1.902147161110562</v>
       </c>
       <c r="F2017" t="n">
         <v>0.2643556020718979</v>
@@ -47965,10 +47965,10 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.399778397073308</v>
+        <v>-4.311515268797179</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.873101873451298</v>
+        <v>1.908407124761749</v>
       </c>
       <c r="F2018" t="n">
         <v>0.2643556020718979</v>
@@ -47988,10 +47988,10 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.652253551081032</v>
+        <v>-4.563990422804904</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.783982300903622</v>
+        <v>1.819287552214074</v>
       </c>
       <c r="F2019" t="n">
         <v>0.2643556020718979</v>
@@ -48011,10 +48011,10 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.945149307560444</v>
+        <v>-4.856886179284316</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.668034532830801</v>
+        <v>1.703339784141253</v>
       </c>
       <c r="F2020" t="n">
         <v>0.2643556020718979</v>
@@ -48034,10 +48034,10 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.131813435695253</v>
+        <v>-5.043550307419124</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.597490623804199</v>
+        <v>1.632795875114651</v>
       </c>
       <c r="F2021" t="n">
         <v>0.237616631247338</v>
@@ -48057,10 +48057,10 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.277834122609215</v>
+        <v>-5.189570994333086</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.534160201774804</v>
+        <v>1.569465453085255</v>
       </c>
       <c r="F2022" t="n">
         <v>0.228533539453481</v>
@@ -48080,10 +48080,10 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.369548131718799</v>
+        <v>-5.281285003442671</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.659678654830014</v>
+        <v>1.694983906140465</v>
       </c>
       <c r="F2023" t="n">
         <v>0.228533539453481</v>
@@ -48103,10 +48103,10 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.401199790778769</v>
+        <v>-5.312936662502641</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.641864629169841</v>
+        <v>1.677169880480291</v>
       </c>
       <c r="F2024" t="n">
         <v>0.2233650822090408</v>
@@ -48126,10 +48126,10 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.483134609047652</v>
+        <v>-5.394871480771524</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.619320119430779</v>
+        <v>1.65462537074123</v>
       </c>
       <c r="F2025" t="n">
         <v>0.2134303366219606</v>
@@ -48149,10 +48149,10 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.58511073129606</v>
+        <v>-5.496847603019932</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.587455308987318</v>
+        <v>1.622760560297769</v>
       </c>
       <c r="F2026" t="n">
         <v>0.1114542143735531</v>
@@ -48172,10 +48172,10 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.475104447818838</v>
+        <v>-5.38684131954271</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.623610709622382</v>
+        <v>1.658915960932833</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1346587862908283</v>
@@ -48195,10 +48195,10 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.332044872077912</v>
+        <v>-5.243781743801784</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.685084550640727</v>
+        <v>1.720389801951177</v>
       </c>
       <c r="F2028" t="n">
         <v>0.1426722128808076</v>
@@ -48218,10 +48218,10 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.030598146606074</v>
+        <v>-4.942335018329946</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.812924123711998</v>
+        <v>1.848229375022449</v>
       </c>
       <c r="F2029" t="n">
         <v>0.4441189383526448</v>
@@ -48241,10 +48241,10 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.055188390841258</v>
+        <v>-4.96692526256513</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.804059203770635</v>
+        <v>1.839364455081086</v>
       </c>
       <c r="F2030" t="n">
         <v>0.4441189383526448</v>
@@ -48264,10 +48264,10 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.004150014834738</v>
+        <v>-4.91588688655861</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.825317458552999</v>
+        <v>1.860622709863449</v>
       </c>
       <c r="F2031" t="n">
         <v>0.4441189383526448</v>
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.963010719968107</v>
+        <v>-4.820971400502144</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.860811275373796</v>
+        <v>1.917627003160181</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.5390344244091111</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.137526927606352</v>
+        <v>4.169792642320253</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.866375807949467</v>
+        <v>-4.724336488483504</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.715649236305187</v>
+        <v>1.772464964091572</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.635669336427751</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011691870941471</v>
+        <v>4.043957585655372</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.99695654248031</v>
+        <v>-4.854917223014346</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.666918986566814</v>
+        <v>1.723734714353199</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4513124107070731</v>
+        <v>0.5050886018969085</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936845474296929</v>
+        <v>3.969111189010831</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.832460208289348</v>
+        <v>-4.690420888823384</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.717144339319281</v>
+        <v>1.773960067105666</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6695849360878704</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.019970093887589</v>
+        <v>4.05223580860149</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.85983014097378</v>
+        <v>-4.717790821507816</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.705384076681938</v>
+        <v>1.762199804468323</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6695849360878704</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019157804324019</v>
+        <v>4.05142351903792</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.870215335863669</v>
+        <v>-4.728176016397706</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.711098777851055</v>
+        <v>1.76791450563744</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6054235500081456</v>
+        <v>0.6591997411979811</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.022795466515158</v>
+        <v>4.055061181229059</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.888803494585894</v>
+        <v>-4.746764175119931</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.77450052013859</v>
+        <v>1.831316247924975</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5868353912859203</v>
+        <v>0.6406115824757557</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.082479577058248</v>
+        <v>4.114745291772149</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.88910204128193</v>
+        <v>-4.747062721815967</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.771250112278474</v>
+        <v>1.828065840064859</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5865368445898844</v>
+        <v>0.6403130357797198</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079169459858925</v>
+        <v>4.111435174572826</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.788278907591502</v>
+        <v>-4.646239588125539</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.816110260694037</v>
+        <v>1.872925988480422</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5990010600742383</v>
+        <v>0.6527772512640736</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091178884088928</v>
+        <v>4.12344459880283</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.597497546839096</v>
+        <v>-4.455458227373131</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.892552058473543</v>
+        <v>1.949367786259928</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7897824208266456</v>
+        <v>0.843558612016481</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.205776954018916</v>
+        <v>4.238042668732817</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.490534188989674</v>
+        <v>-4.34849486952371</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.915174247350908</v>
+        <v>1.971989975137293</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8482470287864471</v>
+        <v>0.9020232199762824</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.220692564532393</v>
+        <v>4.252958279246294</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.435203601087911</v>
+        <v>-4.293164281621947</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.972273419123671</v>
+        <v>2.029089146910056</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>0.9573538078780446</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.32112356859941</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.423149474174949</v>
+        <v>-4.281110154708984</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.970781637790294</v>
+        <v>2.027597365576679</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>0.9694079347910074</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.322042612648626</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.46430459374317</v>
+        <v>-4.322265274277205</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.956200220147141</v>
+        <v>2.013015947933527</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>0.9282528152227865</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.299230171091828</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.39625603105164</v>
+        <v>-4.254216711585675</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.996270671101636</v>
+        <v>2.053086398888022</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9963013779143162</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320644619870728</v>
+        <v>4.352910334584629</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.62785642422114</v>
+        <v>-4.485817104755176</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.92383318400743</v>
+        <v>1.980648911793815</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9963013779143162</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340847290044322</v>
+        <v>4.373113004758223</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.645928932512752</v>
+        <v>-4.503889613046788</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.916604180690785</v>
+        <v>1.973419908477171</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9963013779143162</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.340847290044322</v>
+        <v>4.373113004758223</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.821035765089198</v>
+        <v>-4.678996445623233</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.806813361253674</v>
+        <v>1.863629089040059</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9963013779143162</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.301099203637789</v>
+        <v>4.33336491835169</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.789749744548742</v>
+        <v>-4.647710425082778</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.826350388466796</v>
+        <v>1.883166116253181</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9738112072649363</v>
+        <v>1.027587398454771</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.326893434959002</v>
+        <v>4.359159149672903</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.636724352435458</v>
+        <v>-4.494685032969493</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.986731544885014</v>
+        <v>2.043547272671399</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.12683659937822</v>
+        <v>1.180612790568055</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.517879669799877</v>
+        <v>4.550145384513778</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.665031666308728</v>
+        <v>-4.522992346842764</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.162874844243998</v>
+        <v>2.219690572030383</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.12683659937822</v>
+        <v>1.180612790568055</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.705345894708169</v>
+        <v>4.73761160942207</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.83162489142225</v>
+        <v>-4.689585571956286</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.065640505552671</v>
+        <v>2.122456233339057</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9602433742646979</v>
+        <v>1.014019565454533</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.574792910994137</v>
+        <v>4.607058625708039</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.808589098060684</v>
+        <v>-4.66654977859472</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.078531225559016</v>
+        <v>2.135346953345401</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9602433742646979</v>
+        <v>1.014019565454533</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.578469313655855</v>
+        <v>4.610735028369756</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.779343117604988</v>
+        <v>-4.637303798139023</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.08784767286479</v>
+        <v>2.144663400651175</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9602433742646979</v>
+        <v>1.014019565454533</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.57608736877935</v>
+        <v>4.608353083493252</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.886268665482839</v>
+        <v>-4.744229346016875</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.042370692871284</v>
+        <v>2.099186420657669</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8533178263868465</v>
+        <v>0.9070940175766816</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.509225279210275</v>
+        <v>4.541490993924176</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.031287223990088</v>
+        <v>-4.889247904524123</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.985792071611619</v>
+        <v>2.042607799398004</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.708299267879598</v>
+        <v>0.7620754590694331</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.42364294624916</v>
+        <v>4.455908660963061</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.149628989774805</v>
+        <v>-5.007589670308841</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.038386604555485</v>
+        <v>2.09520233234187</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7727614976323232</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.529985808644647</v>
+        <v>4.562251523358548</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.201039412095513</v>
+        <v>-5.059000092629549</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.01560813275314</v>
+        <v>2.072423860539526</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7727614976323232</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.527771505770586</v>
+        <v>4.560037220484487</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.280458863303265</v>
+        <v>-5.1384195438373</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.983743480344329</v>
+        <v>2.040559208130714</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7727614976323232</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.527674633844875</v>
+        <v>4.559940348558777</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.375921861220482</v>
+        <v>-5.233882541754518</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.945552174735485</v>
+        <v>2.002367902521871</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7727614976323232</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.527668527402919</v>
+        <v>4.55993424211682</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.415941859264266</v>
+        <v>-5.273902539798302</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.927640572080583</v>
+        <v>1.984456299866968</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.7327414995885393</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.501752925139259</v>
+        <v>4.53401863985316</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.47131102139646</v>
+        <v>-5.329271701930495</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.911226724975432</v>
+        <v>1.968042452761817</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.7327414995885393</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.507486742886986</v>
+        <v>4.539752457600887</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.516748801227287</v>
+        <v>-5.374709481761323</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.892589976386034</v>
+        <v>1.949405704172419</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6898965089103797</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.481318111823023</v>
+        <v>4.513583826536924</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.428541967079709</v>
+        <v>-5.286502647613744</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.947747102895384</v>
+        <v>2.00456283068177</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6898965089103797</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.501192504673342</v>
+        <v>4.533458219387243</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.252251742474401</v>
+        <v>-5.110212423008437</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.001963893262235</v>
+        <v>2.05877962104862</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6898965089103797</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.48489320519807</v>
+        <v>4.517158919911971</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.069040079341306</v>
+        <v>-4.927000759875342</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.077679507979519</v>
+        <v>2.134495235765904</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6898965089103797</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.487324154662115</v>
+        <v>4.519589869376016</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.997318632327455</v>
+        <v>-4.855279312861491</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.072159272632948</v>
+        <v>2.128975000419334</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7078417647343952</v>
+        <v>0.7616179559242303</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.496148208718315</v>
+        <v>4.528413923432216</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.974945606719749</v>
+        <v>-4.832906287253785</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.028024228797203</v>
+        <v>2.084839956583588</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7190975158472968</v>
+        <v>0.7728737070371319</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.449817405307228</v>
+        <v>4.482083120021128</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.007961902630494</v>
+        <v>-4.865922583164529</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.20001591531826</v>
+        <v>2.256831643104646</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6496601391805452</v>
+        <v>0.7034363303703803</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.593353184192532</v>
+        <v>4.625618898906433</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.996434266980885</v>
+        <v>-4.854394947514921</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.196548195406352</v>
+        <v>2.253363923192738</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7086607973819077</v>
+        <v>0.7624369885717428</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.620674804941599</v>
+        <v>4.6529405196555</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.093775768323254</v>
+        <v>-4.951736448857289</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.161279707391194</v>
+        <v>2.218095435177579</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6642406152164193</v>
+        <v>0.7180168064062544</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.597690808164095</v>
+        <v>4.629956522877995</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.17963179766322</v>
+        <v>-5.037592478197256</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.128188377848045</v>
+        <v>2.185004105634431</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6218645459902843</v>
+        <v>0.6756407371801194</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.573516248821251</v>
+        <v>4.605781963535152</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.162822873263949</v>
+        <v>-5.020783553797985</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.117331149428256</v>
+        <v>2.174146877214641</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6459306416786644</v>
+        <v>0.6997068328684996</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.570375108054781</v>
+        <v>4.602640822768683</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.85167003146926</v>
+        <v>3.867914706056215</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.254205435829408</v>
+        <v>-5.161451916258785</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.090942635447122</v>
+        <v>2.12804404327537</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5545480791132062</v>
+        <v>0.5590384704076995</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.525710081560556</v>
+        <v>4.528404316337252</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>117.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-677.7%</t>
+          <t>-677.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.4%</t>
+          <t>-163.2%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.4%</t>
+          <t>758.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-306.9%</t>
+          <t>-313.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.1%</t>
+          <t>-159.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2075"/>
+  <dimension ref="A1:G2076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.67740134386217</v>
+        <v>-8.765664472138297</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3045214529931823</v>
+        <v>-0.3398267043036332</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.488355021484225</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.57949430518568</v>
+        <v>-8.667757433461807</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2656589524960467</v>
+        <v>-0.3009642038064975</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.420369271623669</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.555540764209722</v>
+        <v>-8.643803892485849</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2554090299601701</v>
+        <v>-0.2907142812706209</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.396415730647711</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.291480825886925</v>
+        <v>-8.379743954163052</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1630453707928035</v>
+        <v>-0.1983506221032543</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.132355792324915</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.584401202382087</v>
+        <v>-7.672664330658214</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.116999444948831</v>
+        <v>0.08169419363838015</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.132355792324915</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.544216904015896</v>
+        <v>-7.632480032292023</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1334167881831485</v>
+        <v>0.09811153687269769</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.092171493958724</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.380817033076534</v>
+        <v>-7.469080161352661</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1981435577796504</v>
+        <v>0.1628383064691996</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9287716230193617</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.147335810846935</v>
+        <v>-7.235598939123062</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2994604755093424</v>
+        <v>0.2641552241988916</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6952904007897631</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.99766941983942</v>
+        <v>-7.085932548115547</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3564348215993891</v>
+        <v>0.3211295702889383</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6023869095472272</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.865393946208534</v>
+        <v>-6.953657074484661</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3106057970588982</v>
+        <v>0.2753005457484474</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4701114359163405</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.709655613648792</v>
+        <v>-6.797918741924919</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3757161907704321</v>
+        <v>0.3404109394599812</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.314373103356599</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.624690946919472</v>
+        <v>-6.712954075195599</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4226083986858185</v>
+        <v>0.3873031473753676</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2294084366272794</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.730280936692576</v>
+        <v>-6.818544064968703</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2523964731773582</v>
+        <v>0.2170912218669074</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3349984264003837</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987898</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.662046352067149</v>
+        <v>-6.750309480343276</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3282346489046155</v>
+        <v>0.2929293975941647</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3165831035278477</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.51410631065955</v>
+        <v>-6.602369438935677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2707898568292482</v>
+        <v>0.2354846055187974</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.2962621876192902</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.461136788405561</v>
+        <v>-6.549399916681688</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2832636794773653</v>
+        <v>0.2479584281669145</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2432926653653013</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.29534859244527</v>
+        <v>-6.383611720721397</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3426183457663887</v>
+        <v>0.3073130944559379</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2432926653653013</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.261985385966502</v>
+        <v>-6.350248514242629</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.370425982739039</v>
+        <v>0.3351207314285882</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2432926653653013</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.15372624884398</v>
+        <v>-6.241989377120107</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4082617580472427</v>
+        <v>0.3729565067367919</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2432926653653013</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.030435114026849</v>
+        <v>-6.118698242302976</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4550763059846719</v>
+        <v>0.419771054674221</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1200015305481708</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.977738246895558</v>
+        <v>-6.066001375171685</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4838560310745139</v>
+        <v>0.4485507797640631</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.06730466341687963</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.733972804912113</v>
+        <v>-5.822235933188241</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5771429162149424</v>
+        <v>0.5418376649044916</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.06730466341687963</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.644197132535641</v>
+        <v>-5.732460260811768</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6151774990855472</v>
+        <v>0.5798722477750964</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.005705218502569609</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.394346738586567</v>
+        <v>-5.482609866862694</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7078597316488793</v>
+        <v>0.6725544803384285</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.005705218502569609</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.218454646119135</v>
+        <v>-5.306717774395262</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7818156921565005</v>
+        <v>0.7465104408460497</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.005705218502569609</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.047008183096671</v>
+        <v>-5.135271311372798</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8637217834200399</v>
+        <v>0.8284165321095891</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1657412445198935</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.96698589598755</v>
+        <v>-5.055249024263677</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8947511758799851</v>
+        <v>0.8594459245695343</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2457635316290145</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.903350153753616</v>
+        <v>-4.991613282029743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9249002738278762</v>
+        <v>0.8895950225174254</v>
       </c>
       <c r="F1923" t="n">
         <v>0.309399273862949</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.809652835537221</v>
+        <v>-4.897915963813348</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9435734598982299</v>
+        <v>0.9082682085877791</v>
       </c>
       <c r="F1924" t="n">
         <v>0.309399273862949</v>
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.820155458602509</v>
+        <v>-4.817959084029066</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9411154872969916</v>
+        <v>0.9419940371263693</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.3893561536472314</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.048872085530339</v>
+        <v>3.103147787240082</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.747912890431315</v>
+        <v>-4.738349647868667</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9739418284002896</v>
+        <v>0.977767125425349</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.3893561536472314</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.052801399365159</v>
+        <v>3.107077101074902</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.730199203553449</v>
+        <v>-4.720635960990801</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9817058870687758</v>
+        <v>0.9855311840938352</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.3925374825441482</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055388780620649</v>
+        <v>3.109664482330392</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.606724932240431</v>
+        <v>-4.597161689677783</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.028093666813977</v>
+        <v>1.031918963839036</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.3925374825441482</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052386851840643</v>
+        <v>3.106662553550386</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.386704134203421</v>
+        <v>-4.377140891640773</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.117681023039395</v>
+        <v>1.121506320064454</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.5337573276121284</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.192973497601788</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.253836445140143</v>
+        <v>-4.244273202577495</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.186722281466529</v>
+        <v>1.190547578491589</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.5337573276121284</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.208867680403611</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.133663361775644</v>
+        <v>-4.124100119212996</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.235937359252631</v>
+        <v>1.23976265627769</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.6539304109766273</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.282117374862612</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.998410000445667</v>
+        <v>-3.988846757883019</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.300126806346061</v>
+        <v>1.303952103371121</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.7891837723066044</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.373357494222038</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.05828482780336</v>
+        <v>-4.048721585240711</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26221436680441</v>
+        <v>1.26603966382947</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.7293089449489123</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.323470089208849</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.76264747767451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.938464596892522</v>
+        <v>-3.928901354329874</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.325431628402954</v>
+        <v>1.329256925428013</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.7293089449489123</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.338759258443058</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.940934303354328</v>
+        <v>-3.93137106079168</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.232087945140673</v>
+        <v>1.235913242165732</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.7268392384871061</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.244921633888415</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.009304489678338</v>
+        <v>-3.99974124711569</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.12400173209637</v>
+        <v>1.12782702912143</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.736114937523321</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.169748914795446</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.121176769304489</v>
+        <v>-4.111613526741841</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.069689528877801</v>
+        <v>1.073514825902861</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.736114937523321</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.160185623427337</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.176696845197078</v>
+        <v>-4.16713360263443</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.184512335212968</v>
+        <v>1.188337632238027</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.736114937523321</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.29721646011954</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.001222585404609</v>
+        <v>-3.991659342841961</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.259269271121743</v>
+        <v>1.263094568146803</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.736114937523321</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.301783692111327</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.993298210819694</v>
+        <v>-3.983734968257047</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.238181049716916</v>
+        <v>1.242006346741976</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.736114937523321</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.277525720872534</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.987020008249845</v>
+        <v>-3.977456765687198</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.169230644146306</v>
+        <v>1.173055941171365</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.74239314009317</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.209830955815893</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.927167389046122</v>
+        <v>-3.917604146483475</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.203344078259927</v>
+        <v>1.207169375284987</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.74239314009317</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.220003342248026</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.840923926019745</v>
+        <v>-3.831360683457097</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.232787734044339</v>
+        <v>1.236613031069398</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.74239314009317</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.214949612821886</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.886230745418725</v>
+        <v>-3.876667502856077</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.206440781729272</v>
+        <v>1.210266078754331</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.7015829770839392</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.182239290460873</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.915263850121026</v>
+        <v>-3.905700607558379</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.195379412881453</v>
+        <v>1.199204709906512</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.7015829770839392</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.182791163493975</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.822453368670167</v>
+        <v>-3.812890126107519</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.161776297353162</v>
+        <v>1.165601594378222</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.7943934585347986</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.167750144255856</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.866842837999595</v>
+        <v>-3.857279595436947</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.145893985545992</v>
+        <v>1.149719282571051</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.7500039892053709</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.1429899385828</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.983384443104938</v>
+        <v>-3.97382120054229</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.094353052015578</v>
+        <v>1.098178349040637</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.6334623841000282</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>3.068140684031317</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.023308537687509</v>
+        <v>-4.013745295124862</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.083874710013216</v>
+        <v>1.087700007038276</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.6334623841000282</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>3.073631979861985</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.051088935588862</v>
+        <v>-4.041525693026214</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.084259752621215</v>
+        <v>1.088085049646274</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.6056819861986751</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>3.068460942889712</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.169469608319</v>
+        <v>-4.159906365756353</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8752632035298125</v>
+        <v>0.8790885005548716</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.5384641340476989</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.86648595159978</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.278083686762331</v>
+        <v>-4.268520444199684</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9519672328716857</v>
+        <v>0.9557925298967449</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.5384641340476989</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.986635612318985</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.242674648514188</v>
+        <v>-4.233111405951541</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9806438742732657</v>
+        <v>0.9844691712983251</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.5384641340476989</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>3.001148638421308</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.204290985956037</v>
+        <v>-4.19472774339339</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9934167806388949</v>
+        <v>0.9972420776639541</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.5768477966058501</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>3.021598277298568</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.027174655920871</v>
+        <v>-4.017611413358224</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.060992341498263</v>
+        <v>1.064817638523323</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.5768477966058501</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>3.01832730614387</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.072266900754417</v>
+        <v>-4.062703658191769</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.043638835326758</v>
+        <v>1.047464132351817</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.5149517534364603</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.981873072004149</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.892891479515649</v>
+        <v>-3.883328236953002</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.109175979128679</v>
+        <v>1.113001276153739</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.6717285116071789</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>3.069726102212994</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.937905693036255</v>
+        <v>-3.928342450473608</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.071977749052027</v>
+        <v>1.075803046077086</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.6413796162925743</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>3.032324220355821</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.204910203308691</v>
+        <v>-4.195346960746043</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9708675072819983</v>
+        <v>0.9746928043070575</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.4470165782496258</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.921397959868998</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.306107984745863</v>
+        <v>-4.296544742183216</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9295923166036306</v>
+        <v>0.93341761362869</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.3786077647043066</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.879556593638308</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.299597018131551</v>
+        <v>-4.290033775568904</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9297966648036724</v>
+        <v>0.9336219618287318</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.3786077647043066</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.877156555192625</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.280558890424254</v>
+        <v>-4.270995647861606</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9339366350948364</v>
+        <v>0.9377619321198956</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.320424153373112</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.838771107602153</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.333074692699074</v>
+        <v>-4.323511450136427</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.032224715819098</v>
+        <v>1.036050012844158</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.320424153373112</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.958065509236343</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.346941454032992</v>
+        <v>-4.337378211470345</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.027511340271665</v>
+        <v>1.031336637296724</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.2825662366392891</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.936184088182183</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.306458462110647</v>
+        <v>-4.296895219547999</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.049713067437529</v>
+        <v>1.053538364462588</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.2825662366392891</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.942192618579109</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.158715491875644</v>
+        <v>-4.149152249312997</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.006760476808729</v>
+        <v>1.010585773833789</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.4503735938741723</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.940827254197238</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181163</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.242536713150343</v>
+        <v>-4.232973470587695</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.976025609830331</v>
+        <v>0.9798509068553902</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.4503735938741723</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.943620875728719</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.236384007097558</v>
+        <v>-4.226820764534911</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9791490406431032</v>
+        <v>0.9829743376681623</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.4565262999269565</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.947974847752048</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890606</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.25319330524806</v>
+        <v>-4.243630062685413</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9715057981230126</v>
+        <v>0.9753310951480718</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.4397170017764549</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.936969745601858</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798419</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.190895306471938</v>
+        <v>-4.181332063909291</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.062760551430282</v>
+        <v>1.066585848455342</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.4850112660508969</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>3.030481857963343</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.98910510880678</v>
+        <v>-3.979541866244133</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9457686322104726</v>
+        <v>0.9495939292355318</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.6830294582200513</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.951584774978963</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852419</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.039991821492975</v>
+        <v>-4.030428578930327</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.99570417945817</v>
+        <v>0.9995294764832292</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.6321427455338569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.991342979689422</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319537</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.953381078843167</v>
+        <v>-3.94381783628052</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.044976212634136</v>
+        <v>1.048801509659196</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.7107684767390151</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>3.053146154528561</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489378</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.013590376848452</v>
+        <v>-4.004027134285804</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.019428474256694</v>
+        <v>1.023253771281754</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.6505591787337306</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>3.015556556550061</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397787</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.9644037281641</v>
+        <v>-3.954840485601453</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.037594751770363</v>
+        <v>1.041420048795423</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.6505591787337306</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>3.01404817458999</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316242</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.920030596525532</v>
+        <v>-3.910467353962884</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.055206871861227</v>
+        <v>1.059032168886286</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.6949323103722992</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>3.040534921008567</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.942510947384417</v>
+        <v>-3.932947704821769</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.040608525656264</v>
+        <v>1.044433822681323</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.6949323103722992</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>3.034928715147158</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190319</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.894855216823361</v>
+        <v>-3.885291974260713</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.066052574908491</v>
+        <v>1.06987787193355</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.7425880409333548</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>3.069903910511596</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569611</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.794337058324606</v>
+        <v>-3.784773815761959</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.111152211682717</v>
+        <v>1.114977508707777</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.8431061994321094</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.135107178985574</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.778431728892254</v>
+        <v>-3.768868486329606</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.104269015931531</v>
+        <v>1.10809431295659</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.7639935387228705</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>3.074394255035902</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932763</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.733593327283856</v>
+        <v>-3.724030084721208</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.126302079185519</v>
+        <v>1.130127376210578</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.7685369716677399</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>3.081218017413453</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917045</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.753091783525864</v>
+        <v>-3.743528540963216</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.122663636319793</v>
+        <v>1.126488933344852</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.7204523303878356</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>3.056528172276588</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405953</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.708888946439963</v>
+        <v>-3.699325703877316</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.14622437368199</v>
+        <v>1.15004967070705</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.7646551674737361</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.088929477055965</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265637</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.71644861227701</v>
+        <v>-3.706885369714363</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.141610507816419</v>
+        <v>1.145435804841479</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.8194585714835554</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.120221519931104</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284872</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.558157194737738</v>
+        <v>-3.548593952175091</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.256174840015168</v>
+        <v>1.260000137040227</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.8194585714835554</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.171469285114144</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321016</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.350515191103262</v>
+        <v>-3.340951948540615</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.337672346063211</v>
+        <v>1.341497643088271</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>1.027100575118032</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.294495191889083</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475132</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.299483098380734</v>
+        <v>-3.289919855818086</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.353033411390493</v>
+        <v>1.356858708415552</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>1.078132667840559</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.32006267576087</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404846</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.234258917253528</v>
+        <v>-3.224695674690881</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.39631048793408</v>
+        <v>1.400135784959139</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.143356848967765</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.376384588529898</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.196831897182394</v>
+        <v>-3.187268654619747</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.407242268261814</v>
+        <v>1.411067565286873</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.148608386996947</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.375496483646687</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.216943553217102</v>
+        <v>-3.207380310654455</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.400454398179171</v>
+        <v>1.40427969520423</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.159635731994366</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.383369682976379</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.188530290117219</v>
+        <v>-3.178967047554571</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.572377474440335</v>
+        <v>1.576202771465394</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>1.100660169247937</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.508542116349733</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.113748029092206</v>
+        <v>-3.104184786529559</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.722403288068157</v>
+        <v>1.726228585093216</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.17544243027295</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.673524382182558</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998749</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.087663944828398</v>
+        <v>-3.078100702265751</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.724544897787539</v>
+        <v>1.728370194812599</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.17544243027295</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.665232358196417</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896923</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.999786031719278</v>
+        <v>-2.99022278915663</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.757889258614967</v>
+        <v>1.761714555640026</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.291368072696301</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.732980939234206</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.990893570325994</v>
+        <v>-2.981330327763347</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.779000648899072</v>
+        <v>1.782825945924131</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.291368072696301</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.750535344960998</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.159369687295872</v>
+        <v>-3.149806444733225</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.703465249515705</v>
+        <v>1.707290546540764</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.26342023697972</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.725621690935633</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782702</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.713113494666432</v>
+        <v>-2.703550252103785</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.863237423755342</v>
+        <v>1.867062720780402</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.168701567310087</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.650060186321716</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.69039239098328</v>
+        <v>-2.680829148420632</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.862989887725508</v>
+        <v>1.866815184750567</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.168701567310087</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.64072420881862</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.819594204277322</v>
+        <v>-2.810030961714675</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.97021528825906</v>
+        <v>1.974040585284119</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>1.039499754016045</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.722109246693364</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.845468602751348</v>
+        <v>-2.835905360188701</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.996943351363096</v>
+        <v>2.000768648388155</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>1.084411362727786</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.786134034414055</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.838413912536174</v>
+        <v>-2.828850669973527</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.996440583438711</v>
+        <v>2.00026588046377</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>1.09146605294296</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.787042204532705</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.811462688209686</v>
+        <v>-2.801899445647039</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.017227226814048</v>
+        <v>2.021052523839107</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.106346398970679</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.805976565794078</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784102</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.833006916040473</v>
+        <v>-2.823443673477826</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.192712667826693</v>
+        <v>2.196537964851752</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.106346398970679</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.990079697939037</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.855415033845345</v>
+        <v>-2.845851791282698</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.175866115607737</v>
+        <v>2.179691412632796</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.106346398970679</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.98219639284203</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.883639269422946</v>
+        <v>-2.874076026860299</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.166630420926334</v>
+        <v>2.170455717951393</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.124323151421988</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.995036443862453</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.893080195311476</v>
+        <v>-2.883516952748828</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.219107768292769</v>
+        <v>2.222933065317829</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.246750268965379</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.124746432110335</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.945353802647117</v>
+        <v>-2.93579056008447</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.201089419903814</v>
+        <v>2.204914716928873</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.194476661629738</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>4.096273362254252</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.021683780248023</v>
+        <v>-3.012120537685376</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.168669241757226</v>
+        <v>2.172494538782286</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.194476661629738</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>4.094385175148027</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.115347724925564</v>
+        <v>-3.105784482362917</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.126023893489072</v>
+        <v>2.129849190514132</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.010353214102625</v>
+        <v>1.100812716952197</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.978731336234621</v>
+        <v>4.033007037944364</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.276916150452819</v>
+        <v>-3.267352907890172</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.059830533488323</v>
+        <v>2.063655830513382</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.9740297931543173</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.901095592166046</v>
+        <v>3.955371293875789</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.385216812322939</v>
+        <v>-3.375653569760292</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.029583675606193</v>
+        <v>2.033408972631253</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.9740297931543173</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.914168999031965</v>
+        <v>3.968444700741707</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.478364283626306</v>
+        <v>-3.468801041063658</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.984329883867787</v>
+        <v>1.988155180892846</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.8512005818717845</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.832476669045385</v>
+        <v>3.886752370755127</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.506265070735779</v>
+        <v>-3.496701828173131</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.971693610150999</v>
+        <v>1.975518907176059</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.8166036577288497</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810242555686626</v>
+        <v>3.864518257396369</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.628791173438672</v>
+        <v>-3.619227930876025</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.919447613047041</v>
+        <v>1.9232729100721</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.6940775550259558</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733491338042088</v>
+        <v>3.787767039751831</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.859305669624261</v>
+        <v>-3.849742427061614</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.893947774163309</v>
+        <v>1.897773071188368</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.4635630588403671</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.661888599921239</v>
+        <v>3.716164301630982</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.208050754848704</v>
+        <v>-4.198487512286057</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.894761459075379</v>
+        <v>1.898586756100438</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.3548151049214693</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.736951546571747</v>
+        <v>3.79122724828149</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.362037172624845</v>
+        <v>-4.352473930062198</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.902147161110562</v>
+        <v>1.905972458135621</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.3548151049214693</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.805931815717387</v>
+        <v>3.86020751742713</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.311515268797179</v>
+        <v>-4.301952026234532</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.908407124761749</v>
+        <v>1.912232421786809</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.3548151049214693</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.791983017837508</v>
+        <v>3.84625871954725</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.563990422804904</v>
+        <v>-4.554427180242256</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.819287552214074</v>
+        <v>1.823112849239133</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.3548151049214693</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.803853506892922</v>
+        <v>3.858129208602664</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.856886179284316</v>
+        <v>-4.847322936721668</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.703339784141253</v>
+        <v>1.707165081166312</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.3548151049214693</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.805064041411865</v>
+        <v>3.859339743121608</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251941</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.043550307419124</v>
+        <v>-5.033987064856476</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.632795875114651</v>
+        <v>1.63662117213971</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.3280761340969094</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793142401144451</v>
+        <v>3.847418102854194</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.189570994333086</v>
+        <v>-5.180007751770439</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.569465453085255</v>
+        <v>1.573290750110314</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.3189930423030524</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.782770398804326</v>
+        <v>3.837046100514069</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.281285003442671</v>
+        <v>-5.271721760880023</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.694983906140465</v>
+        <v>1.698809203165525</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.3189930423030524</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94497445550337</v>
+        <v>3.999250157213113</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.312936662502641</v>
+        <v>-5.303373419939993</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.677169880480291</v>
+        <v>1.680995177505351</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.3138245850586122</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93672001912052</v>
+        <v>3.990995720830263</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.394871480771524</v>
+        <v>-5.385308238208876</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.65462537074123</v>
+        <v>1.658450667766289</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.303889839471532</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940988589336763</v>
+        <v>3.995264291046507</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.496847603019932</v>
+        <v>-5.487284360457283</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.622760560297769</v>
+        <v>1.626585857322829</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>0.2019137172231245</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888728554443621</v>
+        <v>3.943004256153364</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.38684131954271</v>
+        <v>-5.377278076980062</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.658915960932833</v>
+        <v>1.662741257957892</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.2251182891403997</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.894804184838162</v>
+        <v>3.949079886547905</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.243781743801784</v>
+        <v>-5.234218501239136</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.720389801951177</v>
+        <v>1.724215098976237</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.2331317157303789</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903862251514123</v>
+        <v>3.958137953223867</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.942335018329946</v>
+        <v>-4.932771775767298</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.848229375022449</v>
+        <v>1.852054672047508</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.5345784412022162</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.091991169679762</v>
+        <v>4.146266871389505</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679619</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.96692526256513</v>
+        <v>-4.957362020002482</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.839364455081086</v>
+        <v>1.843189752106145</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.5345784412022162</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.092962347432472</v>
+        <v>4.147238049142215</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.91588688655861</v>
+        <v>-4.906323643995962</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.860622709863449</v>
+        <v>1.864448006888509</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.5345784412022162</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093805251812228</v>
+        <v>4.148080953521971</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969536</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.820971400502144</v>
+        <v>-4.865184349129331</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.917627003160181</v>
+        <v>1.899941823709307</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5390344244091111</v>
+        <v>0.575717736068847</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.169792642320253</v>
+        <v>4.191802629316095</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.724336488483504</v>
+        <v>-4.768549437110691</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.772464964091572</v>
+        <v>1.754779784640697</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.635669336427751</v>
+        <v>0.672352648087487</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.043957585655372</v>
+        <v>4.065967572651213</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.854917223014346</v>
+        <v>-4.899130171641533</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.723734714353199</v>
+        <v>1.706049534902324</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5050886018969085</v>
+        <v>0.5417719135566444</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.969111189010831</v>
+        <v>3.991121176006672</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.690420888823384</v>
+        <v>-4.734633837450572</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.773960067105666</v>
+        <v>1.756274887654792</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6695849360878704</v>
+        <v>0.7062682477476063</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.05223580860149</v>
+        <v>4.074245795597331</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077622</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.717790821507816</v>
+        <v>-4.762003770135004</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.762199804468323</v>
+        <v>1.744514625017449</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6695849360878704</v>
+        <v>0.7062682477476063</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.05142351903792</v>
+        <v>4.073433506033761</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.728176016397706</v>
+        <v>-4.772388965024893</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.76791450563744</v>
+        <v>1.750229326186565</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6591997411979811</v>
+        <v>0.695883052857717</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.055061181229059</v>
+        <v>4.0770711682249</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.746764175119931</v>
+        <v>-4.790977123747118</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.831316247924975</v>
+        <v>1.8136310684741</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6406115824757557</v>
+        <v>0.6772948941354917</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.114745291772149</v>
+        <v>4.13675527876799</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.747062721815967</v>
+        <v>-4.791275670443154</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.828065840064859</v>
+        <v>1.810380660613985</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6403130357797198</v>
+        <v>0.6769963474394558</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.111435174572826</v>
+        <v>4.133445161568667</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.646239588125539</v>
+        <v>-4.690452536752726</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.872925988480422</v>
+        <v>1.855240809029547</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6527772512640736</v>
+        <v>0.6894605629238096</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.12344459880283</v>
+        <v>4.145454585798671</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.455458227373131</v>
+        <v>-4.499671176000319</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.949367786259928</v>
+        <v>1.931682606809053</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.843558612016481</v>
+        <v>0.880241923676217</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.238042668732817</v>
+        <v>4.260052655728659</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.34849486952371</v>
+        <v>-4.392707818150898</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.971989975137293</v>
+        <v>1.954304795686419</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9020232199762824</v>
+        <v>0.9387065316360185</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.252958279246294</v>
+        <v>4.274968266242136</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.293164281621947</v>
+        <v>-4.337377230249135</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.029089146910056</v>
+        <v>2.011403967459182</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9573538078780446</v>
+        <v>0.9940371195377806</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.32112356859941</v>
+        <v>4.343133555595251</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.281110154708984</v>
+        <v>-4.325323103336173</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.027597365576679</v>
+        <v>2.009912186125804</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9694079347910074</v>
+        <v>1.006091246450743</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.322042612648626</v>
+        <v>4.344052599644467</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.322265274277205</v>
+        <v>-4.366478222904393</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.013015947933527</v>
+        <v>1.995330768482652</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9282528152227865</v>
+        <v>0.9649361268825225</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.299230171091828</v>
+        <v>4.32124015808767</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.254216711585675</v>
+        <v>-4.298429660212864</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.053086398888022</v>
+        <v>2.035401219437146</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9963013779143162</v>
+        <v>1.032984689574052</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.352910334584629</v>
+        <v>4.374920321580471</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.485817104755176</v>
+        <v>-4.530030053382364</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.980648911793815</v>
+        <v>1.96296373234294</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9963013779143162</v>
+        <v>1.032984689574052</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.373113004758223</v>
+        <v>4.395122991754065</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.503889613046788</v>
+        <v>-4.548102561673976</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.973419908477171</v>
+        <v>1.955734729026296</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9963013779143162</v>
+        <v>1.032984689574052</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.373113004758223</v>
+        <v>4.395122991754065</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082828</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.678996445623233</v>
+        <v>-4.723209394250421</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.863629089040059</v>
+        <v>1.845943909589184</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9963013779143162</v>
+        <v>1.032984689574052</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.33336491835169</v>
+        <v>4.355374905347531</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.74559333394358</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.647710425082778</v>
+        <v>-4.691923373709966</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.883166116253181</v>
+        <v>1.865480936802306</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.027587398454771</v>
+        <v>1.064270710114508</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.359159149672903</v>
+        <v>4.381169136668745</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677823</v>
+        <v>3.730590658677817</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.494685032969493</v>
+        <v>-4.538897981596682</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.043547272671399</v>
+        <v>2.025862093220525</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.180612790568055</v>
+        <v>1.217296102227792</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.550145384513778</v>
+        <v>4.57215537150962</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073882</v>
+        <v>3.741298518073877</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.522992346842764</v>
+        <v>-4.567205295469952</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.219690572030383</v>
+        <v>2.202005392579508</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.180612790568055</v>
+        <v>1.217296102227792</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.73761160942207</v>
+        <v>4.759621596417912</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.689585571956286</v>
+        <v>-4.733798520583474</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.122456233339057</v>
+        <v>2.104771053888182</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.014019565454533</v>
+        <v>1.050702877114269</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.607058625708039</v>
+        <v>4.629068612703881</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568376</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.66654977859472</v>
+        <v>-4.710762727221908</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.135346953345401</v>
+        <v>2.117661773894526</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.014019565454533</v>
+        <v>1.050702877114269</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.610735028369756</v>
+        <v>4.632745015365598</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682203</v>
+        <v>3.740601586682198</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.637303798139023</v>
+        <v>-4.681516746766212</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.144663400651175</v>
+        <v>2.1269782212003</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.014019565454533</v>
+        <v>1.050702877114269</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.608353083493252</v>
+        <v>4.630363070489094</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539106</v>
+        <v>3.699424827539099</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.744229346016875</v>
+        <v>-4.788442294644063</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.099186420657669</v>
+        <v>2.081501241206794</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9070940175766816</v>
+        <v>0.9437773292364179</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.541490993924176</v>
+        <v>4.563500980920018</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983736</v>
+        <v>3.68996278598373</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.889247904524123</v>
+        <v>-4.933460853151312</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.042607799398004</v>
+        <v>2.024922619947129</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7620754590694331</v>
+        <v>0.7987587707291693</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.455908660963061</v>
+        <v>4.477918647958903</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969748</v>
+        <v>3.711872614969741</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.007589670308841</v>
+        <v>-5.051802618936029</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.09520233234187</v>
+        <v>2.077517152890995</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7727614976323232</v>
+        <v>0.8094448092920594</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.562251523358548</v>
+        <v>4.58426151035439</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073538</v>
+        <v>3.714899237073531</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.059000092629549</v>
+        <v>-5.103213041256737</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.072423860539526</v>
+        <v>2.054738681088651</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7727614976323232</v>
+        <v>0.8094448092920594</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.560037220484487</v>
+        <v>4.582047207480328</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720059</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.1384195438373</v>
+        <v>-5.182632492464489</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.040559208130714</v>
+        <v>2.02287402867984</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7727614976323232</v>
+        <v>0.8094448092920594</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.559940348558777</v>
+        <v>4.581950335554618</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.233882541754518</v>
+        <v>-5.278095490381706</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.002367902521871</v>
+        <v>1.984682723070996</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7727614976323232</v>
+        <v>0.8094448092920594</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.55993424211682</v>
+        <v>4.581944229112661</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.273902539798302</v>
+        <v>-5.31811548842549</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.984456299866968</v>
+        <v>1.966771120416093</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7327414995885393</v>
+        <v>0.7694248112482756</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.53401863985316</v>
+        <v>4.556028626849002</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.736109598636264</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.329271701930495</v>
+        <v>-5.373484650557684</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.968042452761817</v>
+        <v>1.950357273310942</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7327414995885393</v>
+        <v>0.7694248112482756</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.539752457600887</v>
+        <v>4.561762444596729</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396007</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.374709481761323</v>
+        <v>-5.418922430388511</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.949405704172419</v>
+        <v>1.931720524721544</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6898965089103797</v>
+        <v>0.7265798205701159</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.513583826536924</v>
+        <v>4.535593813532766</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396416</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.286502647613744</v>
+        <v>-5.330715596240933</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.00456283068177</v>
+        <v>1.986877651230895</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6898965089103797</v>
+        <v>0.7265798205701159</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.533458219387243</v>
+        <v>4.555468206383085</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299176</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.110212423008437</v>
+        <v>-5.154425371635625</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.05877962104862</v>
+        <v>2.041094441597746</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6898965089103797</v>
+        <v>0.7265798205701159</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.517158919911971</v>
+        <v>4.539168906907813</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.7947252785904</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.927000759875342</v>
+        <v>-4.97121370850253</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.134495235765904</v>
+        <v>2.116810056315029</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6898965089103797</v>
+        <v>0.7265798205701159</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.519589869376016</v>
+        <v>4.541599856371858</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146279</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.855279312861491</v>
+        <v>-4.899492261488679</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.128975000419334</v>
+        <v>2.111289820968459</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7616179559242303</v>
+        <v>0.7983012675839666</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.528413923432216</v>
+        <v>4.550423910428058</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.72380989067684</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.832906287253785</v>
+        <v>-4.877119235880973</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.084839956583588</v>
+        <v>2.067154777132713</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7728737070371319</v>
+        <v>0.8095570186968681</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.482083120021128</v>
+        <v>4.504093107016971</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739465</v>
+        <v>3.715627631739458</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.865922583164529</v>
+        <v>-4.910135531791718</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.256831643104646</v>
+        <v>2.23914646365377</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7034363303703803</v>
+        <v>0.7401196420301166</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.625618898906433</v>
+        <v>4.647628885902275</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166405</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.854394947514921</v>
+        <v>-4.898607896142109</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.253363923192738</v>
+        <v>2.235678743741863</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7624369885717428</v>
+        <v>0.7991203002314791</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.6529405196555</v>
+        <v>4.674950506651342</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519025</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.951736448857289</v>
+        <v>-4.995949397484478</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.218095435177579</v>
+        <v>2.200410255726704</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7180168064062544</v>
+        <v>0.7547001180659907</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.629956522877995</v>
+        <v>4.651966509873837</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710419</v>
+        <v>3.705221264710412</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.037592478197256</v>
+        <v>-5.081805426824444</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.185004105634431</v>
+        <v>2.167318926183556</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6756407371801194</v>
+        <v>0.7123240488398557</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.605781963535152</v>
+        <v>4.627791950530995</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893109</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.020783553797985</v>
+        <v>-5.064996502425173</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.174146877214641</v>
+        <v>2.156461697763766</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6997068328684996</v>
+        <v>0.7363901445282358</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.602640822768683</v>
+        <v>4.624650809764525</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,45 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.867914706056215</v>
+        <v>3.715564596950184</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.161451916258785</v>
+        <v>-5.156379064990632</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.12804404327537</v>
+        <v>2.130073183782632</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5590384704076995</v>
+        <v>0.6450075819627776</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.528404316337252</v>
+        <v>4.579985783270299</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="2" t="n">
+        <v>45538</v>
+      </c>
+      <c r="B2076" t="n">
+        <v>3.78415047775071</v>
+      </c>
+      <c r="C2076" t="n">
+        <v>4.29409630604838</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>-5.156379064990632</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>2.130073183782632</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>0.6450075819627776</v>
+      </c>
+      <c r="G2076" t="n">
+        <v>4.287160103034748</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>119.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-44.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-677.2%</t>
+          <t>-684.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.2%</t>
+          <t>-166.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>758.1%</t>
+          <t>587.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-313.9%</t>
+          <t>-308.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.5%</t>
+          <t>-162.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017765</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839719</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626469</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987898</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392982</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632776</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.817959084029066</v>
+        <v>-4.908418586878637</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9419940371263693</v>
+        <v>0.9058102359865408</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3893561536472314</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.103147787240082</v>
+        <v>3.048872085530339</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.738349647868667</v>
+        <v>-4.836176018707442</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.977767125425349</v>
+        <v>0.9386365770898388</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3893561536472314</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.107077101074902</v>
+        <v>3.052801399365159</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.720635960990801</v>
+        <v>-4.818462331829577</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9855311840938352</v>
+        <v>0.946400635758325</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3925374825441482</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.109664482330392</v>
+        <v>3.055388780620649</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502331</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.597161689677783</v>
+        <v>-4.694988060516558</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.031918963839036</v>
+        <v>0.9927884155035258</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3925374825441482</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.106662553550386</v>
+        <v>3.052386851840643</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.377140891640773</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.121506320064454</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5337573276121284</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.192973497601788</v>
+        <v>3.138697795892045</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.244273202577495</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.190547578491589</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5337573276121284</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.208867680403611</v>
+        <v>3.154591978693869</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.124100119212996</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.23976265627769</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6539304109766273</v>
+        <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.282117374862612</v>
+        <v>3.22784167315287</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.988846757883019</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.303952103371121</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7891837723066044</v>
+        <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.373357494222038</v>
+        <v>3.319081792512296</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.048721585240711</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26603966382947</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7293089449489123</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.323470089208849</v>
+        <v>3.269194387499106</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767451</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.928901354329874</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.329256925428013</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7293089449489123</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.338759258443058</v>
+        <v>3.284483556733315</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.93137106079168</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.235913242165732</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7268392384871061</v>
+        <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.244921633888415</v>
+        <v>3.190645932178673</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.99974124711569</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.12782702912143</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.736114937523321</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.169748914795446</v>
+        <v>3.115473213085703</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.111613526741841</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.073514825902861</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.736114937523321</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.160185623427337</v>
+        <v>3.105909921717594</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.16713360263443</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.188337632238027</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.736114937523321</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.29721646011954</v>
+        <v>3.242940758409797</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.991659342841961</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.263094568146803</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.736114937523321</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.301783692111327</v>
+        <v>3.247507990401584</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225437</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.983734968257047</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.242006346741976</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.736114937523321</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.277525720872534</v>
+        <v>3.223250019162792</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.977456765687198</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.173055941171365</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.74239314009317</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.209830955815893</v>
+        <v>3.155555254106151</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.917604146483475</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.207169375284987</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.74239314009317</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.220003342248026</v>
+        <v>3.165727640538283</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.831360683457097</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.236613031069398</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.74239314009317</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.214949612821886</v>
+        <v>3.160673911112144</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.876667502856077</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.210266078754331</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7015829770839392</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.182239290460873</v>
+        <v>3.127963588751131</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.905700607558379</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.199204709906512</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7015829770839392</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.182791163493975</v>
+        <v>3.128515461784232</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.812890126107519</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.165601594378222</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7943934585347986</v>
+        <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.167750144255856</v>
+        <v>3.113474442546113</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.857279595436947</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.149719282571051</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7500039892053709</v>
+        <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.1429899385828</v>
+        <v>3.088714236873058</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.97382120054229</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.098178349040637</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6334623841000282</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.068140684031317</v>
+        <v>3.013864982321575</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.013745295124862</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.087700007038276</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6334623841000282</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.073631979861985</v>
+        <v>3.019356278152242</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.041525693026214</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.088085049646274</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6056819861986751</v>
+        <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.068460942889712</v>
+        <v>3.014185241179969</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.159906365756353</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8790885005548716</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5384641340476989</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.86648595159978</v>
+        <v>2.812210249890037</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.268520444199684</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9557925298967449</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5384641340476989</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.986635612318985</v>
+        <v>2.932359910609243</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.233111405951541</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9844691712983251</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5384641340476989</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.001148638421308</v>
+        <v>2.946872936711566</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.19472774339339</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9972420776639541</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5768477966058501</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.021598277298568</v>
+        <v>2.967322575588825</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.017611413358224</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.064817638523323</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5768477966058501</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.01832730614387</v>
+        <v>2.964051604434127</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.062703658191769</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.047464132351817</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5149517534364603</v>
+        <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.981873072004149</v>
+        <v>2.927597370294406</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.883328236953002</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.113001276153739</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6717285116071789</v>
+        <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.069726102212994</v>
+        <v>3.015450400503252</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.928342450473608</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.075803046077086</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6413796162925743</v>
+        <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.032324220355821</v>
+        <v>2.978048518646079</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.195346960746043</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9746928043070575</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4470165782496258</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.921397959868998</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.296544742183216</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.93341761362869</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3786077647043066</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.879556593638308</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.290033775568904</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9336219618287318</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3786077647043066</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.877156555192625</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.270995647861606</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9377619321198956</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.320424153373112</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.838771107602153</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.323511450136427</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.036050012844158</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.320424153373112</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.958065509236343</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067859</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.337378211470345</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.031336637296724</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2825662366392891</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.936184088182183</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789117</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.296895219547999</v>
+        <v>-4.394721590386775</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.053538364462588</v>
+        <v>1.014407816127078</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2825662366392891</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.942192618579109</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.149152249312997</v>
+        <v>-4.246978620151772</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.010585773833789</v>
+        <v>0.9714552254982785</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4503735938741723</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.940827254197238</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181163</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.232973470587695</v>
+        <v>-4.330799841426471</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9798509068553902</v>
+        <v>0.9407203585198802</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4503735938741723</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.943620875728719</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394723</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.226820764534911</v>
+        <v>-4.324647135373686</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9829743376681623</v>
+        <v>0.9438437893326523</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4565262999269565</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.947974847752048</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890606</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.243630062685413</v>
+        <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9753310951480718</v>
+        <v>0.9362005468125618</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4397170017764549</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.936969745601858</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798419</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.181332063909291</v>
+        <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.066585848455342</v>
+        <v>1.027455300119831</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4850112660508969</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.030481857963343</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.979541866244133</v>
+        <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9495939292355318</v>
+        <v>0.9104633809000218</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6830294582200513</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.951584774978963</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852419</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.030428578930327</v>
+        <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9995294764832292</v>
+        <v>0.9603989281477192</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6321427455338569</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.991342979689422</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319537</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.94381783628052</v>
+        <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.048801509659196</v>
+        <v>1.009670961323685</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7107684767390151</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.053146154528561</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489378</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.004027134285804</v>
+        <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.023253771281754</v>
+        <v>0.9841232229462431</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6505591787337306</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.015556556550061</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397787</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.954840485601453</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.041420048795423</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6505591787337306</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.01404817458999</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316242</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.910467353962884</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.059032168886286</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6949323103722992</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.040534921008567</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.932947704821769</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.044433822681323</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6949323103722992</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.034928715147158</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190319</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.885291974260713</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06987787193355</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7425880409333548</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.069903910511596</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569611</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.784773815761959</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.114977508707777</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8431061994321094</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.135107178985574</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.768868486329606</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.10809431295659</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7639935387228705</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.074394255035902</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932763</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.724030084721208</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.130127376210578</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7685369716677399</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.081218017413453</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917045</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.743528540963216</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.126488933344852</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7204523303878356</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.056528172276588</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405953</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.699325703877316</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.15004967070705</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7646551674737361</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.088929477055965</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265637</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.706885369714363</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.145435804841479</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8194585714835554</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.120221519931104</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284872</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.548593952175091</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.260000137040227</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8194585714835554</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.171469285114144</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321016</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.340951948540615</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.341497643088271</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.027100575118032</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.294495191889083</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475132</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.289919855818086</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.356858708415552</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.078132667840559</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.32006267576087</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404846</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.224695674690881</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.400135784959139</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.143356848967765</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.376384588529898</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688255</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.187268654619747</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.411067565286873</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.148608386996947</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.375496483646687</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992653</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.207380310654455</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.40427969520423</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.159635731994366</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.383369682976379</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636279</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.178967047554571</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.576202771465394</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.100660169247937</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.508542116349733</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957618</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.104184786529559</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.726228585093216</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.17544243027295</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.673524382182558</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998749</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.078100702265751</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.728370194812599</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.17544243027295</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.665232358196417</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896923</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.99022278915663</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.761714555640026</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.291368072696301</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.732980939234206</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.981330327763347</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.782825945924131</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.291368072696301</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.750535344960998</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.149806444733225</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.707290546540764</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.26342023697972</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.725621690935633</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782702</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.703550252103785</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.867062720780402</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.168701567310087</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.650060186321716</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.680829148420632</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.866815184750567</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.168701567310087</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.64072420881862</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.810030961714675</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.974040585284119</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.039499754016045</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.722109246693364</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.835905360188701</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.000768648388155</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.084411362727786</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.786134034414055</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.828850669973527</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.00026588046377</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.09146605294296</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.787042204532705</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.801899445647039</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.021052523839107</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.106346398970679</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.805976565794078</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784102</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.823443673477826</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.196537964851752</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.106346398970679</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.990079697939037</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.845851791282698</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.179691412632796</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.106346398970679</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.98219639284203</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.874076026860299</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.170455717951393</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.124323151421988</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.995036443862453</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.883516952748828</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.222933065317829</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.246750268965379</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.124746432110335</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.93579056008447</v>
+        <v>-3.033616930923246</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.204914716928873</v>
+        <v>2.165784168593363</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.194476661629738</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.096273362254252</v>
+        <v>4.041997660544508</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.012120537685376</v>
+        <v>-3.109946908524152</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.172494538782286</v>
+        <v>2.133363990446775</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.194476661629738</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.094385175148027</v>
+        <v>4.040109473438283</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.105784482362917</v>
+        <v>-3.203610853201693</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.129849190514132</v>
+        <v>2.090718642178621</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.100812716952197</v>
+        <v>1.010353214102625</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.033007037944364</v>
+        <v>3.978731336234621</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.267352907890172</v>
+        <v>-3.365179278728948</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.063655830513382</v>
+        <v>2.024525282177871</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9740297931543173</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.955371293875789</v>
+        <v>3.901095592166046</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.375653569760292</v>
+        <v>-3.473479940599068</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.033408972631253</v>
+        <v>1.994278424295742</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9740297931543173</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.968444700741707</v>
+        <v>3.914168999031965</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.468801041063658</v>
+        <v>-3.566627411902434</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.988155180892846</v>
+        <v>1.949024632557335</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8512005818717845</v>
+        <v>0.7607410790222131</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.886752370755127</v>
+        <v>3.832476669045385</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.496701828173131</v>
+        <v>-3.594528199011907</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.975518907176059</v>
+        <v>1.936388358840548</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8166036577288497</v>
+        <v>0.7261441548792783</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.864518257396369</v>
+        <v>3.810242555686626</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787383</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.619227930876025</v>
+        <v>-3.717054301714801</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.9232729100721</v>
+        <v>1.88414236173659</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6940775550259558</v>
+        <v>0.6036180521763844</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.787767039751831</v>
+        <v>3.733491338042088</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.849742427061614</v>
+        <v>-3.94756879790039</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.897773071188368</v>
+        <v>1.858642522852858</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4635630588403671</v>
+        <v>0.3731035559907957</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.716164301630982</v>
+        <v>3.661888599921239</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.198487512286057</v>
+        <v>-4.296313883124833</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.898586756100438</v>
+        <v>1.859456207764927</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3548151049214693</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.79122724828149</v>
+        <v>3.736951546571747</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.352473930062198</v>
+        <v>-4.450300300900974</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.905972458135621</v>
+        <v>1.866841909800111</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3548151049214693</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.86020751742713</v>
+        <v>3.805931815717387</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.301952026234532</v>
+        <v>-4.399778397073308</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.912232421786809</v>
+        <v>1.873101873451298</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3548151049214693</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.84625871954725</v>
+        <v>3.791983017837508</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.554427180242256</v>
+        <v>-4.652253551081032</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.823112849239133</v>
+        <v>1.783982300903622</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3548151049214693</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.858129208602664</v>
+        <v>3.803853506892922</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.847322936721668</v>
+        <v>-4.945149307560444</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.707165081166312</v>
+        <v>1.668034532830801</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3548151049214693</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.859339743121608</v>
+        <v>3.805064041411865</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251941</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.033987064856476</v>
+        <v>-5.131813435695253</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.63662117213971</v>
+        <v>1.597490623804199</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3280761340969094</v>
+        <v>0.237616631247338</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.847418102854194</v>
+        <v>3.793142401144451</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.180007751770439</v>
+        <v>-5.277834122609215</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.573290750110314</v>
+        <v>1.534160201774804</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3189930423030524</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.837046100514069</v>
+        <v>3.782770398804326</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.271721760880023</v>
+        <v>-5.369548131718799</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.698809203165525</v>
+        <v>1.659678654830014</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3189930423030524</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.999250157213113</v>
+        <v>3.94497445550337</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.303373419939993</v>
+        <v>-5.401199790778769</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.680995177505351</v>
+        <v>1.641864629169841</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3138245850586122</v>
+        <v>0.2233650822090408</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.990995720830263</v>
+        <v>3.93672001912052</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.385308238208876</v>
+        <v>-5.483134609047652</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.658450667766289</v>
+        <v>1.619320119430779</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.303889839471532</v>
+        <v>0.2134303366219606</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.995264291046507</v>
+        <v>3.940988589336763</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.487284360457283</v>
+        <v>-5.58511073129606</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.626585857322829</v>
+        <v>1.587455308987318</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2019137172231245</v>
+        <v>0.1114542143735531</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.943004256153364</v>
+        <v>3.888728554443621</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.377278076980062</v>
+        <v>-5.475104447818838</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.662741257957892</v>
+        <v>1.623610709622382</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2251182891403997</v>
+        <v>0.1346587862908283</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.949079886547905</v>
+        <v>3.894804184838162</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.234218501239136</v>
+        <v>-5.332044872077912</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.724215098976237</v>
+        <v>1.685084550640727</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2331317157303789</v>
+        <v>0.1426722128808076</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.958137953223867</v>
+        <v>3.903862251514123</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.932771775767298</v>
+        <v>-5.030598146606074</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.852054672047508</v>
+        <v>1.812924123711998</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5345784412022162</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.146266871389505</v>
+        <v>4.091991169679762</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679619</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.957362020002482</v>
+        <v>-5.055188390841258</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.843189752106145</v>
+        <v>1.804059203770635</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5345784412022162</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.147238049142215</v>
+        <v>4.092962347432472</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.906323643995962</v>
+        <v>-5.004150014834738</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.864448006888509</v>
+        <v>1.825317458552999</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5345784412022162</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.148080953521971</v>
+        <v>4.093805251812228</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969536</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.865184349129331</v>
+        <v>-4.963010719968107</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.899941823709307</v>
+        <v>1.860811275373796</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.575717736068847</v>
+        <v>0.4852582332192756</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.191802629316095</v>
+        <v>4.137526927606352</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.768549437110691</v>
+        <v>-4.866375807949467</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.754779784640697</v>
+        <v>1.715649236305187</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.672352648087487</v>
+        <v>0.5818931452379156</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.065967572651213</v>
+        <v>4.011691870941471</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.899130171641533</v>
+        <v>-4.99695654248031</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.706049534902324</v>
+        <v>1.666918986566814</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5417719135566444</v>
+        <v>0.4513124107070731</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.991121176006672</v>
+        <v>3.936845474296929</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.734633837450572</v>
+        <v>-4.832460208289348</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.756274887654792</v>
+        <v>1.717144339319281</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7062682477476063</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.074245795597331</v>
+        <v>4.019970093887589</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077622</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.762003770135004</v>
+        <v>-4.85983014097378</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.744514625017449</v>
+        <v>1.705384076681938</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7062682477476063</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.073433506033761</v>
+        <v>4.019157804324019</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.772388965024893</v>
+        <v>-4.870215335863669</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.750229326186565</v>
+        <v>1.711098777851055</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.695883052857717</v>
+        <v>0.6054235500081456</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.0770711682249</v>
+        <v>4.022795466515158</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.790977123747118</v>
+        <v>-4.888803494585894</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.8136310684741</v>
+        <v>1.77450052013859</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6772948941354917</v>
+        <v>0.5868353912859203</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.13675527876799</v>
+        <v>4.082479577058248</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.791275670443154</v>
+        <v>-4.88910204128193</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.810380660613985</v>
+        <v>1.771250112278474</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6769963474394558</v>
+        <v>0.5865368445898844</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.133445161568667</v>
+        <v>4.079169459858925</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.690452536752726</v>
+        <v>-4.788278907591502</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.855240809029547</v>
+        <v>1.816110260694037</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6894605629238096</v>
+        <v>0.5990010600742383</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.145454585798671</v>
+        <v>4.091178884088928</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.499671176000319</v>
+        <v>-4.597497546839096</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.931682606809053</v>
+        <v>1.892552058473543</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.880241923676217</v>
+        <v>0.7897824208266456</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.260052655728659</v>
+        <v>4.205776954018916</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.392707818150898</v>
+        <v>-4.490534188989674</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.954304795686419</v>
+        <v>1.915174247350908</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9387065316360185</v>
+        <v>0.8482470287864471</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.274968266242136</v>
+        <v>4.220692564532393</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.337377230249135</v>
+        <v>-4.435203601087911</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.011403967459182</v>
+        <v>1.972273419123671</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9940371195377806</v>
+        <v>0.9035776166882092</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.343133555595251</v>
+        <v>4.288857853885509</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.325323103336173</v>
+        <v>-4.423149474174949</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.009912186125804</v>
+        <v>1.970781637790294</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.006091246450743</v>
+        <v>0.9156317436011721</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.344052599644467</v>
+        <v>4.289776897934725</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.366478222904393</v>
+        <v>-4.46430459374317</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.995330768482652</v>
+        <v>1.956200220147141</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9649361268825225</v>
+        <v>0.8744766240329511</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.32124015808767</v>
+        <v>4.266964456377927</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.298429660212864</v>
+        <v>-4.39625603105164</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.035401219437146</v>
+        <v>1.996270671101636</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.032984689574052</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.374920321580471</v>
+        <v>4.320644619870728</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.530030053382364</v>
+        <v>-4.62785642422114</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.96296373234294</v>
+        <v>1.92383318400743</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.032984689574052</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.395122991754065</v>
+        <v>4.340847290044322</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.548102561673976</v>
+        <v>-4.645928932512752</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.955734729026296</v>
+        <v>1.916604180690785</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.032984689574052</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.395122991754065</v>
+        <v>4.340847290044322</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082828</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.723209394250421</v>
+        <v>-4.821035765089198</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.845943909589184</v>
+        <v>1.806813361253674</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.032984689574052</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.355374905347531</v>
+        <v>4.301099203637789</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74559333394358</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.691923373709966</v>
+        <v>-4.789749744548742</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.865480936802306</v>
+        <v>1.826350388466796</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.064270710114508</v>
+        <v>0.9738112072649363</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.381169136668745</v>
+        <v>4.326893434959002</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677817</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.538897981596682</v>
+        <v>-4.636724352435458</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.025862093220525</v>
+        <v>1.986731544885014</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.217296102227792</v>
+        <v>1.12683659937822</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.57215537150962</v>
+        <v>4.517879669799877</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073877</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.567205295469952</v>
+        <v>-4.665031666308728</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.202005392579508</v>
+        <v>2.162874844243998</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.217296102227792</v>
+        <v>1.12683659937822</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.759621596417912</v>
+        <v>4.705345894708169</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.733798520583474</v>
+        <v>-4.83162489142225</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.104771053888182</v>
+        <v>2.065640505552671</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.050702877114269</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.629068612703881</v>
+        <v>4.574792910994137</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568376</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.710762727221908</v>
+        <v>-4.808589098060684</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.117661773894526</v>
+        <v>2.078531225559016</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.050702877114269</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.632745015365598</v>
+        <v>4.578469313655855</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682198</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.681516746766212</v>
+        <v>-4.779343117604988</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.1269782212003</v>
+        <v>2.08784767286479</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.050702877114269</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.630363070489094</v>
+        <v>4.57608736877935</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539099</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.788442294644063</v>
+        <v>-4.886268665482839</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.081501241206794</v>
+        <v>2.042370692871284</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9437773292364179</v>
+        <v>0.8533178263868465</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.563500980920018</v>
+        <v>4.509225279210275</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.68996278598373</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.933460853151312</v>
+        <v>-5.031287223990088</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.024922619947129</v>
+        <v>1.985792071611619</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7987587707291693</v>
+        <v>0.708299267879598</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.477918647958903</v>
+        <v>4.42364294624916</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969741</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.051802618936029</v>
+        <v>-5.149628989774805</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.077517152890995</v>
+        <v>2.038386604555485</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8094448092920594</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.58426151035439</v>
+        <v>4.529985808644647</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073531</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.103213041256737</v>
+        <v>-5.201039412095513</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.054738681088651</v>
+        <v>2.01560813275314</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8094448092920594</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.582047207480328</v>
+        <v>4.527771505770586</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720059</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.182632492464489</v>
+        <v>-5.280458863303265</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.02287402867984</v>
+        <v>1.983743480344329</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8094448092920594</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.581950335554618</v>
+        <v>4.527674633844875</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.278095490381706</v>
+        <v>-5.375921861220482</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.984682723070996</v>
+        <v>1.945552174735485</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8094448092920594</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.581944229112661</v>
+        <v>4.527668527402919</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.31811548842549</v>
+        <v>-5.415941859264266</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.966771120416093</v>
+        <v>1.927640572080583</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7694248112482756</v>
+        <v>0.6789653083987042</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.556028626849002</v>
+        <v>4.501752925139259</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636264</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.373484650557684</v>
+        <v>-5.47131102139646</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.950357273310942</v>
+        <v>1.911226724975432</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7694248112482756</v>
+        <v>0.6789653083987042</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.561762444596729</v>
+        <v>4.507486742886986</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396007</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.418922430388511</v>
+        <v>-5.516748801227287</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.931720524721544</v>
+        <v>1.892589976386034</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7265798205701159</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.535593813532766</v>
+        <v>4.481318111823023</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396416</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.330715596240933</v>
+        <v>-5.428541967079709</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.986877651230895</v>
+        <v>1.947747102895384</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7265798205701159</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.555468206383085</v>
+        <v>4.501192504673342</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.154425371635625</v>
+        <v>-5.252251742474401</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.041094441597746</v>
+        <v>2.001963893262235</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7265798205701159</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.539168906907813</v>
+        <v>4.48489320519807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.7947252785904</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.97121370850253</v>
+        <v>-5.069040079341306</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.116810056315029</v>
+        <v>2.077679507979519</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7265798205701159</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.541599856371858</v>
+        <v>4.487324154662115</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146279</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.899492261488679</v>
+        <v>-4.997318632327455</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.111289820968459</v>
+        <v>2.072159272632948</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7983012675839666</v>
+        <v>0.7078417647343952</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.550423910428058</v>
+        <v>4.496148208718315</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72380989067684</v>
+        <v>3.723809890676846</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.877119235880973</v>
+        <v>-4.974945606719749</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.067154777132713</v>
+        <v>2.028024228797203</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8095570186968681</v>
+        <v>0.7190975158472968</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.504093107016971</v>
+        <v>4.449817405307228</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739458</v>
+        <v>3.715627631739463</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.910135531791718</v>
+        <v>-4.980560755611432</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.23914646365377</v>
+        <v>2.210976374125885</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7401196420301166</v>
+        <v>0.7145890443998656</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.647628885902275</v>
+        <v>4.632310527324124</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166405</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.898607896142109</v>
+        <v>-4.969033119961823</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.235678743741863</v>
+        <v>2.207508654213977</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7991203002314791</v>
+        <v>0.7735897026012281</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.674950506651342</v>
+        <v>4.659632148073191</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519025</v>
+        <v>3.717170884519031</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.995949397484478</v>
+        <v>-5.066374621304192</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.200410255726704</v>
+        <v>2.172240166198819</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7547001180659907</v>
+        <v>0.7291695204357397</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.651966509873837</v>
+        <v>4.636648151295686</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710412</v>
+        <v>3.705221264710417</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.081805426824444</v>
+        <v>-5.152230650644158</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.167318926183556</v>
+        <v>2.13914883665567</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7123240488398557</v>
+        <v>0.6867934512096047</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.627791950530995</v>
+        <v>4.612473591952844</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893109</v>
+        <v>3.691855684893114</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.064996502425173</v>
+        <v>-5.135421726244887</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.156461697763766</v>
+        <v>2.12829160823588</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7363901445282358</v>
+        <v>0.7108595468979848</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.624650809764525</v>
+        <v>4.609332451186374</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950184</v>
+        <v>3.715564596950187</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.156379064990632</v>
+        <v>-5.226804288810346</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.130073183782632</v>
+        <v>2.101903094254746</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6450075819627776</v>
+        <v>0.6194769843325265</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.579985783270299</v>
+        <v>4.564667424692148</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.78415047775071</v>
+        <v>3.84943138993288</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.29409630604838</v>
+        <v>4.31046766093099</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.156379064990632</v>
+        <v>-5.226804288810346</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.130073183782632</v>
+        <v>2.101903094254746</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6450075819627776</v>
+        <v>0.6194769843325265</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.287160103034748</v>
+        <v>4.303531457917358</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>127.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.7%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.3%</t>
+          <t>-679.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.0%</t>
+          <t>-164.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.8%</t>
+          <t>591.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.4%</t>
+          <t>-304.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-162.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.555286489354224</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.050248080979074</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.3865658371823568</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.104658603343925</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.422418800290946</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.119289339406208</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.3865658371823568</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.120552786145748</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.302245716926447</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.16850441719231</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.5067389205468558</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.19380248060475</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.16699235559647</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.23269386428574</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6419922818768329</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.285042599964175</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.226867182954162</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.194781424744089</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.5821174545191408</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.235155194950986</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-4.107046952043325</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.257998686342632</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.5821174545191408</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.250444364185195</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-4.109516658505131</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.164655003080352</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.5796477480573345</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.156606739630552</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.177886844829142</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.056568790036049</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.5889234470935495</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.081434020537583</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.289759124455292</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.00225658681748</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.5889234470935495</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.071870729169474</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.345279200347882</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.117079393152647</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.5889234470935495</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.208901565861677</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.169804940555412</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.191836329061422</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.5889234470935495</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.213468797853464</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-4.161880565970498</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.170748107656595</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.5889234470935495</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.189210826614671</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-4.155602363400649</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.101797702085984</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.5952016496633985</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.12151606155803</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-4.095749744196926</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.135911136199606</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.5952016496633985</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.131688447990163</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-4.009506281170548</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.165354791984017</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.5952016496633985</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.126634718564023</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-4.054813100569528</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.139007839668951</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5543914866541677</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.09392439620301</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-4.083846205271829</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.127946470821132</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5543914866541677</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.094476269236112</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.99103572382097</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.094343355292841</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.6472019681050271</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.079435249997993</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-4.035425193150398</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.078461043485671</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.6028124987755994</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.054675044324938</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-4.15196679825574</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.026920109955257</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.4862708936702566</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>2.979825789773455</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.191890892838313</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.016441767952895</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.4862708936702566</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>2.985317085604122</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.219671290739665</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.016826810560894</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.4584904957689035</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>2.980146048631849</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.338051963469804</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8078302614694914</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.3912726436179274</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.778171057341916</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.446666041913135</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.8845342908113645</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.3912726436179274</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.898320718061123</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.411257003664992</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9132109322129447</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.3912726436179274</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.912833744163446</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.372873341106841</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9259838385785737</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4296563061760785</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.933283383040705</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.195757011071675</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>0.9935593994379421</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4296563061760785</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.930012411886007</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.24084925590522</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>0.976205893266437</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.3677602630066887</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.893558177746286</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-4.061473834666453</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.041743037068358</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.5245370211774074</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>2.981411207955131</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-4.106488048187058</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.004544806991706</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.4941881258628028</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.944009326097958</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.373492558459493</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9034345652216775</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.2998250878198542</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.833083065611135</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.474690339896666</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.8621593745433098</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.231416274274535</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.791241699380445</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.468179373282354</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.8623637227433516</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.231416274274535</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.788841660934762</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.449141245575056</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.8665036930345156</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.1732326629433405</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.75045621334429</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.501657047849877</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>0.9647917737587777</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.1732326629433405</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.86975061497848</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.515523809183795</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>0.9600783982113441</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1353747462095176</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.84786919392432</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.394721590386775</v>
+        <v>-4.47504081726145</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014407816127078</v>
+        <v>0.982280125377208</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1353747462095176</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.853877724321246</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.327297847026447</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>0.9393275347484087</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3031821034444007</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.852512359939375</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.411119068301145</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.9085926677700102</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3031821034444007</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.855305981470856</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.404966362248361</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.9117160985827824</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.309334809497185</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.859659953494185</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.421775660398863</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.9040728560626918</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.2925255113466834</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.848654851343995</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.359477661622741</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>0.9953276093699617</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.3378197756211254</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.942166963705481</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-4.157687463957583</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.8783356901501518</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.5358379677902798</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.8632698807211</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.208574176643777</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.9282712373978492</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.4849512551040853</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.903028085431559</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-4.121963433993971</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>0.9775432705738156</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.5635769863092435</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.964831260270697</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.182172731999255</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>0.9519955321963733</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5033676883039589</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.927241662292198</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-4.132986083314904</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>0.9701618097100424</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5033676883039589</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.925733280332127</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-4.088612951676335</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>0.9877739298009061</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5477408199425275</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.952220026750704</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-4.11109330253522</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>0.9731755835959426</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5477408199425275</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.946613820889295</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-4.063437571974164</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>0.9986196328481696</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.5953965505035832</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>2.981589016253733</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.96291941347541</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.043719269622396</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.6959147090023378</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.04679228472771</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.947014084043057</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.036836073871209</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.6168020482930989</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>2.986079360778039</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.902175682434659</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.058869137125197</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.6213454812379684</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>2.992903123155589</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.921674138676667</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.055230694259472</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.5732608399580641</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.968213278018725</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.877471301590767</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.078791431621669</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.6174636770439645</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.000614582798102</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.885030967427814</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.074177565756098</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.6722670810537839</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.031906625673241</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.726739549888542</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.188741897954847</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.6722670810537839</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.083154390856281</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.519097546254065</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.27023940400289</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.87990908468826</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.20618029763122</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.468065453531537</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.285600469330171</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.930941177410788</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.231747781503007</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.402841272404332</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.328877545873759</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>0.9961653585379935</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.288069694272035</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.365414252333198</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.339809326201493</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.001416896567175</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.287181589388824</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.3611542728315</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.342770110333412</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.075754162455079</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.333040741252807</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.332741009731616</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.514693186594577</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>1.01677859970865</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.45821317462616</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.257958748706603</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.664719000222399</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.091560860733663</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.623195440458985</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.231874664442795</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.666860609941781</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.091560860733663</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.614903416472844</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.143996751333675</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.700204970769209</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.207486503157014</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.682651997510634</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.135104289940392</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.721316361053313</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.207486503157014</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.700206403237426</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.30358040691027</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.645780961669946</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.179538667440433</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.675292749212062</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.85732421428083</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.805553135909584</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.084819997770801</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.599731244598144</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.834603110597677</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.805305599879749</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.084819997770801</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.590395267095048</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.96380492389172</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.912531000413301</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.9556181844767584</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.671780304969792</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.989679322365745</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.939259063517338</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>1.0005297931885</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.735805092690483</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.982624632150572</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.938756295592952</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>1.007584483403673</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.736713262809133</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.955673407824084</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>1.959542938968289</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.022464829431392</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.755647624070506</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.977217635654871</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.135028379980934</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.022464829431392</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.939750756215465</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.999625753459743</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.118181827761978</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.022464829431392</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.931867451118459</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-3.027849989037343</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.108946133080575</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.040441581882701</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.944707502138881</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-3.037290914925873</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.161423480447011</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.162868699426093</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.074417490386763</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.033616930923246</v>
+        <v>-3.089564522261515</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.165784168593363</v>
+        <v>2.143405132058055</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.110595092090451</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>4.045944420530679</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.109946908524152</v>
+        <v>-3.165894499862421</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.133363990446775</v>
+        <v>2.110984953911468</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.110595092090451</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>4.044056233424454</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.203610853201693</v>
+        <v>-3.259558444539962</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.090718642178621</v>
+        <v>2.068339605643314</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.010353214102625</v>
+        <v>1.01693114741291</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.978731336234621</v>
+        <v>3.982678096220792</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.365179278728948</v>
+        <v>-3.421126870067217</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.024525282177871</v>
+        <v>2.002146245642564</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.8901482236150305</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.901095592166046</v>
+        <v>3.905042352152217</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.473479940599068</v>
+        <v>-3.529427531937336</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.994278424295742</v>
+        <v>1.971899387760435</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.8901482236150305</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.914168999031965</v>
+        <v>3.918115759018135</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.566627411902434</v>
+        <v>-3.622575003240703</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.949024632557335</v>
+        <v>1.926645596022028</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.7673190123324978</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.832476669045385</v>
+        <v>3.836423429031556</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.594528199011907</v>
+        <v>-3.650475790350176</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.936388358840548</v>
+        <v>1.914009322305241</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.732722088189563</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810242555686626</v>
+        <v>3.814189315672797</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.717054301714801</v>
+        <v>-3.77300189305307</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.88414236173659</v>
+        <v>1.861763325201282</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.6101959854866691</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733491338042088</v>
+        <v>3.737438098028259</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.94756879790039</v>
+        <v>-4.003516389238658</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.858642522852858</v>
+        <v>1.83626348631755</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.3796814893010804</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.661888599921239</v>
+        <v>3.66583535990741</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.296313883124833</v>
+        <v>-4.352261474463102</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.859456207764927</v>
+        <v>1.83707717122962</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2709335353821826</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.736951546571747</v>
+        <v>3.740898306557918</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.450300300900974</v>
+        <v>-4.506247892239243</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.866841909800111</v>
+        <v>1.844462873264804</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2709335353821826</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.805931815717387</v>
+        <v>3.809878575703558</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.399778397073308</v>
+        <v>-4.455725988411577</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.873101873451298</v>
+        <v>1.850722836915991</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2709335353821826</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.791983017837508</v>
+        <v>3.795929777823678</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.652253551081032</v>
+        <v>-4.708201142419301</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.783982300903622</v>
+        <v>1.761603264368315</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2709335353821826</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.803853506892922</v>
+        <v>3.807800266879092</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.945149307560444</v>
+        <v>-5.001096898898713</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.668034532830801</v>
+        <v>1.645655496295494</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2709335353821826</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.805064041411865</v>
+        <v>3.809010801398036</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.131813435695253</v>
+        <v>-5.187761027033521</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.597490623804199</v>
+        <v>1.575111587268892</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.2441945645576227</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793142401144451</v>
+        <v>3.797089161130622</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.277834122609215</v>
+        <v>-5.333781713947483</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.534160201774804</v>
+        <v>1.511781165239497</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.2351114727637657</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.782770398804326</v>
+        <v>3.786717158790497</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.369548131718799</v>
+        <v>-5.425495723057068</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.659678654830014</v>
+        <v>1.637299618294707</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.2351114727637657</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94497445550337</v>
+        <v>3.948921215489541</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.401199790778769</v>
+        <v>-5.457147382117038</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.641864629169841</v>
+        <v>1.619485592634533</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.2299430155193255</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93672001912052</v>
+        <v>3.940666779106691</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.483134609047652</v>
+        <v>-5.539082200385921</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.619320119430779</v>
+        <v>1.596941082895471</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.2200082699322453</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940988589336763</v>
+        <v>3.944935349322934</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.58511073129606</v>
+        <v>-5.641058322634328</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.587455308987318</v>
+        <v>1.565076272452011</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>0.1180321476838377</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888728554443621</v>
+        <v>3.892675314429792</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.475104447818838</v>
+        <v>-5.531052039157107</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.623610709622382</v>
+        <v>1.601231673087074</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.1412367196011129</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.894804184838162</v>
+        <v>3.898750944824333</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.332044872077912</v>
+        <v>-5.387992463416181</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.685084550640727</v>
+        <v>1.662705514105419</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.1492501461910922</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903862251514123</v>
+        <v>3.907809011500294</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.030598146606074</v>
+        <v>-5.086545737944343</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.812924123711998</v>
+        <v>1.79054508717669</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4506968716629295</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.091991169679762</v>
+        <v>4.095937929665933</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.055188390841258</v>
+        <v>-5.111135982179527</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.804059203770635</v>
+        <v>1.781680167235328</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4506968716629295</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.092962347432472</v>
+        <v>4.096909107418643</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.004150014834738</v>
+        <v>-5.060097606173007</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.825317458552999</v>
+        <v>1.802938422017691</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4506968716629295</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093805251812228</v>
+        <v>4.097752011798399</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.963010719968107</v>
+        <v>-5.018958311306376</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.860811275373796</v>
+        <v>1.838432238838489</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.4918361665295603</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.137526927606352</v>
+        <v>4.141473687592523</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.866375807949467</v>
+        <v>-4.922323399287736</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.715649236305187</v>
+        <v>1.693270199769879</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.5884710785482002</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011691870941471</v>
+        <v>4.015638630927642</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.99695654248031</v>
+        <v>-5.052904133818578</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.666918986566814</v>
+        <v>1.644539950031506</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4513124107070731</v>
+        <v>0.4578903440173577</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936845474296929</v>
+        <v>3.9407922342831</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.832460208289348</v>
+        <v>-4.888407799627617</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.717144339319281</v>
+        <v>1.694765302783974</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6223866782083196</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.019970093887589</v>
+        <v>4.02391685387376</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.85983014097378</v>
+        <v>-4.915777732312049</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.705384076681938</v>
+        <v>1.683005040146631</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6223866782083196</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019157804324019</v>
+        <v>4.02310456431019</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.870215335863669</v>
+        <v>-4.926162927201938</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.711098777851055</v>
+        <v>1.688719741315747</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6054235500081456</v>
+        <v>0.6120014833184303</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.022795466515158</v>
+        <v>4.026742226501328</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.888803494585894</v>
+        <v>-4.944751085924163</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.77450052013859</v>
+        <v>1.752121483603283</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5868353912859203</v>
+        <v>0.593413324596205</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.082479577058248</v>
+        <v>4.086426337044418</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.88910204128193</v>
+        <v>-4.945049632620199</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.771250112278474</v>
+        <v>1.748871075743167</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5865368445898844</v>
+        <v>0.5931147779001691</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079169459858925</v>
+        <v>4.083116219845095</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.788278907591502</v>
+        <v>-4.844226498929771</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.816110260694037</v>
+        <v>1.793731224158729</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5990010600742383</v>
+        <v>0.6055789933845229</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091178884088928</v>
+        <v>4.095125644075098</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.597497546839096</v>
+        <v>-4.653445138177364</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.892552058473543</v>
+        <v>1.870173021938235</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7897824208266456</v>
+        <v>0.7963603541369303</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.205776954018916</v>
+        <v>4.209723714005086</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.490534188989674</v>
+        <v>-4.546481780327943</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.915174247350908</v>
+        <v>1.8927952108156</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8482470287864471</v>
+        <v>0.8548249620967318</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.220692564532393</v>
+        <v>4.224639324518564</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.435203601087911</v>
+        <v>-4.49115119242618</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.972273419123671</v>
+        <v>1.949894382588364</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>0.9101555499984939</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.29280461387168</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.423149474174949</v>
+        <v>-4.479097065513217</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.970781637790294</v>
+        <v>1.948402601254987</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>0.9222096769114567</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.293723657920895</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.46430459374317</v>
+        <v>-4.520252185081438</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.956200220147141</v>
+        <v>1.933821183611834</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>0.8810545573432358</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.270911216364098</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.39625603105164</v>
+        <v>-4.452203622389908</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.996270671101636</v>
+        <v>1.973891634566328</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9491031200347656</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320644619870728</v>
+        <v>4.324591379856899</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.62785642422114</v>
+        <v>-4.683804015559409</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.92383318400743</v>
+        <v>1.901454147472122</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9491031200347656</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340847290044322</v>
+        <v>4.344794050030493</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.645928932512752</v>
+        <v>-4.701876523851021</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.916604180690785</v>
+        <v>1.894225144155478</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9491031200347656</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.340847290044322</v>
+        <v>4.344794050030493</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.821035765089198</v>
+        <v>-4.876983356427466</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.806813361253674</v>
+        <v>1.784434324718366</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9491031200347656</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.301099203637789</v>
+        <v>4.30504596362396</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.789749744548742</v>
+        <v>-4.845697335887011</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.826350388466796</v>
+        <v>1.803971351931488</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9738112072649363</v>
+        <v>0.980389140575221</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.326893434959002</v>
+        <v>4.330840194945173</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.636724352435458</v>
+        <v>-4.692671943773727</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.986731544885014</v>
+        <v>1.964352508349707</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.12683659937822</v>
+        <v>1.133414532688505</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.517879669799877</v>
+        <v>4.521826429786048</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073882</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.665031666308728</v>
+        <v>-4.720979257646997</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.162874844243998</v>
+        <v>2.140495807708691</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.12683659937822</v>
+        <v>1.133414532688505</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.705345894708169</v>
+        <v>4.70929265469434</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.83162489142225</v>
+        <v>-4.887572482760519</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.065640505552671</v>
+        <v>2.043261469017364</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.9668213075749825</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.574792910994137</v>
+        <v>4.578739670980308</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.808589098060684</v>
+        <v>-4.864536689398953</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.078531225559016</v>
+        <v>2.056152189023708</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.9668213075749825</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.578469313655855</v>
+        <v>4.582416073642026</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.779343117604988</v>
+        <v>-4.835290708943257</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.08784767286479</v>
+        <v>2.065468636329482</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.9668213075749825</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.57608736877935</v>
+        <v>4.580034128765521</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539106</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.886268665482839</v>
+        <v>-4.942216256821108</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.042370692871284</v>
+        <v>2.019991656335977</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8533178263868465</v>
+        <v>0.8598957596971312</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.509225279210275</v>
+        <v>4.513172039196446</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.031287223990088</v>
+        <v>-5.087234815328356</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.985792071611619</v>
+        <v>1.963413035076311</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.708299267879598</v>
+        <v>0.7148772011898826</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.42364294624916</v>
+        <v>4.427589706235331</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.149628989774805</v>
+        <v>-5.071559387531087</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.038386604555485</v>
+        <v>2.069614445452972</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7749876643537973</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.529985808644647</v>
+        <v>4.563587223391433</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073536</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.201039412095513</v>
+        <v>-5.122969809851795</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.01560813275314</v>
+        <v>2.046835973650627</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7749876643537973</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.527771505770586</v>
+        <v>4.561372920517371</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.280458863303265</v>
+        <v>-5.202389261059547</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.983743480344329</v>
+        <v>2.014971321241816</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7749876643537973</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.527674633844875</v>
+        <v>4.561276048591661</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.375921861220482</v>
+        <v>-5.297852258976764</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.945552174735485</v>
+        <v>1.976780015632973</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.718985306442488</v>
+        <v>0.7749876643537973</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.527668527402919</v>
+        <v>4.561269942149704</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.415941859264266</v>
+        <v>-5.337872257020548</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.927640572080583</v>
+        <v>1.95886841297807</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.7349676663100135</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.501752925139259</v>
+        <v>4.535354339886045</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.47131102139646</v>
+        <v>-5.393241419152742</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.911226724975432</v>
+        <v>1.942454565872919</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.7349676663100135</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.507486742886986</v>
+        <v>4.541088157633771</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.516748801227287</v>
+        <v>-5.438679198983569</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.892589976386034</v>
+        <v>1.923817817283521</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6921226756318539</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.481318111823023</v>
+        <v>4.514919526569809</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.428541967079709</v>
+        <v>-5.350472364835991</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.947747102895384</v>
+        <v>1.978974943792871</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6921226756318539</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.501192504673342</v>
+        <v>4.534793919420128</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.252251742474401</v>
+        <v>-5.174182140230683</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.001963893262235</v>
+        <v>2.033191734159722</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6921226756318539</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.48489320519807</v>
+        <v>4.518494619944855</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.069040079341306</v>
+        <v>-4.990970477097588</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.077679507979519</v>
+        <v>2.108907348877006</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6921226756318539</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.487324154662115</v>
+        <v>4.520925569408901</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.997318632327455</v>
+        <v>-4.919249030083737</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.072159272632948</v>
+        <v>2.103387113530435</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7078417647343952</v>
+        <v>0.7638441226457046</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.496148208718315</v>
+        <v>4.529749623465101</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676846</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.974945606719749</v>
+        <v>-4.896876004476031</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.028024228797203</v>
+        <v>2.05925206969469</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7190975158472968</v>
+        <v>0.7750998737586061</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.449817405307228</v>
+        <v>4.483418820054013</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739463</v>
+        <v>3.715627631739466</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.980560755611432</v>
+        <v>-4.929892300386776</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.210976374125885</v>
+        <v>2.231243756215747</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7145890443998656</v>
+        <v>0.7056624970918546</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.632310527324124</v>
+        <v>4.626954598939318</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.969033119961823</v>
+        <v>-4.918364664737167</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.207508654213977</v>
+        <v>2.22777603630384</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7735897026012281</v>
+        <v>0.764663155293217</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.659632148073191</v>
+        <v>4.654276219688384</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519031</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.066374621304192</v>
+        <v>-5.015706166079536</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.172240166198819</v>
+        <v>2.192507548288681</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7291695204357397</v>
+        <v>0.7202429731277287</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.636648151295686</v>
+        <v>4.63129222291088</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710417</v>
+        <v>3.705221264710419</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.152230650644158</v>
+        <v>-5.101562195419502</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.13914883665567</v>
+        <v>2.159416218745533</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6867934512096047</v>
+        <v>0.6778669039015937</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.612473591952844</v>
+        <v>4.607117663568038</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893114</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.135421726244887</v>
+        <v>-5.084753271020231</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.12829160823588</v>
+        <v>2.148558990325743</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7108595468979848</v>
+        <v>0.7019329995899738</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.609332451186374</v>
+        <v>4.603976522801567</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.226804288810346</v>
+        <v>-5.17613583358569</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.101903094254746</v>
+        <v>2.122170476344609</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6194769843325265</v>
+        <v>0.6105504370245156</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.564667424692148</v>
+        <v>4.559311496307342</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.84943138993288</v>
+        <v>3.885329953651988</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.31046766093099</v>
+        <v>4.395562195069364</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.226804288810346</v>
+        <v>-5.17613583358569</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.101903094254746</v>
+        <v>2.122170476344609</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6194769843325265</v>
+        <v>0.6105504370245156</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.303531457917358</v>
+        <v>4.388625992055732</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,27 +834,27 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>114.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.2%</t>
+          <t>-664.9%</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.0%</t>
+          <t>-163.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>591.6%</t>
+          <t>590.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.5%</t>
+          <t>-305.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.9%</t>
+          <t>-147.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-20.7%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839719</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.555286489354224</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.050248080979074</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3865658371823568</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.104658603343925</v>
+        <v>3.138697795892045</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.422418800290946</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.119289339406208</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3865658371823568</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.120552786145748</v>
+        <v>3.154591978693869</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.302245716926447</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.16850441719231</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5067389205468558</v>
+        <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.19380248060475</v>
+        <v>3.22784167315287</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.16699235559647</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.23269386428574</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6419922818768329</v>
+        <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.285042599964175</v>
+        <v>3.319081792512296</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.226867182954162</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.194781424744089</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5821174545191408</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.235155194950986</v>
+        <v>3.269194387499106</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.107046952043325</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.257998686342632</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5821174545191408</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.250444364185195</v>
+        <v>3.284483556733315</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.109516658505131</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.164655003080352</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5796477480573345</v>
+        <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.156606739630552</v>
+        <v>3.190645932178673</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.177886844829142</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.056568790036049</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5889234470935495</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.081434020537583</v>
+        <v>3.115473213085703</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.289759124455292</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.00225658681748</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5889234470935495</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.071870729169474</v>
+        <v>3.105909921717594</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.345279200347882</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.117079393152647</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5889234470935495</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.208901565861677</v>
+        <v>3.242940758409797</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.169804940555412</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.191836329061422</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5889234470935495</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.213468797853464</v>
+        <v>3.247507990401584</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.161880565970498</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.170748107656595</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5889234470935495</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.189210826614671</v>
+        <v>3.223250019162792</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.155602363400649</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.101797702085984</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5952016496633985</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.12151606155803</v>
+        <v>3.155555254106151</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.095749744196926</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.135911136199606</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5952016496633985</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.131688447990163</v>
+        <v>3.165727640538283</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.009506281170548</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165354791984017</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5952016496633985</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.126634718564023</v>
+        <v>3.160673911112144</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.054813100569528</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.139007839668951</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5543914866541677</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.09392439620301</v>
+        <v>3.127963588751131</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.083846205271829</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.127946470821132</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5543914866541677</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.094476269236112</v>
+        <v>3.128515461784232</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.99103572382097</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.094343355292841</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6472019681050271</v>
+        <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.079435249997993</v>
+        <v>3.113474442546113</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.035425193150398</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.078461043485671</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6028124987755994</v>
+        <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.054675044324938</v>
+        <v>3.088714236873058</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.15196679825574</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.026920109955257</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4862708936702566</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.979825789773455</v>
+        <v>3.013864982321575</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.191890892838313</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.016441767952895</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4862708936702566</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.985317085604122</v>
+        <v>3.019356278152242</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.219671290739665</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.016826810560894</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4584904957689035</v>
+        <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.980146048631849</v>
+        <v>3.014185241179969</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.338051963469804</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8078302614694914</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3912726436179274</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.778171057341916</v>
+        <v>2.812210249890037</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.446666041913135</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8845342908113645</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3912726436179274</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.898320718061123</v>
+        <v>2.932359910609243</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.411257003664992</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9132109322129447</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3912726436179274</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.912833744163446</v>
+        <v>2.946872936711566</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.372873341106841</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9259838385785737</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4296563061760785</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.933283383040705</v>
+        <v>2.967322575588825</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.195757011071675</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9935593994379421</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4296563061760785</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.930012411886007</v>
+        <v>2.964051604434127</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.24084925590522</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.976205893266437</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3677602630066887</v>
+        <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.893558177746286</v>
+        <v>2.927597370294406</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.061473834666453</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.041743037068358</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5245370211774074</v>
+        <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.981411207955131</v>
+        <v>3.015450400503252</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.106488048187058</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.004544806991706</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4941881258628028</v>
+        <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.944009326097958</v>
+        <v>2.978048518646079</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.373492558459493</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9034345652216775</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2998250878198542</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.833083065611135</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.474690339896666</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8621593745433098</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.231416274274535</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.791241699380445</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.468179373282354</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8623637227433516</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.231416274274535</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.788841660934762</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.449141245575056</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8665036930345156</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1732326629433405</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.75045621334429</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.501657047849877</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9647917737587777</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1732326629433405</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.86975061497848</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.515523809183795</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9600783982113441</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1353747462095176</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.84786919392432</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.47504081726145</v>
+        <v>-4.394721590386775</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.982280125377208</v>
+        <v>1.014407816127078</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1353747462095176</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.853877724321246</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.327297847026447</v>
+        <v>-4.246978620151772</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9393275347484087</v>
+        <v>0.9714552254982785</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3031821034444007</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.852512359939375</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.411119068301145</v>
+        <v>-4.330799841426471</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9085926677700102</v>
+        <v>0.9407203585198802</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3031821034444007</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.855305981470856</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.404966362248361</v>
+        <v>-4.324647135373686</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9117160985827824</v>
+        <v>0.9438437893326523</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.309334809497185</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.859659953494185</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.616727494248718</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.421775660398863</v>
+        <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9040728560626918</v>
+        <v>0.879788496525296</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2925255113466834</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.848654851343995</v>
+        <v>2.826281993604849</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.683063048045539</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.359477661622741</v>
+        <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9953276093699617</v>
+        <v>0.9710432498325656</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3378197756211254</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.942166963705481</v>
+        <v>2.919794105966335</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.485355049759666</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.157687463957583</v>
+        <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8783356901501518</v>
+        <v>0.854051330612756</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5358379677902798</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.8632698807211</v>
+        <v>2.840897022981955</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.555645282081842</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.208574176643777</v>
+        <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9282712373978492</v>
+        <v>0.9039868778604534</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4849512551040853</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.903028085431559</v>
+        <v>2.880655227692413</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.570273018197885</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.121963433993971</v>
+        <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9775432705738156</v>
+        <v>0.9532589110364196</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5635769863092435</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.964831260270697</v>
+        <v>2.942458402531552</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.568808999022557</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.182172731999255</v>
+        <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9519955321963733</v>
+        <v>0.9277111726589773</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5033676883039589</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.927241662292198</v>
+        <v>2.904868804553053</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.567300617062485</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.132986083314904</v>
+        <v>-4.04052132760904</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9701618097100424</v>
+        <v>0.9507356617051221</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5033676883039589</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.925733280332127</v>
+        <v>2.903360422592981</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.567163484497922</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.088612951676335</v>
+        <v>-3.996148195970472</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9877739298009061</v>
+        <v>0.9683477817959858</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5477408199425275</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.952220026750704</v>
+        <v>2.929847169011559</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.561557278636512</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.11109330253522</v>
+        <v>-4.018628546829357</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9731755835959426</v>
+        <v>0.9537494355910223</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5477408199425275</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.946613820889295</v>
+        <v>2.924240963150149</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.567939035664317</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.063437571974164</v>
+        <v>-3.970972816268301</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9986196328481696</v>
+        <v>0.9791934848432493</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5953965505035832</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.981589016253733</v>
+        <v>2.959216158514587</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.572831409039042</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.96291941347541</v>
+        <v>-3.870454657769546</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.043719269622396</v>
+        <v>1.024293121617476</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6959147090023378</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.04679228472771</v>
+        <v>3.024419426988565</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.559586081514914</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.947014084043057</v>
+        <v>-3.854549328337193</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.036836073871209</v>
+        <v>1.017409925866289</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6168020482930989</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.986079360778039</v>
+        <v>2.963706503038894</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.563683784125542</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.902175682434659</v>
+        <v>-3.809710926728795</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.058869137125197</v>
+        <v>1.039442989120277</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6213454812379684</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.992903123155589</v>
+        <v>2.970530265416444</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.56784472375662</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.921674138676667</v>
+        <v>-3.829209382970804</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.055230694259472</v>
+        <v>1.035804546254552</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5732608399580641</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.968213278018725</v>
+        <v>2.94584042027958</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.573724326284458</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.877471301590767</v>
+        <v>-3.785006545884903</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.078791431621669</v>
+        <v>1.059365283616749</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6174636770439645</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.000614582798102</v>
+        <v>2.978241725058957</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.572134326753705</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.885030967427814</v>
+        <v>-3.79256621172195</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.074177565756098</v>
+        <v>1.054751417751178</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6722670810537839</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.031906625673241</v>
+        <v>3.009533767934096</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.623382091936745</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.726739549888542</v>
+        <v>-3.634274794182678</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.188741897954847</v>
+        <v>1.169315749949926</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6722670810537839</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.083154390856281</v>
+        <v>3.060781533117136</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.621822796530998</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.519097546254065</v>
+        <v>-3.426632790548202</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.27023940400289</v>
+        <v>1.25081325599797</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.87990908468826</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.20618029763122</v>
+        <v>3.183807439892075</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.616771024769268</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.468065453531537</v>
+        <v>-3.375600697825674</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.285600469330171</v>
+        <v>1.266174321325251</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.930941177410788</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.231747781503007</v>
+        <v>3.209374923763861</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.633958428861973</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.402841272404332</v>
+        <v>-3.310376516698468</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.328877545873759</v>
+        <v>1.309451397868838</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9961653585379935</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.288069694272035</v>
+        <v>3.265696836532889</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.629919401161253</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.365414252333198</v>
+        <v>-3.272949496627334</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.339809326201493</v>
+        <v>1.320383178196572</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.001416896567175</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.287181589388824</v>
+        <v>3.264808731649679</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.631176193492494</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.3611542728315</v>
+        <v>-3.293061152662042</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.342770110333412</v>
+        <v>1.313595308113929</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.075754162455079</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.333040741252807</v>
+        <v>3.27268193097937</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.791733964513704</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.332741009731616</v>
+        <v>-3.264647889562159</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.514693186594577</v>
+        <v>1.485518384375093</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.01677859970865</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45821317462616</v>
+        <v>3.397854364352724</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.911846873731522</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.257958748706603</v>
+        <v>-3.189865628537146</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.664719000222399</v>
+        <v>1.635544198002916</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.091560860733663</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.623195440458985</v>
+        <v>3.562836630185549</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.90355484974538</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.231874664442795</v>
+        <v>-3.163781544273338</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.666860609941781</v>
+        <v>1.637685807722298</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.091560860733663</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.614903416472844</v>
+        <v>3.554544606199408</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.90174804532916</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.143996751333675</v>
+        <v>-3.075903631164218</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.700204970769209</v>
+        <v>1.671030168549726</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.207486503157014</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.682651997510634</v>
+        <v>3.622293187237198</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.919302451055951</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.135104289940392</v>
+        <v>-3.067011169770934</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.721316361053313</v>
+        <v>1.69214155883383</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.207486503157014</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.700206403237426</v>
+        <v>3.639847592963989</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.911157498460535</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.30358040691027</v>
+        <v>-3.235487286740812</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.645780961669946</v>
+        <v>1.616606159450463</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.179538667440433</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.675292749212062</v>
+        <v>3.614933938938625</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.892427195648397</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.85732421428083</v>
+        <v>-2.789231094111372</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.805553135909584</v>
+        <v>1.776378333690101</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.084819997770801</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.599731244598144</v>
+        <v>3.539372434324707</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.883091218145302</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.834603110597677</v>
+        <v>-2.76650999042822</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.805305599879749</v>
+        <v>1.776130797660267</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.084819997770801</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.590395267095048</v>
+        <v>3.530036456821612</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>3.041997343996471</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.96380492389172</v>
+        <v>-2.895711803722262</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.912531000413301</v>
+        <v>1.883356198193819</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9556181844767584</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.671780304969792</v>
+        <v>3.611421494696355</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.079075166490117</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.989679322365745</v>
+        <v>-2.921586202196288</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.939259063517338</v>
+        <v>1.910084261297855</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.0005297931885</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.735805092690483</v>
+        <v>3.675446282417046</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.075750522479662</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.982624632150572</v>
+        <v>-2.914531511981114</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.938756295592952</v>
+        <v>1.90958149337347</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.007584483403673</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.736713262809133</v>
+        <v>3.676354452535696</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.085756676124404</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.955673407824084</v>
+        <v>-2.887580287654626</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.959542938968289</v>
+        <v>1.930368136748807</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.022464829431392</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.755647624070506</v>
+        <v>3.695288813797069</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.269859808269364</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.977217635654871</v>
+        <v>-2.909124515485413</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.135028379980934</v>
+        <v>2.105853577761451</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.022464829431392</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.939750756215465</v>
+        <v>3.879391945942029</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.261976503172357</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.999625753459743</v>
+        <v>-2.931532633290285</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.118181827761978</v>
+        <v>2.089007025542496</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.022464829431392</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.931867451118459</v>
+        <v>3.871508640845022</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.264030502721994</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.027849989037343</v>
+        <v>-2.959756868867886</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.108946133080575</v>
+        <v>2.079771330861093</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.040441581882701</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.944707502138881</v>
+        <v>3.884348691865444</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.320284220443841</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.037290914925873</v>
+        <v>-2.969197794756416</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.161423480447011</v>
+        <v>2.132248678227528</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.162868699426093</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.074417490386763</v>
+        <v>4.014058680113326</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.323175314989142</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.089564522261515</v>
+        <v>-3.021471402092057</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.143405132058055</v>
+        <v>2.114230329838573</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.110595092090451</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.045944420530679</v>
+        <v>3.985585610257242</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.321287127882917</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.165894499862421</v>
+        <v>-3.097801379692963</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.110984953911468</v>
+        <v>2.081810151691985</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.110595092090451</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.044056233424454</v>
+        <v>3.983697423151018</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.31610735748578</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.259558444539962</v>
+        <v>-3.191465324370504</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.068339605643314</v>
+        <v>2.039164803423831</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.01693114741291</v>
+        <v>1.010353214102625</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.982678096220792</v>
+        <v>3.922319285947355</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.314541367695932</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.421126870067217</v>
+        <v>-3.353033749897759</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.002146245642564</v>
+        <v>1.972971443423081</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8901482236150305</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.905042352152217</v>
+        <v>3.84468354187878</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.327614774561851</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.529427531937336</v>
+        <v>-3.461334411767879</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.971899387760435</v>
+        <v>1.942724585540952</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8901482236150305</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.918115759018135</v>
+        <v>3.857756948744699</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.319619971344791</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.622575003240703</v>
+        <v>-3.554481883071245</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.926645596022028</v>
+        <v>1.897470793802545</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7673190123324978</v>
+        <v>0.7607410790222131</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.836423429031556</v>
+        <v>3.776064618758119</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.318144012471793</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.650475790350176</v>
+        <v>-3.582382670180718</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.914009322305241</v>
+        <v>1.884834520085758</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.732722088189563</v>
+        <v>0.7261441548792783</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.814189315672797</v>
+        <v>3.75383050539936</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.314908456448991</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.77300189305307</v>
+        <v>-3.704908772883612</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.861763325201282</v>
+        <v>1.832588522981799</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6101959854866691</v>
+        <v>0.6036180521763844</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.737438098028259</v>
+        <v>3.677079287754822</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.381614416039495</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.003516389238658</v>
+        <v>-3.935423269069201</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.83626348631755</v>
+        <v>1.807088684098068</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3796814893010804</v>
+        <v>0.3731035559907957</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.66583535990741</v>
+        <v>3.605476549633973</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.521926135041342</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.352261474463102</v>
+        <v>-4.284168354293644</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.83707717122962</v>
+        <v>1.807902369010137</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2709335353821826</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.740898306557918</v>
+        <v>3.680539496284481</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.590906404186982</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.506247892239243</v>
+        <v>-4.438154772069785</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.844462873264804</v>
+        <v>1.815288071045321</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2709335353821826</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.809878575703558</v>
+        <v>3.749519765430121</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.576957606307103</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.455725988411577</v>
+        <v>-4.387632868242119</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.850722836915991</v>
+        <v>1.821548034696508</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2709335353821826</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.795929777823678</v>
+        <v>3.735570967550242</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.588828095362517</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.708201142419301</v>
+        <v>-4.640108022249843</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.761603264368315</v>
+        <v>1.732428462148832</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2709335353821826</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.807800266879092</v>
+        <v>3.747441456605656</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.590038629881461</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.001096898898713</v>
+        <v>-4.933003778729256</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.645655496295494</v>
+        <v>1.616480694076011</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2709335353821826</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.809010801398036</v>
+        <v>3.748651991124599</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.594160372108782</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.187761027033521</v>
+        <v>-5.119667906864064</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.575111587268892</v>
+        <v>1.545936785049409</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2441945645576227</v>
+        <v>0.237616631247338</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.797089161130622</v>
+        <v>3.736730350857185</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.589238224844971</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.333781713947483</v>
+        <v>-5.265688593778026</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.511781165239497</v>
+        <v>1.482606363020014</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2351114727637657</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.786717158790497</v>
+        <v>3.72635834851706</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.751442281544016</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.425495723057068</v>
+        <v>-5.35740260288761</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.637299618294707</v>
+        <v>1.608124816075224</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2351114727637657</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.948921215489541</v>
+        <v>3.888562405216105</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.74628891950783</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.457147382117038</v>
+        <v>-5.38905426194758</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.619485592634533</v>
+        <v>1.59031079041505</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2299430155193255</v>
+        <v>0.2233650822090408</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.940666779106691</v>
+        <v>3.880307968833255</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.756518337076321</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.539082200385921</v>
+        <v>-5.470989080216463</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.596941082895471</v>
+        <v>1.567766280675988</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2200082699322453</v>
+        <v>0.2134303366219606</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.944935349322934</v>
+        <v>3.884576539049498</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.765443975532223</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.641058322634328</v>
+        <v>-5.572965202464871</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.565076272452011</v>
+        <v>1.535901470232528</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1180321476838377</v>
+        <v>0.1114542143735531</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.892675314429792</v>
+        <v>3.832316504156355</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.757596862776399</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.531052039157107</v>
+        <v>-5.462958918987649</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.601231673087074</v>
+        <v>1.572056870867592</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1412367196011129</v>
+        <v>0.1346587862908283</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.898750944824333</v>
+        <v>3.838392134550896</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.761846873498373</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.387992463416181</v>
+        <v>-5.319899343246723</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.662705514105419</v>
+        <v>1.633530711885936</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1492501461910922</v>
+        <v>0.1426722128808076</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.907809011500294</v>
+        <v>3.847450201226858</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.769107756380909</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.086545737944343</v>
+        <v>-5.018452617774885</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.79054508717669</v>
+        <v>1.761370284957207</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4506968716629295</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.095937929665933</v>
+        <v>4.035579119392496</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.77007893413362</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.111135982179527</v>
+        <v>-5.043042862010069</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.781680167235328</v>
+        <v>1.752505365015844</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4506968716629295</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.096909107418643</v>
+        <v>4.036550297145206</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.770921838513375</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.060097606173007</v>
+        <v>-4.992004486003549</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.802938422017691</v>
+        <v>1.773763619798208</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4506968716629295</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.097752011798399</v>
+        <v>4.037393201524962</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.789959937387521</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.018958311306376</v>
+        <v>-4.950865191136918</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.838432238838489</v>
+        <v>1.809257436619006</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4918361665295603</v>
+        <v>0.4852582332192756</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.141473687592523</v>
+        <v>4.081114877319086</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.606143933511455</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.922323399287736</v>
+        <v>-4.854230279118278</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.693270199769879</v>
+        <v>1.664095397550397</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5884710785482002</v>
+        <v>0.5818931452379156</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.015638630927642</v>
+        <v>3.955279820654205</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.609645977585419</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.052904133818578</v>
+        <v>-4.776446387981196</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.644539950031506</v>
+        <v>1.698710998079193</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4578903440173577</v>
+        <v>0.6596770363749975</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.9407922342831</v>
+        <v>4.005452199410418</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.594072796661502</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.888407799627617</v>
+        <v>-4.611950053790235</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.694765302783974</v>
+        <v>1.748936350831661</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6223866782083196</v>
+        <v>0.8241733705659594</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.02391685387376</v>
+        <v>4.088576819001077</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.593260507097932</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.915777732312049</v>
+        <v>-4.639319986474667</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.683005040146631</v>
+        <v>1.737176088194317</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6223866782083196</v>
+        <v>0.8241733705659594</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.02310456431019</v>
+        <v>4.087764529437507</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.603129286223004</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.926162927201938</v>
+        <v>-4.649705181364556</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.688719741315747</v>
+        <v>1.742890789363434</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6120014833184303</v>
+        <v>0.8137881756760701</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.026742226501328</v>
+        <v>4.091402191628646</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.673966291999429</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.944751085924163</v>
+        <v>-4.668293340086781</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.752121483603283</v>
+        <v>1.806292531650969</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.593413324596205</v>
+        <v>0.7952000169538447</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.086426337044418</v>
+        <v>4.151086302171736</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.670835302817728</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.945049632620199</v>
+        <v>-4.668591886782817</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.748871075743167</v>
+        <v>1.803042123790854</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5931147779001691</v>
+        <v>0.7949014702578088</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.083116219845095</v>
+        <v>4.147776184972413</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.675366197757119</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.844226498929771</v>
+        <v>-4.567768753092389</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.793731224158729</v>
+        <v>1.847902272206416</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6055789933845229</v>
+        <v>0.8073656857421626</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.095125644075098</v>
+        <v>4.159785609202417</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.675495451235662</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.653445138177364</v>
+        <v>-4.376987392339982</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.870173021938235</v>
+        <v>1.924344069985922</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7963603541369303</v>
+        <v>0.9981470464945699</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.209723714005086</v>
+        <v>4.274383679132405</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.655332296973259</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.546481780327943</v>
+        <v>-4.270024034490561</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.8927952108156</v>
+        <v>1.946966258863287</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8548249620967318</v>
+        <v>1.056611654454371</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.224639324518564</v>
+        <v>4.289299289645882</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.690299233585317</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.49115119242618</v>
+        <v>-4.214693446588798</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.949894382588364</v>
+        <v>2.004065430636051</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9101555499984939</v>
+        <v>1.111942242356133</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.29280461387168</v>
+        <v>4.357464578998997</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.683985801486755</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.479097065513217</v>
+        <v>-4.202639319675836</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.948402601254987</v>
+        <v>2.002573649302674</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9222096769114567</v>
+        <v>1.123996369269096</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.293723657920895</v>
+        <v>4.358383623048213</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.685866431670891</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.520252185081438</v>
+        <v>-4.243794439244057</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.933821183611834</v>
+        <v>1.987992231659521</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8810545573432358</v>
+        <v>1.082841249700875</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.270911216364098</v>
+        <v>4.335571181491416</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.698717457548773</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.452203622389908</v>
+        <v>-4.175745876552527</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.973891634566328</v>
+        <v>2.028062682614015</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9491031200347656</v>
+        <v>1.150889812392405</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.324591379856899</v>
+        <v>4.389251344984217</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.718920127722368</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.683804015559409</v>
+        <v>-4.407346269722027</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.901454147472122</v>
+        <v>1.95562519551981</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9491031200347656</v>
+        <v>1.150889812392405</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.344794050030493</v>
+        <v>4.409454015157811</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.775332178009633</v>
+        <v>3.718920127722368</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.701876523851021</v>
+        <v>-4.425418778013639</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.894225144155478</v>
+        <v>1.948396192203165</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9491031200347656</v>
+        <v>1.150889812392405</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.344794050030493</v>
+        <v>4.409454015157811</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.7355840916031</v>
+        <v>3.679172041315834</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.876983356427466</v>
+        <v>-4.600525610590084</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.784434324718366</v>
+        <v>1.838605372766053</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9491031200347656</v>
+        <v>1.150889812392405</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.30504596362396</v>
+        <v>4.369705928751277</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.74260671060004</v>
+        <v>3.686194660312774</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.845697335887011</v>
+        <v>-4.569239590049629</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.803971351931488</v>
+        <v>1.858142399979175</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.980389140575221</v>
+        <v>1.18217583293286</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.330840194945173</v>
+        <v>4.395500160072491</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.841777710172944</v>
+        <v>3.785365659885679</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.692671943773727</v>
+        <v>-4.416214197936345</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.964352508349707</v>
+        <v>2.018523556397394</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.133414532688505</v>
+        <v>1.335201225046144</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.521826429786048</v>
+        <v>4.586486394913366</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073882</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.029243935081237</v>
+        <v>3.972831884793971</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.720979257646997</v>
+        <v>-4.444521511809615</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.140495807708691</v>
+        <v>2.194666855756378</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.133414532688505</v>
+        <v>1.335201225046144</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.70929265469434</v>
+        <v>4.773952619821658</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.998646886435319</v>
+        <v>3.942234836148053</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.887572482760519</v>
+        <v>-4.611114736923137</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.043261469017364</v>
+        <v>2.097432517065051</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9668213075749825</v>
+        <v>1.168607999932622</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.578739670980308</v>
+        <v>4.643399636107627</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.002323289097037</v>
+        <v>3.945911238809771</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.864536689398953</v>
+        <v>-4.588078943561571</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.056152189023708</v>
+        <v>2.110323237071395</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9668213075749825</v>
+        <v>1.168607999932622</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.582416073642026</v>
+        <v>4.647076038769344</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.999941344220532</v>
+        <v>3.943529293933266</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.835290708943257</v>
+        <v>-4.558832963105875</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.065468636329482</v>
+        <v>2.119639684377169</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9668213075749825</v>
+        <v>1.168607999932622</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.580034128765521</v>
+        <v>4.64469409389284</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539106</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.997234583378167</v>
+        <v>3.940822533090901</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.942216256821108</v>
+        <v>-4.665758510983726</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.019991656335977</v>
+        <v>2.074162704383664</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8598957596971312</v>
+        <v>1.061682452054771</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.513172039196446</v>
+        <v>4.577832004323763</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.998663385521401</v>
+        <v>3.942251335234135</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.087234815328356</v>
+        <v>-4.810777069490975</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.963413035076311</v>
+        <v>2.017584083123998</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7148772011898826</v>
+        <v>0.9166638935475222</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.427589706235331</v>
+        <v>4.492249671362649</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969748</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.098594624779154</v>
+        <v>4.042182574491888</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.071559387531087</v>
+        <v>-4.929118835275692</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.069614445452972</v>
+        <v>2.070178616067864</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7749876643537973</v>
+        <v>0.9273499321104123</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.563587223391433</v>
+        <v>4.598592533758135</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073538</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.096380321905093</v>
+        <v>4.039968271617827</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.122969809851795</v>
+        <v>-4.9805292575964</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.046835973650627</v>
+        <v>2.04740014426552</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7749876643537973</v>
+        <v>0.9273499321104123</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.561372920517371</v>
+        <v>4.596378230884074</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.096283449979382</v>
+        <v>4.039871399692117</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.202389261059547</v>
+        <v>-5.059948708804152</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.014971321241816</v>
+        <v>2.015535491856709</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7749876643537973</v>
+        <v>0.9273499321104123</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.561276048591661</v>
+        <v>4.596281358958364</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.096277343537426</v>
+        <v>4.03986529325016</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.297852258976764</v>
+        <v>-5.155411706721369</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.976780015632973</v>
+        <v>1.977344186247865</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7749876643537973</v>
+        <v>0.9273499321104123</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.561269942149704</v>
+        <v>4.596275252516407</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.094373740100036</v>
+        <v>4.037961689812771</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.337872257020548</v>
+        <v>-5.195431704765153</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.95886841297807</v>
+        <v>1.959432583592962</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7349676663100135</v>
+        <v>0.8873299340666285</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.535354339886045</v>
+        <v>4.570359650252747</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.100107557847763</v>
+        <v>4.043695507560497</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.393241419152742</v>
+        <v>-5.250800866897347</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.942454565872919</v>
+        <v>1.943018736487811</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7349676663100135</v>
+        <v>0.8873299340666285</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.541088157633771</v>
+        <v>4.576093468000474</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.099645921190696</v>
+        <v>4.04323387090343</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.438679198983569</v>
+        <v>-5.296238646728174</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.923817817283521</v>
+        <v>1.924381987898413</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6921226756318539</v>
+        <v>0.8444849433884689</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.514919526569809</v>
+        <v>4.549924836936512</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.119520314041015</v>
+        <v>4.063108263753749</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.350472364835991</v>
+        <v>-5.208031812580596</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.978974943792871</v>
+        <v>1.979539114407764</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6921226756318539</v>
+        <v>0.8444849433884689</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.534793919420128</v>
+        <v>4.569799229786831</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.103221014565743</v>
+        <v>4.046808964278477</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.174182140230683</v>
+        <v>-5.031741587975288</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.033191734159722</v>
+        <v>2.033755904774615</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6921226756318539</v>
+        <v>0.8444849433884689</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.518494619944855</v>
+        <v>4.553499930311559</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.105651964029788</v>
+        <v>4.049239913742523</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.990970477097588</v>
+        <v>-4.848529924842193</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.108907348877006</v>
+        <v>2.109471519491898</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6921226756318539</v>
+        <v>0.8444849433884689</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.520925569408901</v>
+        <v>4.555930879775604</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.071443149877678</v>
+        <v>4.015031099590412</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.919249030083737</v>
+        <v>-4.776808477828342</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.103387113530435</v>
+        <v>2.103951284145328</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7638441226457046</v>
+        <v>0.9162063904023195</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.529749623465101</v>
+        <v>4.564754933831804</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.018358895798849</v>
+        <v>3.961946845511584</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.896876004476031</v>
+        <v>-4.754435452220636</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.05925206969469</v>
+        <v>2.059816240309582</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7750998737586061</v>
+        <v>0.9274621415152211</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.483418820054013</v>
+        <v>4.518424130420716</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739466</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.203557100684205</v>
+        <v>4.147145050396939</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.929892300386776</v>
+        <v>-4.787451748131381</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.231243756215747</v>
+        <v>2.23180792683064</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7056624970918546</v>
+        <v>0.8580247648484696</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.626954598939318</v>
+        <v>4.661959909306021</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166411</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.195478326512454</v>
+        <v>4.139066276225188</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.918364664737167</v>
+        <v>-4.775924112481772</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.22777603630384</v>
+        <v>2.228340206918732</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.764663155293217</v>
+        <v>0.917025423049832</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.654276219688384</v>
+        <v>4.689281530055087</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.199146439034243</v>
+        <v>4.142734388746977</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.015706166079536</v>
+        <v>-4.873265613824141</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.192507548288681</v>
+        <v>2.193071718903573</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7202429731277287</v>
+        <v>0.8726052408843437</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.63129222291088</v>
+        <v>4.666297533277583</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710419</v>
+        <v>3.705221264710418</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.200397521227081</v>
+        <v>4.143985470939815</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.101562195419502</v>
+        <v>-4.959121643164107</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.159416218745533</v>
+        <v>2.159980389360425</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6778669039015937</v>
+        <v>0.8302291716582086</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.607117663568038</v>
+        <v>4.64212297393474</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893115</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.182816723047583</v>
+        <v>4.126404672760317</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.084753271020231</v>
+        <v>-4.942312718764836</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.148558990325743</v>
+        <v>2.149123160940635</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7019329995899738</v>
+        <v>0.8542952673465888</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.603976522801567</v>
+        <v>4.638981833168271</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950187</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.192981234092632</v>
+        <v>4.136569183805366</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.17613583358569</v>
+        <v>-5.033695281330295</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.122170476344609</v>
+        <v>2.122734646959501</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6105504370245156</v>
+        <v>0.7629127047811306</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.559311496307342</v>
+        <v>4.594316806674045</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.885329953651988</v>
+        <v>3.714277188515212</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.395562195069364</v>
+        <v>4.260157569812528</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.17613583358569</v>
+        <v>-5.033695281330295</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.122170476344609</v>
+        <v>2.122734646959501</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6105504370245156</v>
+        <v>0.7629127047811306</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.388625992055732</v>
+        <v>4.253221366798896</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>108.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.9%</t>
+          <t>-688.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.9%</t>
+          <t>-167.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.5%</t>
+          <t>590.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-305.3%</t>
+          <t>-307.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-147.7%</t>
+          <t>-174.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.616727494248718</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.879788496525296</v>
+        <v>0.9362005468125618</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.826281993604849</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.683063048045539</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9710432498325656</v>
+        <v>1.027455300119831</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.919794105966335</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.485355049759666</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.854051330612756</v>
+        <v>0.9104633809000218</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.840897022981955</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.555645282081842</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9039868778604534</v>
+        <v>0.9603989281477192</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.880655227692413</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.570273018197885</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9532589110364196</v>
+        <v>1.009670961323685</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.942458402531552</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.568808999022557</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9277111726589773</v>
+        <v>0.9841232229462431</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.904868804553053</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.567300617062485</v>
+        <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.04052132760904</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9507356617051221</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.903360422592981</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.567163484497922</v>
+        <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.996148195970472</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9683477817959858</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.929847169011559</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.561557278636512</v>
+        <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.018628546829357</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9537494355910223</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.924240963150149</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.567939035664317</v>
+        <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.970972816268301</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9791934848432493</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.959216158514587</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.572831409039042</v>
+        <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.870454657769546</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.024293121617476</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.024419426988565</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.559586081514914</v>
+        <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.854549328337193</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.017409925866289</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.963706503038894</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.563683784125542</v>
+        <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.809710926728795</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.039442989120277</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.970530265416444</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.56784472375662</v>
+        <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.829209382970804</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.035804546254552</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.94584042027958</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.573724326284458</v>
+        <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.785006545884903</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.059365283616749</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.978241725058957</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.572134326753705</v>
+        <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.79256621172195</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.054751417751178</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.009533767934096</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.623382091936745</v>
+        <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.634274794182678</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.169315749949926</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.060781533117136</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.621822796530998</v>
+        <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.426632790548202</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.25081325599797</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.183807439892075</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.616771024769268</v>
+        <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.375600697825674</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.266174321325251</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.209374923763861</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.633958428861973</v>
+        <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.310376516698468</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.309451397868838</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.265696836532889</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.629919401161253</v>
+        <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.272949496627334</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.320383178196572</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.264808731649679</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.631176193492494</v>
+        <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.293061152662042</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.313595308113929</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.27268193097937</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.791733964513704</v>
+        <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.264647889562159</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.485518384375093</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.397854364352724</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.911846873731522</v>
+        <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.189865628537146</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.635544198002916</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.562836630185549</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.90355484974538</v>
+        <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.163781544273338</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.637685807722298</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.554544606199408</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.90174804532916</v>
+        <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.075903631164218</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.671030168549726</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.622293187237198</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.919302451055951</v>
+        <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.067011169770934</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.69214155883383</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.639847592963989</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.911157498460535</v>
+        <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.235487286740812</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.616606159450463</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.614933938938625</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.892427195648397</v>
+        <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.789231094111372</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.776378333690101</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.539372434324707</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.883091218145302</v>
+        <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.76650999042822</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.776130797660267</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.530036456821612</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.041997343996471</v>
+        <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.895711803722262</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.883356198193819</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.611421494696355</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.079075166490117</v>
+        <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.921586202196288</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.910084261297855</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.675446282417046</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.075750522479662</v>
+        <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.914531511981114</v>
+        <v>-2.95189432830046</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.90958149337347</v>
+        <v>1.951048417132997</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9757892626052311</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.676354452535696</v>
+        <v>3.717636130330067</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.085756676124404</v>
+        <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.887580287654626</v>
+        <v>-2.924943103973972</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.930368136748807</v>
+        <v>1.971835060508334</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9906696086329503</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.695288813797069</v>
+        <v>3.73657049159144</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.269859808269364</v>
+        <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.909124515485413</v>
+        <v>-2.94648733180476</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.105853577761451</v>
+        <v>2.147320501520978</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9906696086329503</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.879391945942029</v>
+        <v>3.9206736237364</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.261976503172357</v>
+        <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.931532633290285</v>
+        <v>-2.968895449609632</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.089007025542496</v>
+        <v>2.130473949302023</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9906696086329503</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.871508640845022</v>
+        <v>3.912790318639393</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.264030502721994</v>
+        <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.959756868867886</v>
+        <v>-2.997119685187232</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.079771330861093</v>
+        <v>2.12123825462062</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.008646361084259</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.884348691865444</v>
+        <v>3.925630369659816</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.320284220443841</v>
+        <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.969197794756416</v>
+        <v>-3.006560611075762</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.132248678227528</v>
+        <v>2.173715601987055</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.13107347862765</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.014058680113326</v>
+        <v>4.055340357907697</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.323175314989142</v>
+        <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.021471402092057</v>
+        <v>-3.058834218411403</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.114230329838573</v>
+        <v>2.1556972535981</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.078799871292009</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.985585610257242</v>
+        <v>4.026867288051614</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.321287127882917</v>
+        <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.097801379692963</v>
+        <v>-3.135164196012309</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.081810151691985</v>
+        <v>2.123277075451512</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.078799871292009</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.983697423151018</v>
+        <v>4.024979100945389</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.31610735748578</v>
+        <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.191465324370504</v>
+        <v>-3.22882814068985</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.039164803423831</v>
+        <v>2.080631727183358</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.010353214102625</v>
+        <v>0.9851359266144674</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.922319285947355</v>
+        <v>3.963600963741726</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.314541367695932</v>
+        <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.353033749897759</v>
+        <v>-3.390396566217106</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.972971443423081</v>
+        <v>2.014438367182608</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.858353002816588</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.84468354187878</v>
+        <v>3.885965219673151</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.327614774561851</v>
+        <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.461334411767879</v>
+        <v>-3.498697228087225</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.942724585540952</v>
+        <v>1.984191509300479</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.858353002816588</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.857756948744699</v>
+        <v>3.89903862653907</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.319619971344791</v>
+        <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.554481883071245</v>
+        <v>-3.591844699390592</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.897470793802545</v>
+        <v>1.938937717562073</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.7355237915340552</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.776064618758119</v>
+        <v>3.81734629655249</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.318144012471793</v>
+        <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.582382670180718</v>
+        <v>-3.619745486500065</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.884834520085758</v>
+        <v>1.926301443845285</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.7009268673911204</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.75383050539936</v>
+        <v>3.795112183193731</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.314908456448991</v>
+        <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.704908772883612</v>
+        <v>-3.742271589202959</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.832588522981799</v>
+        <v>1.874055446741327</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.5784007646882265</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.677079287754822</v>
+        <v>3.718360965549194</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.381614416039495</v>
+        <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.935423269069201</v>
+        <v>-3.972786085388547</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.807088684098068</v>
+        <v>1.848555607857595</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.3478862685026378</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.605476549633973</v>
+        <v>3.646758227428344</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.521926135041342</v>
+        <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.284168354293644</v>
+        <v>-4.321531170612991</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.807902369010137</v>
+        <v>1.849369292769665</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.23913831458374</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.680539496284481</v>
+        <v>3.721821174078852</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.590906404186982</v>
+        <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.438154772069785</v>
+        <v>-4.475517588389131</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.815288071045321</v>
+        <v>1.856754994804848</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.23913831458374</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.749519765430121</v>
+        <v>3.790801443224492</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.576957606307103</v>
+        <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.387632868242119</v>
+        <v>-4.424995684561465</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.821548034696508</v>
+        <v>1.863014958456035</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.23913831458374</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.735570967550242</v>
+        <v>3.776852645344613</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.588828095362517</v>
+        <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.640108022249843</v>
+        <v>-4.67747083856919</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.732428462148832</v>
+        <v>1.773895385908359</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.23913831458374</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.747441456605656</v>
+        <v>3.788723134400027</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.590038629881461</v>
+        <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.933003778729256</v>
+        <v>-4.970366595048602</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.616480694076011</v>
+        <v>1.657947617835538</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.23913831458374</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.748651991124599</v>
+        <v>3.789933668918971</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.594160372108782</v>
+        <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.119667906864064</v>
+        <v>-5.15703072318341</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.545936785049409</v>
+        <v>1.587403708808937</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.2123993437591801</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.736730350857185</v>
+        <v>3.778012028651556</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.589238224844971</v>
+        <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.265688593778026</v>
+        <v>-5.303051410097372</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.482606363020014</v>
+        <v>1.524073286779541</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.2033162519653232</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.72635834851706</v>
+        <v>3.767640026311431</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.751442281544016</v>
+        <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.35740260288761</v>
+        <v>-5.394765419206957</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.608124816075224</v>
+        <v>1.649591739834751</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.2033162519653232</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.888562405216105</v>
+        <v>3.929844083010476</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.74628891950783</v>
+        <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.38905426194758</v>
+        <v>-5.426417078266926</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.59031079041505</v>
+        <v>1.631777714174578</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.198147794720883</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.880307968833255</v>
+        <v>3.921589646627625</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.756518337076321</v>
+        <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.470989080216463</v>
+        <v>-5.508351896535809</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.567766280675988</v>
+        <v>1.609233204435516</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.1882130491338028</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.884576539049498</v>
+        <v>3.925858216843869</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.765443975532223</v>
+        <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.572965202464871</v>
+        <v>-5.610328018784217</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.535901470232528</v>
+        <v>1.577368393992055</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>0.08623692688539519</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.832316504156355</v>
+        <v>3.873598181950726</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.757596862776399</v>
+        <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.462958918987649</v>
+        <v>-5.500321735306995</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.572056870867592</v>
+        <v>1.613523794627119</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.1094414988026704</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.838392134550896</v>
+        <v>3.879673812345267</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.761846873498373</v>
+        <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.319899343246723</v>
+        <v>-5.357262159566069</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.633530711885936</v>
+        <v>1.674997635645464</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.1174549253926497</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.847450201226858</v>
+        <v>3.888731879021229</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.769107756380909</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.018452617774885</v>
+        <v>-5.055815434094232</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.761370284957207</v>
+        <v>1.802837208716735</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4189016508644869</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.035579119392496</v>
+        <v>4.076860797186868</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.77007893413362</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.043042862010069</v>
+        <v>-5.080405678329416</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.752505365015844</v>
+        <v>1.793972288775372</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4189016508644869</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.036550297145206</v>
+        <v>4.077831974939578</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.770921838513375</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.992004486003549</v>
+        <v>-5.029367302322895</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.773763619798208</v>
+        <v>1.815230543557735</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4189016508644869</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.037393201524962</v>
+        <v>4.078674879319333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.789959937387521</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.950865191136918</v>
+        <v>-4.988228007456264</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.809257436619006</v>
+        <v>1.850724360378533</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.4600409457311178</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.081114877319086</v>
+        <v>4.122396555113458</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.606143933511455</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.854230279118278</v>
+        <v>-4.891593095437624</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.664095397550397</v>
+        <v>1.705562321309924</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.5566758577497577</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.955279820654205</v>
+        <v>3.996561498448576</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.609645977585419</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.776446387981196</v>
+        <v>-5.022173829968467</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.698710998079193</v>
+        <v>1.656832071571551</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6596770363749975</v>
+        <v>0.4260951232189152</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.005452199410418</v>
+        <v>3.921715101804034</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.594072796661502</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.611950053790235</v>
+        <v>-4.857677495777505</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.748936350831661</v>
+        <v>1.707057424324018</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8241733705659594</v>
+        <v>0.5905914574098771</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.088576819001077</v>
+        <v>4.004839721394694</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.593260507097932</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.639319986474667</v>
+        <v>-4.885047428461937</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.737176088194317</v>
+        <v>1.695297161686675</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8241733705659594</v>
+        <v>0.5905914574098771</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.087764529437507</v>
+        <v>4.004027431831124</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.603129286223004</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.649705181364556</v>
+        <v>-4.895432623351827</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.742890789363434</v>
+        <v>1.701011862855792</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8137881756760701</v>
+        <v>0.5802062625199877</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.091402191628646</v>
+        <v>4.007665094022263</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.673966291999429</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.668293340086781</v>
+        <v>-4.914020782074052</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.806292531650969</v>
+        <v>1.764413605143327</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7952000169538447</v>
+        <v>0.5616181037977623</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.151086302171736</v>
+        <v>4.067349204565352</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.670835302817728</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.668591886782817</v>
+        <v>-4.914319328770087</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.803042123790854</v>
+        <v>1.761163197283211</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7949014702578088</v>
+        <v>0.5613195571017264</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.147776184972413</v>
+        <v>4.064039087366029</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.675366197757119</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.567768753092389</v>
+        <v>-4.81349619507966</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.847902272206416</v>
+        <v>1.806023345698774</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8073656857421626</v>
+        <v>0.5737837725860803</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.159785609202417</v>
+        <v>4.076048511596033</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.675495451235662</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.376987392339982</v>
+        <v>-4.622714834327253</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.924344069985922</v>
+        <v>1.88246514347828</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9981470464945699</v>
+        <v>0.7645651333384876</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.274383679132405</v>
+        <v>4.190646581526021</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.655332296973259</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.270024034490561</v>
+        <v>-4.515751476477831</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.946966258863287</v>
+        <v>1.905087332355645</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.056611654454371</v>
+        <v>0.8230297412982891</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.289299289645882</v>
+        <v>4.205562192039499</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.690299233585317</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.214693446588798</v>
+        <v>-4.460420888576069</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.004065430636051</v>
+        <v>1.962186504128408</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.111942242356133</v>
+        <v>0.8783603292000512</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.357464578998997</v>
+        <v>4.273727481392614</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.683985801486755</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.202639319675836</v>
+        <v>-4.448366761663106</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.002573649302674</v>
+        <v>1.960694722795031</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.123996369269096</v>
+        <v>0.8904144561130141</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.358383623048213</v>
+        <v>4.274646525441829</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.685866431670891</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.243794439244057</v>
+        <v>-4.489521881231327</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.987992231659521</v>
+        <v>1.946113305151878</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.082841249700875</v>
+        <v>0.8492593365447931</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.335571181491416</v>
+        <v>4.251834083885033</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.698717457548773</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.175745876552527</v>
+        <v>-4.421473318539797</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.028062682614015</v>
+        <v>1.986183756106373</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.150889812392405</v>
+        <v>0.9173078992363229</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.389251344984217</v>
+        <v>4.305514247377833</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.718920127722368</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.407346269722027</v>
+        <v>-4.653073711709298</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.95562519551981</v>
+        <v>1.913746269012167</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.150889812392405</v>
+        <v>0.9173078992363229</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.409454015157811</v>
+        <v>4.325716917551428</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.718920127722368</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.425418778013639</v>
+        <v>-4.671146220000909</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.948396192203165</v>
+        <v>1.906517265695522</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.150889812392405</v>
+        <v>0.9173078992363229</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.409454015157811</v>
+        <v>4.325716917551428</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.679172041315834</v>
+        <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.600525610590084</v>
+        <v>-4.846253052577355</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.838605372766053</v>
+        <v>1.796726446258411</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.150889812392405</v>
+        <v>0.9173078992363229</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.369705928751277</v>
+        <v>4.285968831144894</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.686194660312774</v>
+        <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.569239590049629</v>
+        <v>-4.8149670320369</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.858142399979175</v>
+        <v>1.816263473471533</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.18217583293286</v>
+        <v>0.9485939197767783</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.395500160072491</v>
+        <v>4.311763062466107</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.785365659885679</v>
+        <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.416214197936345</v>
+        <v>-4.661941639923615</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.018523556397394</v>
+        <v>1.976644629889751</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.335201225046144</v>
+        <v>1.101619311890063</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.586486394913366</v>
+        <v>4.502749297306982</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073882</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.972831884793971</v>
+        <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.444521511809615</v>
+        <v>-4.690248953796885</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.194666855756378</v>
+        <v>2.152787929248735</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.335201225046144</v>
+        <v>1.101619311890063</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.773952619821658</v>
+        <v>4.690215522215274</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.942234836148053</v>
+        <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.611114736923137</v>
+        <v>-4.856842178910408</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.097432517065051</v>
+        <v>2.055553590557408</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.168607999932622</v>
+        <v>0.9350260867765401</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.643399636107627</v>
+        <v>4.559662538501243</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.945911238809771</v>
+        <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.588078943561571</v>
+        <v>-4.833806385548842</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.110323237071395</v>
+        <v>2.068444310563753</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.168607999932622</v>
+        <v>0.9350260867765401</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.647076038769344</v>
+        <v>4.563338941162961</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.943529293933266</v>
+        <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.558832963105875</v>
+        <v>-4.804560405093145</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.119639684377169</v>
+        <v>2.077760757869527</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.168607999932622</v>
+        <v>0.9350260867765401</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.64469409389284</v>
+        <v>4.560956996286456</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539106</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.940822533090901</v>
+        <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.665758510983726</v>
+        <v>-4.911485952970996</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.074162704383664</v>
+        <v>2.032283777876021</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.061682452054771</v>
+        <v>0.8281005388986887</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.577832004323763</v>
+        <v>4.494094906717381</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.942251335234135</v>
+        <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.810777069490975</v>
+        <v>-5.056504511478245</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.017584083123998</v>
+        <v>1.975705156616356</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9166638935475222</v>
+        <v>0.6830819803914402</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.492249671362649</v>
+        <v>4.408512573756266</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969748</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.042182574491888</v>
+        <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.929118835275692</v>
+        <v>-5.174846277262962</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.070178616067864</v>
+        <v>2.028299689560222</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9273499321104123</v>
+        <v>0.6937680189543303</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.598592533758135</v>
+        <v>4.514855436151753</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714899237073538</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.039968271617827</v>
+        <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.9805292575964</v>
+        <v>-5.22625669958367</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.04740014426552</v>
+        <v>2.005521217757877</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9273499321104123</v>
+        <v>0.6937680189543303</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.596378230884074</v>
+        <v>4.512641133277691</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.039871399692117</v>
+        <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.059948708804152</v>
+        <v>-5.305676150791422</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.015535491856709</v>
+        <v>1.973656565349066</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9273499321104123</v>
+        <v>0.6937680189543303</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.596281358958364</v>
+        <v>4.512544261351981</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.03986529325016</v>
+        <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.155411706721369</v>
+        <v>-5.40113914870864</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.977344186247865</v>
+        <v>1.935465259740222</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9273499321104123</v>
+        <v>0.6937680189543303</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.596275252516407</v>
+        <v>4.512538154910025</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.037961689812771</v>
+        <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.195431704765153</v>
+        <v>-5.441159146752423</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.959432583592962</v>
+        <v>1.91755365708532</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.8873299340666285</v>
+        <v>0.6537480209105464</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.570359650252747</v>
+        <v>4.486622552646365</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.043695507560497</v>
+        <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.250800866897347</v>
+        <v>-5.496528308884617</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.943018736487811</v>
+        <v>1.901139809980169</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.8873299340666285</v>
+        <v>0.6537480209105464</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.576093468000474</v>
+        <v>4.492356370394091</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.04323387090343</v>
+        <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.296238646728174</v>
+        <v>-5.541966088715444</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.924381987898413</v>
+        <v>1.882503061390771</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8444849433884689</v>
+        <v>0.6109030302323868</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.549924836936512</v>
+        <v>4.466187739330128</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.063108263753749</v>
+        <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.208031812580596</v>
+        <v>-5.453759254567866</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.979539114407764</v>
+        <v>1.937660187900121</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8444849433884689</v>
+        <v>0.6109030302323868</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.569799229786831</v>
+        <v>4.486062132180447</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.046808964278477</v>
+        <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.031741587975288</v>
+        <v>-5.277469029962559</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.033755904774615</v>
+        <v>1.991876978266972</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8444849433884689</v>
+        <v>0.6109030302323868</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.553499930311559</v>
+        <v>4.469762832705175</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.049239913742523</v>
+        <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.848529924842193</v>
+        <v>-5.094257366829464</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.109471519491898</v>
+        <v>2.067592592984256</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8444849433884689</v>
+        <v>0.6109030302323868</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.555930879775604</v>
+        <v>4.472193782169221</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.015031099590412</v>
+        <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.776808477828342</v>
+        <v>-5.022535919815613</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.103951284145328</v>
+        <v>2.062072357637685</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9162063904023195</v>
+        <v>0.6826244772462374</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.564754933831804</v>
+        <v>4.48101783622542</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.961946845511584</v>
+        <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.754435452220636</v>
+        <v>-5.000162894207906</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.059816240309582</v>
+        <v>2.01793731380194</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9274621415152211</v>
+        <v>0.693880228359139</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.518424130420716</v>
+        <v>4.434687032814333</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.147145050396939</v>
+        <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.787451748131381</v>
+        <v>-5.033179190118651</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.23180792683064</v>
+        <v>2.189929000322997</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8580247648484696</v>
+        <v>0.6244428516923874</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.661959909306021</v>
+        <v>4.578222811699638</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166411</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.139066276225188</v>
+        <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.775924112481772</v>
+        <v>-5.038565966369447</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.228340206918732</v>
+        <v>2.179695515650928</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.917025423049832</v>
+        <v>0.6172284980004504</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.689281530055087</v>
+        <v>4.565815425312724</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.142734388746977</v>
+        <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.873265613824141</v>
+        <v>-5.135907467711815</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.193071718903573</v>
+        <v>2.144427027635769</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8726052408843437</v>
+        <v>0.5728083158349621</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.666297533277583</v>
+        <v>4.54283142853522</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710418</v>
+        <v>3.705221264710419</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.143985470939815</v>
+        <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.959121643164107</v>
+        <v>-5.221763497051782</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.159980389360425</v>
+        <v>2.111335698092621</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8302291716582086</v>
+        <v>0.530432246608827</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.64212297393474</v>
+        <v>4.518656869192378</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893115</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.126404672760317</v>
+        <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.942312718764836</v>
+        <v>-5.204954572652511</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.149123160940635</v>
+        <v>2.100478469672831</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8542952673465888</v>
+        <v>0.5544983422972072</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.638981833168271</v>
+        <v>4.515515728425907</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.715564596950191</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.136569183805366</v>
+        <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.033695281330295</v>
+        <v>-5.29633713521797</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.122734646959501</v>
+        <v>2.074089955691697</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7629127047811306</v>
+        <v>0.4631157797317489</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.594316806674045</v>
+        <v>4.470850701931681</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.714277188515212</v>
+        <v>3.71713807735147</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.260157569812528</v>
+        <v>4.1970084398496</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.033695281330295</v>
+        <v>-5.271998967103341</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.122734646959501</v>
+        <v>2.087852428694516</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7629127047811306</v>
+        <v>0.4981414298290425</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.253221366798896</v>
+        <v>4.495893297747026</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240903.xlsx
+++ b/tame_output/ON/bt/strategyON_20240903.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.8%</t>
+          <t>-689.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.4%</t>
+          <t>-167.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.1%</t>
+          <t>588.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.9%</t>
+          <t>-307.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.2%</t>
+          <t>-170.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.95189432830046</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.951048417132997</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9757892626052311</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.717636130330067</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.924943103973972</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.971835060508334</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9906696086329503</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.73657049159144</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.94648733180476</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.147320501520978</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9906696086329503</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.9206736237364</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.968895449609632</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.130473949302023</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9906696086329503</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.912790318639393</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.997119685187232</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.12123825462062</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.008646361084259</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.925630369659816</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.006560611075762</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.173715601987055</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.13107347862765</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.055340357907697</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.058834218411403</v>
+        <v>-3.070219954756078</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.1556972535981</v>
+        <v>2.15114295906023</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.078799871292009</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.026867288051614</v>
+        <v>4.020035846244808</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.135164196012309</v>
+        <v>-3.146549932356984</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.123277075451512</v>
+        <v>2.118722780913642</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.078799871292009</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.024979100945389</v>
+        <v>4.018147659138584</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.22882814068985</v>
+        <v>-3.240213877034526</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.080631727183358</v>
+        <v>2.076077432645488</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9851359266144674</v>
+        <v>0.9737501902697926</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.963600963741726</v>
+        <v>3.956769521934921</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.390396566217106</v>
+        <v>-3.401782302561781</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.014438367182608</v>
+        <v>2.009884072644738</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.858353002816588</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.885965219673151</v>
+        <v>3.879133777866346</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.498697228087225</v>
+        <v>-3.5100829644319</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.984191509300479</v>
+        <v>1.979637214762609</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.858353002816588</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.89903862653907</v>
+        <v>3.892207184732265</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591844699390592</v>
+        <v>-3.603230435735267</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.938937717562073</v>
+        <v>1.934383423024203</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7355237915340552</v>
+        <v>0.7241380551893805</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.81734629655249</v>
+        <v>3.810514854745685</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619745486500065</v>
+        <v>-3.63113122284474</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.926301443845285</v>
+        <v>1.921747149307415</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7009268673911204</v>
+        <v>0.6895411310464457</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.795112183193731</v>
+        <v>3.788280741386926</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.742271589202959</v>
+        <v>-3.753657325547634</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.874055446741327</v>
+        <v>1.869501152203457</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5784007646882265</v>
+        <v>0.5670150283435518</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.718360965549194</v>
+        <v>3.711529523742389</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972786085388547</v>
+        <v>-3.984171821733223</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.848555607857595</v>
+        <v>1.844001313319725</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3478862685026378</v>
+        <v>0.3365005321579631</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.646758227428344</v>
+        <v>3.639926785621539</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.321531170612991</v>
+        <v>-4.332916906957666</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.849369292769665</v>
+        <v>1.844814998231794</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.23913831458374</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.721821174078852</v>
+        <v>3.714989732272048</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.475517588389131</v>
+        <v>-4.486903324733807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.856754994804848</v>
+        <v>1.852200700266978</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.23913831458374</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.790801443224492</v>
+        <v>3.783970001417687</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.424995684561465</v>
+        <v>-4.436381420906141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.863014958456035</v>
+        <v>1.858460663918165</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.23913831458374</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.776852645344613</v>
+        <v>3.770021203537808</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.67747083856919</v>
+        <v>-4.688856574913865</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.773895385908359</v>
+        <v>1.769341091370489</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.23913831458374</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.788723134400027</v>
+        <v>3.781891692593222</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.970366595048602</v>
+        <v>-4.981752331393277</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.657947617835538</v>
+        <v>1.653393323297668</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.23913831458374</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.789933668918971</v>
+        <v>3.783102227112166</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.15703072318341</v>
+        <v>-5.168416459528085</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.587403708808937</v>
+        <v>1.582849414271066</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2123993437591801</v>
+        <v>0.2010136074145054</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.778012028651556</v>
+        <v>3.771180586844751</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.303051410097372</v>
+        <v>-5.314437146442048</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.524073286779541</v>
+        <v>1.519518992241671</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2033162519653232</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.767640026311431</v>
+        <v>3.760808584504626</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.394765419206957</v>
+        <v>-5.406151155551633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.649591739834751</v>
+        <v>1.645037445296881</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2033162519653232</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.929844083010476</v>
+        <v>3.923012641203671</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.426417078266926</v>
+        <v>-5.437802814611603</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.631777714174578</v>
+        <v>1.627223419636707</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.198147794720883</v>
+        <v>0.1867620583762082</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.921589646627625</v>
+        <v>3.914758204820821</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.508351896535809</v>
+        <v>-5.519737632880486</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.609233204435516</v>
+        <v>1.604678909897645</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1882130491338028</v>
+        <v>0.176827312789128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.925858216843869</v>
+        <v>3.919026775037064</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.610328018784217</v>
+        <v>-5.621713755128893</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.577368393992055</v>
+        <v>1.572814099454185</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.08623692688539519</v>
+        <v>0.07485119054072042</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.873598181950726</v>
+        <v>3.866766740143922</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.500321735306995</v>
+        <v>-5.511707471651672</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.613523794627119</v>
+        <v>1.608969500089248</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1094414988026704</v>
+        <v>0.09805576245799563</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.879673812345267</v>
+        <v>3.872842370538462</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.357262159566069</v>
+        <v>-5.368647895910746</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.674997635645464</v>
+        <v>1.670443341107593</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1174549253926497</v>
+        <v>0.1060691890479749</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.888731879021229</v>
+        <v>3.881900437214424</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.055815434094232</v>
+        <v>-5.067201170438908</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.802837208716735</v>
+        <v>1.798282914178864</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4189016508644869</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.076860797186868</v>
+        <v>4.070029355380062</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.080405678329416</v>
+        <v>-5.091791414674092</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.793972288775372</v>
+        <v>1.789417994237501</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4189016508644869</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.077831974939578</v>
+        <v>4.071000533132773</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.029367302322895</v>
+        <v>-5.040753038667572</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.815230543557735</v>
+        <v>1.810676249019865</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4189016508644869</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.078674879319333</v>
+        <v>4.071843437512529</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.988228007456264</v>
+        <v>-4.999613743800941</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.850724360378533</v>
+        <v>1.846170065840663</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4600409457311178</v>
+        <v>0.448655209386443</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.122396555113458</v>
+        <v>4.115565113306652</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.891593095437624</v>
+        <v>-4.902978831782301</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.705562321309924</v>
+        <v>1.701008026772053</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5566758577497577</v>
+        <v>0.5452901214050829</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.996561498448576</v>
+        <v>3.989730056641771</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.022173829968467</v>
+        <v>-5.033559566313143</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.656832071571551</v>
+        <v>1.65227777703368</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4260951232189152</v>
+        <v>0.4147093868742404</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.921715101804034</v>
+        <v>3.91488365999723</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.857677495777505</v>
+        <v>-4.869063232122182</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.707057424324018</v>
+        <v>1.702503129786148</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5905914574098771</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.004839721394694</v>
+        <v>3.998008279587889</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.885047428461937</v>
+        <v>-4.896433164806614</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.695297161686675</v>
+        <v>1.690742867148805</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5905914574098771</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.004027431831124</v>
+        <v>3.997195990024319</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.895432623351827</v>
+        <v>-4.906818359696503</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.701011862855792</v>
+        <v>1.696457568317921</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5802062625199877</v>
+        <v>0.568820526175313</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.007665094022263</v>
+        <v>4.000833652215458</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.914020782074052</v>
+        <v>-4.925406518418728</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.764413605143327</v>
+        <v>1.759859310605457</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5616181037977623</v>
+        <v>0.5502323674530876</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.067349204565352</v>
+        <v>4.060517762758548</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.914319328770087</v>
+        <v>-4.925705065114764</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.761163197283211</v>
+        <v>1.756608902745341</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5613195571017264</v>
+        <v>0.5499338207570517</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.064039087366029</v>
+        <v>4.057207645559225</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.81349619507966</v>
+        <v>-4.824881931424336</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.806023345698774</v>
+        <v>1.801469051160903</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5737837725860803</v>
+        <v>0.5623980362414055</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.076048511596033</v>
+        <v>4.069217069789229</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.622714834327253</v>
+        <v>-4.634100570671929</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.88246514347828</v>
+        <v>1.877910848940409</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7645651333384876</v>
+        <v>0.7531793969938129</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.190646581526021</v>
+        <v>4.183815139719216</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.515751476477831</v>
+        <v>-4.527137212822508</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.905087332355645</v>
+        <v>1.900533037817774</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8230297412982891</v>
+        <v>0.8116440049536143</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.205562192039499</v>
+        <v>4.198730750232693</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.460420888576069</v>
+        <v>-4.471806624920745</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.962186504128408</v>
+        <v>1.957632209590538</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8783603292000512</v>
+        <v>0.8669745928553765</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.273727481392614</v>
+        <v>4.266896039585809</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.448366761663106</v>
+        <v>-4.459752498007783</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.960694722795031</v>
+        <v>1.956140428257161</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8904144561130141</v>
+        <v>0.8790287197683393</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.274646525441829</v>
+        <v>4.267815083635025</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.489521881231327</v>
+        <v>-4.500907617576003</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.946113305151878</v>
+        <v>1.941559010614008</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8492593365447931</v>
+        <v>0.8378736002001184</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.251834083885033</v>
+        <v>4.245002642078228</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.421473318539797</v>
+        <v>-4.432859054884474</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.986183756106373</v>
+        <v>1.981629461568502</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9173078992363229</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.305514247377833</v>
+        <v>4.298682805571028</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.653073711709298</v>
+        <v>-4.664459448053974</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.913746269012167</v>
+        <v>1.909191974474296</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9173078992363229</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.325716917551428</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.671146220000909</v>
+        <v>-4.682531956345586</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.906517265695522</v>
+        <v>1.901962971157652</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9173078992363229</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.325716917551428</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.846253052577355</v>
+        <v>-4.857638788922031</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.796726446258411</v>
+        <v>1.79217215172054</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9173078992363229</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.285968831144894</v>
+        <v>4.279137389338089</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.8149670320369</v>
+        <v>-4.826352768381576</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.816263473471533</v>
+        <v>1.811709178933662</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9485939197767783</v>
+        <v>0.9372081834321035</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.311763062466107</v>
+        <v>4.304931620659302</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.661941639923615</v>
+        <v>-4.673327376268292</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.976644629889751</v>
+        <v>1.972090335351881</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.101619311890063</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.502749297306982</v>
+        <v>4.495917855500178</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.690248953796885</v>
+        <v>-4.701634690141562</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.152787929248735</v>
+        <v>2.148233634710865</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.101619311890063</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.690215522215274</v>
+        <v>4.683384080408469</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.856842178910408</v>
+        <v>-4.868227915255084</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.055553590557408</v>
+        <v>2.050999296019538</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9350260867765401</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.559662538501243</v>
+        <v>4.552831096694439</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.833806385548842</v>
+        <v>-4.845192121893518</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.068444310563753</v>
+        <v>2.063890016025882</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9350260867765401</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.563338941162961</v>
+        <v>4.556507499356156</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.804560405093145</v>
+        <v>-4.815946141437822</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.077760757869527</v>
+        <v>2.073206463331656</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9350260867765401</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.560956996286456</v>
+        <v>4.554125554479652</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.911485952970996</v>
+        <v>-4.922871689315673</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.032283777876021</v>
+        <v>2.027729483338151</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8281005388986887</v>
+        <v>0.816714802554014</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.494094906717381</v>
+        <v>4.487263464910575</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.056504511478245</v>
+        <v>-5.067890247822922</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.975705156616356</v>
+        <v>1.971150862078485</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6830819803914402</v>
+        <v>0.6716962440467654</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.408512573756266</v>
+        <v>4.40168113194946</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.174846277262962</v>
+        <v>-5.186232013607639</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.028299689560222</v>
+        <v>2.023745395022351</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6937680189543303</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.514855436151753</v>
+        <v>4.508023994344947</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.22625669958367</v>
+        <v>-5.237642435928347</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.005521217757877</v>
+        <v>2.000966923220007</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6937680189543303</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.512641133277691</v>
+        <v>4.505809691470886</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.305676150791422</v>
+        <v>-5.317061887136099</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.973656565349066</v>
+        <v>1.969102270811196</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6937680189543303</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.512544261351981</v>
+        <v>4.505712819545176</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.40113914870864</v>
+        <v>-5.412524885053316</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.935465259740222</v>
+        <v>1.930910965202352</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6937680189543303</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.512538154910025</v>
+        <v>4.505706713103219</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.441159146752423</v>
+        <v>-5.4525448830971</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.91755365708532</v>
+        <v>1.912999362547449</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6537480209105464</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.486622552646365</v>
+        <v>4.479791110839559</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.496528308884617</v>
+        <v>-5.507914045229294</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.901139809980169</v>
+        <v>1.896585515442298</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6537480209105464</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.492356370394091</v>
+        <v>4.485524928587286</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.541966088715444</v>
+        <v>-5.553351825060121</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.882503061390771</v>
+        <v>1.8779487668529</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6109030302323868</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.466187739330128</v>
+        <v>4.459356297523323</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.453759254567866</v>
+        <v>-5.465144990912543</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.937660187900121</v>
+        <v>1.933105893362251</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6109030302323868</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.486062132180447</v>
+        <v>4.479230690373642</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.277469029962559</v>
+        <v>-5.288854766307235</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.991876978266972</v>
+        <v>1.987322683729102</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6109030302323868</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.469762832705175</v>
+        <v>4.462931390898371</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.094257366829464</v>
+        <v>-5.10564310317414</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.067592592984256</v>
+        <v>2.063038298446385</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6109030302323868</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.472193782169221</v>
+        <v>4.465362340362416</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.022535919815613</v>
+        <v>-5.033921656160289</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.062072357637685</v>
+        <v>2.057518063099815</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6826244772462374</v>
+        <v>0.6712387409015627</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.48101783622542</v>
+        <v>4.474186394418616</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.000162894207906</v>
+        <v>-5.011548630552583</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.01793731380194</v>
+        <v>2.013383019264069</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.693880228359139</v>
+        <v>0.6824944920144642</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.434687032814333</v>
+        <v>4.427855591007528</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.033179190118651</v>
+        <v>-5.044564926463328</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.189929000322997</v>
+        <v>2.185374705785127</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6244428516923874</v>
+        <v>0.6130571153477127</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.578222811699638</v>
+        <v>4.571391369892833</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.038565966369447</v>
+        <v>-5.033037290813719</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.179695515650928</v>
+        <v>2.181906985873219</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6172284980004504</v>
+        <v>0.6720577735490751</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.565815425312724</v>
+        <v>4.598712990641899</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.135907467711815</v>
+        <v>-5.130378792156088</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.144427027635769</v>
+        <v>2.14663849785806</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5728083158349621</v>
+        <v>0.6276375913835868</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.54283142853522</v>
+        <v>4.575728993864395</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.221763497051782</v>
+        <v>-5.216234821496054</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.111335698092621</v>
+        <v>2.113547168314912</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.530432246608827</v>
+        <v>0.5852615221574518</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.518656869192378</v>
+        <v>4.551554434521552</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.204954572652511</v>
+        <v>-5.199425897096783</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.100478469672831</v>
+        <v>2.102689939895122</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5544983422972072</v>
+        <v>0.6093276178458319</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.515515728425907</v>
+        <v>4.548413293755082</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950191</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.29633713521797</v>
+        <v>-5.290808459662242</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.074089955691697</v>
+        <v>2.076301425913988</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4631157797317489</v>
+        <v>0.5179450552803737</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.470850701931681</v>
+        <v>4.503748267260857</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.71713807735147</v>
+        <v>3.744102601720875</v>
       </c>
       <c r="C2076" t="n">
         <v>4.1970084398496</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.271998967103341</v>
+        <v>-5.275224529015467</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.087852428694516</v>
+        <v>2.086562203929666</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4981414298290425</v>
+        <v>0.5335289859271489</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.495893297747026</v>
+        <v>4.517125831405889</v>
       </c>
     </row>
   </sheetData>
